--- a/Template/TN.xlsx
+++ b/Template/TN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\senkx\OneDrive\Документы\LabsSGK\Дипломное проектирование\Программный продукт\Blank\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4631FC8-387F-4BC2-ABCE-E7E0AA81CD27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3705E14A-D9E8-4161-A07F-9814E2DEEE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="60">
   <si>
     <t>"</t>
   </si>
@@ -194,6 +194,12 @@
   </si>
   <si>
     <t>{total_c}</t>
+  </si>
+  <si>
+    <t>{sender_unp}</t>
+  </si>
+  <si>
+    <t>{receiver_unp}</t>
   </si>
 </sst>
 </file>
@@ -535,12 +541,150 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="5" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="49" fontId="12" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -552,144 +696,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="5" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="13">
@@ -1080,49 +1086,49 @@
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="22" t="s">
+      <c r="Z2" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="AA2" s="23"/>
-      <c r="AB2" s="23"/>
-      <c r="AC2" s="23"/>
-      <c r="AD2" s="23"/>
-      <c r="AE2" s="23"/>
-      <c r="AF2" s="23"/>
-      <c r="AG2" s="23"/>
-      <c r="AH2" s="23"/>
-      <c r="AI2" s="23"/>
-      <c r="AJ2" s="23"/>
-      <c r="AK2" s="23"/>
-      <c r="AL2" s="23"/>
-      <c r="AM2" s="23"/>
-      <c r="AN2" s="23"/>
-      <c r="AO2" s="23"/>
-      <c r="AP2" s="23"/>
-      <c r="AQ2" s="23"/>
-      <c r="AR2" s="24"/>
-      <c r="AS2" s="37" t="s">
+      <c r="AA2" s="38"/>
+      <c r="AB2" s="38"/>
+      <c r="AC2" s="38"/>
+      <c r="AD2" s="38"/>
+      <c r="AE2" s="38"/>
+      <c r="AF2" s="38"/>
+      <c r="AG2" s="38"/>
+      <c r="AH2" s="38"/>
+      <c r="AI2" s="38"/>
+      <c r="AJ2" s="38"/>
+      <c r="AK2" s="38"/>
+      <c r="AL2" s="38"/>
+      <c r="AM2" s="38"/>
+      <c r="AN2" s="38"/>
+      <c r="AO2" s="38"/>
+      <c r="AP2" s="38"/>
+      <c r="AQ2" s="38"/>
+      <c r="AR2" s="39"/>
+      <c r="AS2" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="AT2" s="38"/>
-      <c r="AU2" s="38"/>
-      <c r="AV2" s="38"/>
-      <c r="AW2" s="38"/>
-      <c r="AX2" s="38"/>
-      <c r="AY2" s="38"/>
-      <c r="AZ2" s="38"/>
-      <c r="BA2" s="38"/>
-      <c r="BB2" s="38"/>
-      <c r="BC2" s="38"/>
-      <c r="BD2" s="38"/>
-      <c r="BE2" s="38"/>
-      <c r="BF2" s="38"/>
-      <c r="BG2" s="38"/>
-      <c r="BH2" s="38"/>
-      <c r="BI2" s="38"/>
-      <c r="BJ2" s="38"/>
-      <c r="BK2" s="38"/>
-      <c r="BL2" s="39"/>
+      <c r="AT2" s="53"/>
+      <c r="AU2" s="53"/>
+      <c r="AV2" s="53"/>
+      <c r="AW2" s="53"/>
+      <c r="AX2" s="53"/>
+      <c r="AY2" s="53"/>
+      <c r="AZ2" s="53"/>
+      <c r="BA2" s="53"/>
+      <c r="BB2" s="53"/>
+      <c r="BC2" s="53"/>
+      <c r="BD2" s="53"/>
+      <c r="BE2" s="53"/>
+      <c r="BF2" s="53"/>
+      <c r="BG2" s="53"/>
+      <c r="BH2" s="53"/>
+      <c r="BI2" s="53"/>
+      <c r="BJ2" s="53"/>
+      <c r="BK2" s="53"/>
+      <c r="BL2" s="54"/>
       <c r="BM2" s="1"/>
       <c r="BN2" s="1"/>
       <c r="BO2" s="1"/>
@@ -1259,45 +1265,45 @@
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="25"/>
-      <c r="AA3" s="26"/>
-      <c r="AB3" s="26"/>
-      <c r="AC3" s="26"/>
-      <c r="AD3" s="26"/>
-      <c r="AE3" s="26"/>
-      <c r="AF3" s="26"/>
-      <c r="AG3" s="26"/>
-      <c r="AH3" s="26"/>
-      <c r="AI3" s="26"/>
-      <c r="AJ3" s="26"/>
-      <c r="AK3" s="26"/>
-      <c r="AL3" s="26"/>
-      <c r="AM3" s="26"/>
-      <c r="AN3" s="26"/>
-      <c r="AO3" s="26"/>
-      <c r="AP3" s="26"/>
-      <c r="AQ3" s="26"/>
-      <c r="AR3" s="27"/>
-      <c r="AS3" s="40"/>
-      <c r="AT3" s="41"/>
-      <c r="AU3" s="41"/>
-      <c r="AV3" s="41"/>
-      <c r="AW3" s="41"/>
-      <c r="AX3" s="41"/>
-      <c r="AY3" s="41"/>
-      <c r="AZ3" s="41"/>
-      <c r="BA3" s="41"/>
-      <c r="BB3" s="41"/>
-      <c r="BC3" s="41"/>
-      <c r="BD3" s="41"/>
-      <c r="BE3" s="41"/>
-      <c r="BF3" s="41"/>
-      <c r="BG3" s="41"/>
-      <c r="BH3" s="41"/>
-      <c r="BI3" s="41"/>
-      <c r="BJ3" s="41"/>
-      <c r="BK3" s="41"/>
-      <c r="BL3" s="42"/>
+      <c r="Z3" s="40"/>
+      <c r="AA3" s="41"/>
+      <c r="AB3" s="41"/>
+      <c r="AC3" s="41"/>
+      <c r="AD3" s="41"/>
+      <c r="AE3" s="41"/>
+      <c r="AF3" s="41"/>
+      <c r="AG3" s="41"/>
+      <c r="AH3" s="41"/>
+      <c r="AI3" s="41"/>
+      <c r="AJ3" s="41"/>
+      <c r="AK3" s="41"/>
+      <c r="AL3" s="41"/>
+      <c r="AM3" s="41"/>
+      <c r="AN3" s="41"/>
+      <c r="AO3" s="41"/>
+      <c r="AP3" s="41"/>
+      <c r="AQ3" s="41"/>
+      <c r="AR3" s="42"/>
+      <c r="AS3" s="55"/>
+      <c r="AT3" s="56"/>
+      <c r="AU3" s="56"/>
+      <c r="AV3" s="56"/>
+      <c r="AW3" s="56"/>
+      <c r="AX3" s="56"/>
+      <c r="AY3" s="56"/>
+      <c r="AZ3" s="56"/>
+      <c r="BA3" s="56"/>
+      <c r="BB3" s="56"/>
+      <c r="BC3" s="56"/>
+      <c r="BD3" s="56"/>
+      <c r="BE3" s="56"/>
+      <c r="BF3" s="56"/>
+      <c r="BG3" s="56"/>
+      <c r="BH3" s="56"/>
+      <c r="BI3" s="56"/>
+      <c r="BJ3" s="56"/>
+      <c r="BK3" s="56"/>
+      <c r="BL3" s="57"/>
       <c r="BM3" s="1"/>
       <c r="BN3" s="1"/>
       <c r="BO3" s="1"/>
@@ -1434,45 +1440,45 @@
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="Z4" s="28"/>
-      <c r="AA4" s="29"/>
-      <c r="AB4" s="29"/>
-      <c r="AC4" s="29"/>
-      <c r="AD4" s="29"/>
-      <c r="AE4" s="29"/>
-      <c r="AF4" s="29"/>
-      <c r="AG4" s="29"/>
-      <c r="AH4" s="29"/>
-      <c r="AI4" s="29"/>
-      <c r="AJ4" s="29"/>
-      <c r="AK4" s="29"/>
-      <c r="AL4" s="29"/>
-      <c r="AM4" s="29"/>
-      <c r="AN4" s="29"/>
-      <c r="AO4" s="29"/>
-      <c r="AP4" s="29"/>
-      <c r="AQ4" s="29"/>
-      <c r="AR4" s="30"/>
-      <c r="AS4" s="43"/>
-      <c r="AT4" s="44"/>
-      <c r="AU4" s="44"/>
-      <c r="AV4" s="44"/>
-      <c r="AW4" s="44"/>
-      <c r="AX4" s="44"/>
-      <c r="AY4" s="44"/>
-      <c r="AZ4" s="44"/>
-      <c r="BA4" s="44"/>
-      <c r="BB4" s="44"/>
-      <c r="BC4" s="44"/>
-      <c r="BD4" s="44"/>
-      <c r="BE4" s="44"/>
-      <c r="BF4" s="44"/>
-      <c r="BG4" s="44"/>
-      <c r="BH4" s="44"/>
-      <c r="BI4" s="44"/>
-      <c r="BJ4" s="44"/>
-      <c r="BK4" s="44"/>
-      <c r="BL4" s="45"/>
+      <c r="Z4" s="43"/>
+      <c r="AA4" s="44"/>
+      <c r="AB4" s="44"/>
+      <c r="AC4" s="44"/>
+      <c r="AD4" s="44"/>
+      <c r="AE4" s="44"/>
+      <c r="AF4" s="44"/>
+      <c r="AG4" s="44"/>
+      <c r="AH4" s="44"/>
+      <c r="AI4" s="44"/>
+      <c r="AJ4" s="44"/>
+      <c r="AK4" s="44"/>
+      <c r="AL4" s="44"/>
+      <c r="AM4" s="44"/>
+      <c r="AN4" s="44"/>
+      <c r="AO4" s="44"/>
+      <c r="AP4" s="44"/>
+      <c r="AQ4" s="44"/>
+      <c r="AR4" s="45"/>
+      <c r="AS4" s="58"/>
+      <c r="AT4" s="59"/>
+      <c r="AU4" s="59"/>
+      <c r="AV4" s="59"/>
+      <c r="AW4" s="59"/>
+      <c r="AX4" s="59"/>
+      <c r="AY4" s="59"/>
+      <c r="AZ4" s="59"/>
+      <c r="BA4" s="59"/>
+      <c r="BB4" s="59"/>
+      <c r="BC4" s="59"/>
+      <c r="BD4" s="59"/>
+      <c r="BE4" s="59"/>
+      <c r="BF4" s="59"/>
+      <c r="BG4" s="59"/>
+      <c r="BH4" s="59"/>
+      <c r="BI4" s="59"/>
+      <c r="BJ4" s="59"/>
+      <c r="BK4" s="59"/>
+      <c r="BL4" s="60"/>
       <c r="BM4" s="1"/>
       <c r="BN4" s="1"/>
       <c r="BO4" s="1"/>
@@ -1603,57 +1609,57 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="47" t="s">
+      <c r="T5" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="U5" s="47"/>
-      <c r="V5" s="47"/>
-      <c r="W5" s="47"/>
-      <c r="X5" s="47"/>
+      <c r="U5" s="33"/>
+      <c r="V5" s="33"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="33"/>
       <c r="Y5" s="1"/>
-      <c r="Z5" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="32"/>
-      <c r="AD5" s="32"/>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="32"/>
-      <c r="AG5" s="32"/>
-      <c r="AH5" s="32"/>
-      <c r="AI5" s="32"/>
-      <c r="AJ5" s="32"/>
-      <c r="AK5" s="32"/>
-      <c r="AL5" s="32"/>
-      <c r="AM5" s="32"/>
-      <c r="AN5" s="32"/>
-      <c r="AO5" s="32"/>
-      <c r="AP5" s="32"/>
-      <c r="AQ5" s="32"/>
-      <c r="AR5" s="33"/>
-      <c r="AS5" s="31" t="s">
-        <v>40</v>
-      </c>
-      <c r="AT5" s="32"/>
-      <c r="AU5" s="32"/>
-      <c r="AV5" s="32"/>
-      <c r="AW5" s="32"/>
-      <c r="AX5" s="32"/>
-      <c r="AY5" s="32"/>
-      <c r="AZ5" s="32"/>
-      <c r="BA5" s="32"/>
-      <c r="BB5" s="32"/>
-      <c r="BC5" s="32"/>
-      <c r="BD5" s="32"/>
-      <c r="BE5" s="32"/>
-      <c r="BF5" s="32"/>
-      <c r="BG5" s="32"/>
-      <c r="BH5" s="32"/>
-      <c r="BI5" s="32"/>
-      <c r="BJ5" s="32"/>
-      <c r="BK5" s="32"/>
-      <c r="BL5" s="33"/>
+      <c r="Z5" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA5" s="47"/>
+      <c r="AB5" s="47"/>
+      <c r="AC5" s="47"/>
+      <c r="AD5" s="47"/>
+      <c r="AE5" s="47"/>
+      <c r="AF5" s="47"/>
+      <c r="AG5" s="47"/>
+      <c r="AH5" s="47"/>
+      <c r="AI5" s="47"/>
+      <c r="AJ5" s="47"/>
+      <c r="AK5" s="47"/>
+      <c r="AL5" s="47"/>
+      <c r="AM5" s="47"/>
+      <c r="AN5" s="47"/>
+      <c r="AO5" s="47"/>
+      <c r="AP5" s="47"/>
+      <c r="AQ5" s="47"/>
+      <c r="AR5" s="48"/>
+      <c r="AS5" s="46" t="s">
+        <v>59</v>
+      </c>
+      <c r="AT5" s="47"/>
+      <c r="AU5" s="47"/>
+      <c r="AV5" s="47"/>
+      <c r="AW5" s="47"/>
+      <c r="AX5" s="47"/>
+      <c r="AY5" s="47"/>
+      <c r="AZ5" s="47"/>
+      <c r="BA5" s="47"/>
+      <c r="BB5" s="47"/>
+      <c r="BC5" s="47"/>
+      <c r="BD5" s="47"/>
+      <c r="BE5" s="47"/>
+      <c r="BF5" s="47"/>
+      <c r="BG5" s="47"/>
+      <c r="BH5" s="47"/>
+      <c r="BI5" s="47"/>
+      <c r="BJ5" s="47"/>
+      <c r="BK5" s="47"/>
+      <c r="BL5" s="48"/>
       <c r="BM5" s="1"/>
       <c r="BN5" s="1"/>
       <c r="BO5" s="1"/>
@@ -1784,51 +1790,51 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="47"/>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="33"/>
+      <c r="V6" s="33"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="33"/>
       <c r="Y6" s="1"/>
-      <c r="Z6" s="34"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="35"/>
-      <c r="AC6" s="35"/>
-      <c r="AD6" s="35"/>
-      <c r="AE6" s="35"/>
-      <c r="AF6" s="35"/>
-      <c r="AG6" s="35"/>
-      <c r="AH6" s="35"/>
-      <c r="AI6" s="35"/>
-      <c r="AJ6" s="35"/>
-      <c r="AK6" s="35"/>
-      <c r="AL6" s="35"/>
-      <c r="AM6" s="35"/>
-      <c r="AN6" s="35"/>
-      <c r="AO6" s="35"/>
-      <c r="AP6" s="35"/>
-      <c r="AQ6" s="35"/>
-      <c r="AR6" s="36"/>
-      <c r="AS6" s="34"/>
-      <c r="AT6" s="35"/>
-      <c r="AU6" s="35"/>
-      <c r="AV6" s="35"/>
-      <c r="AW6" s="35"/>
-      <c r="AX6" s="35"/>
-      <c r="AY6" s="35"/>
-      <c r="AZ6" s="35"/>
-      <c r="BA6" s="35"/>
-      <c r="BB6" s="35"/>
-      <c r="BC6" s="35"/>
-      <c r="BD6" s="35"/>
-      <c r="BE6" s="35"/>
-      <c r="BF6" s="35"/>
-      <c r="BG6" s="35"/>
-      <c r="BH6" s="35"/>
-      <c r="BI6" s="35"/>
-      <c r="BJ6" s="35"/>
-      <c r="BK6" s="35"/>
-      <c r="BL6" s="36"/>
+      <c r="Z6" s="49"/>
+      <c r="AA6" s="50"/>
+      <c r="AB6" s="50"/>
+      <c r="AC6" s="50"/>
+      <c r="AD6" s="50"/>
+      <c r="AE6" s="50"/>
+      <c r="AF6" s="50"/>
+      <c r="AG6" s="50"/>
+      <c r="AH6" s="50"/>
+      <c r="AI6" s="50"/>
+      <c r="AJ6" s="50"/>
+      <c r="AK6" s="50"/>
+      <c r="AL6" s="50"/>
+      <c r="AM6" s="50"/>
+      <c r="AN6" s="50"/>
+      <c r="AO6" s="50"/>
+      <c r="AP6" s="50"/>
+      <c r="AQ6" s="50"/>
+      <c r="AR6" s="51"/>
+      <c r="AS6" s="49"/>
+      <c r="AT6" s="50"/>
+      <c r="AU6" s="50"/>
+      <c r="AV6" s="50"/>
+      <c r="AW6" s="50"/>
+      <c r="AX6" s="50"/>
+      <c r="AY6" s="50"/>
+      <c r="AZ6" s="50"/>
+      <c r="BA6" s="50"/>
+      <c r="BB6" s="50"/>
+      <c r="BC6" s="50"/>
+      <c r="BD6" s="50"/>
+      <c r="BE6" s="50"/>
+      <c r="BF6" s="50"/>
+      <c r="BG6" s="50"/>
+      <c r="BH6" s="50"/>
+      <c r="BI6" s="50"/>
+      <c r="BJ6" s="50"/>
+      <c r="BK6" s="50"/>
+      <c r="BL6" s="51"/>
       <c r="BM6" s="1"/>
       <c r="BN6" s="1"/>
       <c r="BO6" s="1"/>
@@ -1967,256 +1973,256 @@
       <c r="CW15" s="2"/>
     </row>
     <row r="16" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Z16" s="57" t="s">
+      <c r="Z16" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="AA16" s="57"/>
-      <c r="AB16" s="58"/>
-      <c r="AC16" s="58"/>
-      <c r="AD16" s="58"/>
-      <c r="AE16" s="58"/>
-      <c r="AF16" s="53" t="s">
+      <c r="AA16" s="23"/>
+      <c r="AB16" s="62"/>
+      <c r="AC16" s="62"/>
+      <c r="AD16" s="62"/>
+      <c r="AE16" s="62"/>
+      <c r="AF16" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="AG16" s="53"/>
-      <c r="AI16" s="54" t="s">
+      <c r="AG16" s="19"/>
+      <c r="AI16" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="AJ16" s="54"/>
-      <c r="AK16" s="54"/>
-      <c r="AL16" s="54"/>
-      <c r="AM16" s="54"/>
-      <c r="AN16" s="54"/>
-      <c r="AO16" s="54"/>
-      <c r="AP16" s="54"/>
-      <c r="AQ16" s="54"/>
-      <c r="AR16" s="54"/>
-      <c r="AS16" s="54"/>
-      <c r="AT16" s="54"/>
-      <c r="AU16" s="54"/>
-      <c r="AV16" s="54"/>
-      <c r="AW16" s="54"/>
-      <c r="AX16" s="54"/>
-      <c r="AY16" s="54"/>
-      <c r="AZ16" s="54"/>
-      <c r="BA16" s="54"/>
-      <c r="BB16" s="54"/>
-      <c r="BC16" s="54"/>
-      <c r="BD16" s="54"/>
-      <c r="BF16" s="57">
+      <c r="AJ16" s="20"/>
+      <c r="AK16" s="20"/>
+      <c r="AL16" s="20"/>
+      <c r="AM16" s="20"/>
+      <c r="AN16" s="20"/>
+      <c r="AO16" s="20"/>
+      <c r="AP16" s="20"/>
+      <c r="AQ16" s="20"/>
+      <c r="AR16" s="20"/>
+      <c r="AS16" s="20"/>
+      <c r="AT16" s="20"/>
+      <c r="AU16" s="20"/>
+      <c r="AV16" s="20"/>
+      <c r="AW16" s="20"/>
+      <c r="AX16" s="20"/>
+      <c r="AY16" s="20"/>
+      <c r="AZ16" s="20"/>
+      <c r="BA16" s="20"/>
+      <c r="BB16" s="20"/>
+      <c r="BC16" s="20"/>
+      <c r="BD16" s="20"/>
+      <c r="BF16" s="23">
         <v>20</v>
       </c>
-      <c r="BG16" s="57"/>
-      <c r="BH16" s="57"/>
-      <c r="BI16" s="56"/>
-      <c r="BJ16" s="56"/>
-      <c r="BK16" s="56"/>
-      <c r="BM16" s="53" t="s">
+      <c r="BG16" s="23"/>
+      <c r="BH16" s="23"/>
+      <c r="BI16" s="61"/>
+      <c r="BJ16" s="61"/>
+      <c r="BK16" s="61"/>
+      <c r="BM16" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="BN16" s="53"/>
-      <c r="BO16" s="53"/>
+      <c r="BN16" s="19"/>
+      <c r="BO16" s="19"/>
       <c r="CW16" s="2"/>
     </row>
     <row r="17" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CW17" s="2"/>
     </row>
     <row r="18" spans="1:173" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="53" t="s">
+      <c r="A18" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="53"/>
-      <c r="C18" s="53"/>
-      <c r="D18" s="53"/>
-      <c r="E18" s="53"/>
-      <c r="F18" s="53"/>
-      <c r="G18" s="53"/>
-      <c r="H18" s="53"/>
-      <c r="I18" s="53"/>
-      <c r="J18" s="53"/>
-      <c r="K18" s="53"/>
-      <c r="L18" s="53"/>
-      <c r="M18" s="53"/>
-      <c r="N18" s="53"/>
-      <c r="O18" s="53"/>
-      <c r="P18" s="53"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
       <c r="Q18" s="4"/>
-      <c r="R18" s="54" t="s">
+      <c r="R18" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="S18" s="54"/>
-      <c r="T18" s="54"/>
-      <c r="U18" s="54"/>
-      <c r="V18" s="54"/>
-      <c r="W18" s="54"/>
-      <c r="X18" s="54"/>
-      <c r="Y18" s="54"/>
-      <c r="Z18" s="54"/>
-      <c r="AA18" s="54"/>
-      <c r="AB18" s="54"/>
-      <c r="AC18" s="54"/>
-      <c r="AD18" s="54"/>
-      <c r="AE18" s="54"/>
-      <c r="AF18" s="54"/>
-      <c r="AG18" s="54"/>
-      <c r="AH18" s="54"/>
-      <c r="AI18" s="54"/>
-      <c r="AJ18" s="54"/>
-      <c r="AK18" s="54"/>
-      <c r="AL18" s="54"/>
-      <c r="AM18" s="54"/>
-      <c r="AN18" s="54"/>
-      <c r="AO18" s="54"/>
-      <c r="AP18" s="54"/>
-      <c r="AQ18" s="54"/>
-      <c r="AR18" s="54"/>
-      <c r="AS18" s="54"/>
-      <c r="AT18" s="54"/>
-      <c r="AU18" s="54"/>
-      <c r="AV18" s="54"/>
-      <c r="AW18" s="54"/>
-      <c r="AX18" s="54"/>
-      <c r="AY18" s="54"/>
-      <c r="AZ18" s="54"/>
-      <c r="BA18" s="54"/>
-      <c r="BB18" s="54"/>
-      <c r="BC18" s="54"/>
-      <c r="BD18" s="54"/>
-      <c r="BE18" s="54"/>
-      <c r="BF18" s="54"/>
-      <c r="BG18" s="54"/>
-      <c r="BH18" s="54"/>
-      <c r="BI18" s="54"/>
-      <c r="BJ18" s="54"/>
-      <c r="BK18" s="54"/>
-      <c r="BL18" s="54"/>
-      <c r="BM18" s="54"/>
-      <c r="BN18" s="54"/>
-      <c r="BO18" s="54"/>
-      <c r="BP18" s="54"/>
-      <c r="BQ18" s="54"/>
-      <c r="BR18" s="54"/>
-      <c r="BS18" s="54"/>
-      <c r="BT18" s="54"/>
-      <c r="BU18" s="54"/>
-      <c r="BV18" s="54"/>
-      <c r="BW18" s="54"/>
-      <c r="BX18" s="54"/>
-      <c r="BY18" s="54"/>
-      <c r="BZ18" s="54"/>
-      <c r="CA18" s="54"/>
-      <c r="CB18" s="54"/>
-      <c r="CC18" s="54"/>
-      <c r="CD18" s="54"/>
-      <c r="CE18" s="54"/>
-      <c r="CF18" s="54"/>
-      <c r="CG18" s="54"/>
-      <c r="CH18" s="54"/>
-      <c r="CI18" s="54"/>
-      <c r="CJ18" s="54"/>
-      <c r="CK18" s="54"/>
-      <c r="CL18" s="54"/>
-      <c r="CM18" s="54"/>
-      <c r="CN18" s="54"/>
-      <c r="CO18" s="54"/>
-      <c r="CP18" s="54"/>
-      <c r="CQ18" s="54"/>
-      <c r="CR18" s="54"/>
-      <c r="CS18" s="54"/>
-      <c r="CT18" s="54"/>
-      <c r="CU18" s="54"/>
-      <c r="CV18" s="54"/>
+      <c r="S18" s="20"/>
+      <c r="T18" s="20"/>
+      <c r="U18" s="20"/>
+      <c r="V18" s="20"/>
+      <c r="W18" s="20"/>
+      <c r="X18" s="20"/>
+      <c r="Y18" s="20"/>
+      <c r="Z18" s="20"/>
+      <c r="AA18" s="20"/>
+      <c r="AB18" s="20"/>
+      <c r="AC18" s="20"/>
+      <c r="AD18" s="20"/>
+      <c r="AE18" s="20"/>
+      <c r="AF18" s="20"/>
+      <c r="AG18" s="20"/>
+      <c r="AH18" s="20"/>
+      <c r="AI18" s="20"/>
+      <c r="AJ18" s="20"/>
+      <c r="AK18" s="20"/>
+      <c r="AL18" s="20"/>
+      <c r="AM18" s="20"/>
+      <c r="AN18" s="20"/>
+      <c r="AO18" s="20"/>
+      <c r="AP18" s="20"/>
+      <c r="AQ18" s="20"/>
+      <c r="AR18" s="20"/>
+      <c r="AS18" s="20"/>
+      <c r="AT18" s="20"/>
+      <c r="AU18" s="20"/>
+      <c r="AV18" s="20"/>
+      <c r="AW18" s="20"/>
+      <c r="AX18" s="20"/>
+      <c r="AY18" s="20"/>
+      <c r="AZ18" s="20"/>
+      <c r="BA18" s="20"/>
+      <c r="BB18" s="20"/>
+      <c r="BC18" s="20"/>
+      <c r="BD18" s="20"/>
+      <c r="BE18" s="20"/>
+      <c r="BF18" s="20"/>
+      <c r="BG18" s="20"/>
+      <c r="BH18" s="20"/>
+      <c r="BI18" s="20"/>
+      <c r="BJ18" s="20"/>
+      <c r="BK18" s="20"/>
+      <c r="BL18" s="20"/>
+      <c r="BM18" s="20"/>
+      <c r="BN18" s="20"/>
+      <c r="BO18" s="20"/>
+      <c r="BP18" s="20"/>
+      <c r="BQ18" s="20"/>
+      <c r="BR18" s="20"/>
+      <c r="BS18" s="20"/>
+      <c r="BT18" s="20"/>
+      <c r="BU18" s="20"/>
+      <c r="BV18" s="20"/>
+      <c r="BW18" s="20"/>
+      <c r="BX18" s="20"/>
+      <c r="BY18" s="20"/>
+      <c r="BZ18" s="20"/>
+      <c r="CA18" s="20"/>
+      <c r="CB18" s="20"/>
+      <c r="CC18" s="20"/>
+      <c r="CD18" s="20"/>
+      <c r="CE18" s="20"/>
+      <c r="CF18" s="20"/>
+      <c r="CG18" s="20"/>
+      <c r="CH18" s="20"/>
+      <c r="CI18" s="20"/>
+      <c r="CJ18" s="20"/>
+      <c r="CK18" s="20"/>
+      <c r="CL18" s="20"/>
+      <c r="CM18" s="20"/>
+      <c r="CN18" s="20"/>
+      <c r="CO18" s="20"/>
+      <c r="CP18" s="20"/>
+      <c r="CQ18" s="20"/>
+      <c r="CR18" s="20"/>
+      <c r="CS18" s="20"/>
+      <c r="CT18" s="20"/>
+      <c r="CU18" s="20"/>
+      <c r="CV18" s="20"/>
       <c r="CW18" s="2"/>
     </row>
     <row r="19" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
-      <c r="R19" s="55" t="s">
+      <c r="R19" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="S19" s="55"/>
-      <c r="T19" s="55"/>
-      <c r="U19" s="55"/>
-      <c r="V19" s="55"/>
-      <c r="W19" s="55"/>
-      <c r="X19" s="55"/>
-      <c r="Y19" s="55"/>
-      <c r="Z19" s="55"/>
-      <c r="AA19" s="55"/>
-      <c r="AB19" s="55"/>
-      <c r="AC19" s="55"/>
-      <c r="AD19" s="55"/>
-      <c r="AE19" s="55"/>
-      <c r="AF19" s="55"/>
-      <c r="AG19" s="55"/>
-      <c r="AH19" s="55"/>
-      <c r="AI19" s="55"/>
-      <c r="AJ19" s="55"/>
-      <c r="AK19" s="55"/>
-      <c r="AL19" s="55"/>
-      <c r="AM19" s="55"/>
-      <c r="AN19" s="55"/>
-      <c r="AO19" s="55"/>
-      <c r="AP19" s="55"/>
-      <c r="AQ19" s="55"/>
-      <c r="AR19" s="55"/>
-      <c r="AS19" s="55"/>
-      <c r="AT19" s="55"/>
-      <c r="AU19" s="55"/>
-      <c r="AV19" s="55"/>
-      <c r="AW19" s="55"/>
-      <c r="AX19" s="55"/>
-      <c r="AY19" s="55"/>
-      <c r="AZ19" s="55"/>
-      <c r="BA19" s="55"/>
-      <c r="BB19" s="55"/>
-      <c r="BC19" s="55"/>
-      <c r="BD19" s="55"/>
-      <c r="BE19" s="55"/>
-      <c r="BF19" s="55"/>
-      <c r="BG19" s="55"/>
-      <c r="BH19" s="55"/>
-      <c r="BI19" s="55"/>
-      <c r="BJ19" s="55"/>
-      <c r="BK19" s="55"/>
-      <c r="BL19" s="55"/>
-      <c r="BM19" s="55"/>
-      <c r="BN19" s="55"/>
-      <c r="BO19" s="55"/>
-      <c r="BP19" s="55"/>
-      <c r="BQ19" s="55"/>
-      <c r="BR19" s="55"/>
-      <c r="BS19" s="55"/>
-      <c r="BT19" s="55"/>
-      <c r="BU19" s="55"/>
-      <c r="BV19" s="55"/>
-      <c r="BW19" s="55"/>
-      <c r="BX19" s="55"/>
-      <c r="BY19" s="55"/>
-      <c r="BZ19" s="55"/>
-      <c r="CA19" s="55"/>
-      <c r="CB19" s="55"/>
-      <c r="CC19" s="55"/>
-      <c r="CD19" s="55"/>
-      <c r="CE19" s="55"/>
-      <c r="CF19" s="55"/>
-      <c r="CG19" s="55"/>
-      <c r="CH19" s="55"/>
-      <c r="CI19" s="55"/>
-      <c r="CJ19" s="55"/>
-      <c r="CK19" s="55"/>
-      <c r="CL19" s="55"/>
-      <c r="CM19" s="55"/>
-      <c r="CN19" s="55"/>
-      <c r="CO19" s="55"/>
-      <c r="CP19" s="55"/>
-      <c r="CQ19" s="55"/>
-      <c r="CR19" s="55"/>
-      <c r="CS19" s="55"/>
-      <c r="CT19" s="55"/>
-      <c r="CU19" s="55"/>
-      <c r="CV19" s="55"/>
+      <c r="S19" s="21"/>
+      <c r="T19" s="21"/>
+      <c r="U19" s="21"/>
+      <c r="V19" s="21"/>
+      <c r="W19" s="21"/>
+      <c r="X19" s="21"/>
+      <c r="Y19" s="21"/>
+      <c r="Z19" s="21"/>
+      <c r="AA19" s="21"/>
+      <c r="AB19" s="21"/>
+      <c r="AC19" s="21"/>
+      <c r="AD19" s="21"/>
+      <c r="AE19" s="21"/>
+      <c r="AF19" s="21"/>
+      <c r="AG19" s="21"/>
+      <c r="AH19" s="21"/>
+      <c r="AI19" s="21"/>
+      <c r="AJ19" s="21"/>
+      <c r="AK19" s="21"/>
+      <c r="AL19" s="21"/>
+      <c r="AM19" s="21"/>
+      <c r="AN19" s="21"/>
+      <c r="AO19" s="21"/>
+      <c r="AP19" s="21"/>
+      <c r="AQ19" s="21"/>
+      <c r="AR19" s="21"/>
+      <c r="AS19" s="21"/>
+      <c r="AT19" s="21"/>
+      <c r="AU19" s="21"/>
+      <c r="AV19" s="21"/>
+      <c r="AW19" s="21"/>
+      <c r="AX19" s="21"/>
+      <c r="AY19" s="21"/>
+      <c r="AZ19" s="21"/>
+      <c r="BA19" s="21"/>
+      <c r="BB19" s="21"/>
+      <c r="BC19" s="21"/>
+      <c r="BD19" s="21"/>
+      <c r="BE19" s="21"/>
+      <c r="BF19" s="21"/>
+      <c r="BG19" s="21"/>
+      <c r="BH19" s="21"/>
+      <c r="BI19" s="21"/>
+      <c r="BJ19" s="21"/>
+      <c r="BK19" s="21"/>
+      <c r="BL19" s="21"/>
+      <c r="BM19" s="21"/>
+      <c r="BN19" s="21"/>
+      <c r="BO19" s="21"/>
+      <c r="BP19" s="21"/>
+      <c r="BQ19" s="21"/>
+      <c r="BR19" s="21"/>
+      <c r="BS19" s="21"/>
+      <c r="BT19" s="21"/>
+      <c r="BU19" s="21"/>
+      <c r="BV19" s="21"/>
+      <c r="BW19" s="21"/>
+      <c r="BX19" s="21"/>
+      <c r="BY19" s="21"/>
+      <c r="BZ19" s="21"/>
+      <c r="CA19" s="21"/>
+      <c r="CB19" s="21"/>
+      <c r="CC19" s="21"/>
+      <c r="CD19" s="21"/>
+      <c r="CE19" s="21"/>
+      <c r="CF19" s="21"/>
+      <c r="CG19" s="21"/>
+      <c r="CH19" s="21"/>
+      <c r="CI19" s="21"/>
+      <c r="CJ19" s="21"/>
+      <c r="CK19" s="21"/>
+      <c r="CL19" s="21"/>
+      <c r="CM19" s="21"/>
+      <c r="CN19" s="21"/>
+      <c r="CO19" s="21"/>
+      <c r="CP19" s="21"/>
+      <c r="CQ19" s="21"/>
+      <c r="CR19" s="21"/>
+      <c r="CS19" s="21"/>
+      <c r="CT19" s="21"/>
+      <c r="CU19" s="21"/>
+      <c r="CV19" s="21"/>
       <c r="CW19" s="2"/>
     </row>
     <row r="20" spans="1:173" ht="3" customHeight="1" x14ac:dyDescent="0.2">
@@ -2309,110 +2315,110 @@
       <c r="CW20" s="2"/>
     </row>
     <row r="21" spans="1:173" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="53" t="s">
+      <c r="A21" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="53"/>
-      <c r="C21" s="53"/>
-      <c r="D21" s="53"/>
-      <c r="E21" s="53"/>
-      <c r="F21" s="53"/>
-      <c r="G21" s="53"/>
-      <c r="H21" s="53"/>
-      <c r="I21" s="53"/>
-      <c r="J21" s="53"/>
-      <c r="K21" s="53"/>
-      <c r="L21" s="53"/>
-      <c r="M21" s="53"/>
-      <c r="N21" s="53"/>
-      <c r="O21" s="53"/>
-      <c r="P21" s="53"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+      <c r="L21" s="19"/>
+      <c r="M21" s="19"/>
+      <c r="N21" s="19"/>
+      <c r="O21" s="19"/>
+      <c r="P21" s="19"/>
       <c r="Q21" s="4"/>
-      <c r="R21" s="54" t="s">
+      <c r="R21" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="S21" s="54"/>
-      <c r="T21" s="54"/>
-      <c r="U21" s="54"/>
-      <c r="V21" s="54"/>
-      <c r="W21" s="54"/>
-      <c r="X21" s="54"/>
-      <c r="Y21" s="54"/>
-      <c r="Z21" s="54"/>
-      <c r="AA21" s="54"/>
-      <c r="AB21" s="54"/>
-      <c r="AC21" s="54"/>
-      <c r="AD21" s="54"/>
-      <c r="AE21" s="54"/>
-      <c r="AF21" s="54"/>
-      <c r="AG21" s="54"/>
-      <c r="AH21" s="54"/>
-      <c r="AI21" s="54"/>
-      <c r="AJ21" s="54"/>
-      <c r="AK21" s="54"/>
-      <c r="AL21" s="54"/>
-      <c r="AM21" s="54"/>
-      <c r="AN21" s="54"/>
-      <c r="AO21" s="54"/>
-      <c r="AP21" s="54"/>
-      <c r="AQ21" s="54"/>
-      <c r="AR21" s="54"/>
-      <c r="AS21" s="54"/>
-      <c r="AT21" s="54"/>
-      <c r="AU21" s="54"/>
-      <c r="AV21" s="54"/>
-      <c r="AW21" s="54"/>
-      <c r="AX21" s="54"/>
-      <c r="AY21" s="54"/>
-      <c r="AZ21" s="54"/>
-      <c r="BA21" s="54"/>
-      <c r="BB21" s="54"/>
-      <c r="BC21" s="54"/>
-      <c r="BD21" s="54"/>
-      <c r="BE21" s="54"/>
-      <c r="BF21" s="54"/>
-      <c r="BG21" s="54"/>
-      <c r="BH21" s="54"/>
-      <c r="BI21" s="54"/>
-      <c r="BJ21" s="54"/>
-      <c r="BK21" s="54"/>
-      <c r="BL21" s="54"/>
-      <c r="BM21" s="54"/>
-      <c r="BN21" s="54"/>
-      <c r="BO21" s="54"/>
-      <c r="BP21" s="54"/>
-      <c r="BQ21" s="54"/>
-      <c r="BR21" s="54"/>
-      <c r="BS21" s="54"/>
-      <c r="BT21" s="54"/>
-      <c r="BU21" s="54"/>
-      <c r="BV21" s="54"/>
-      <c r="BW21" s="54"/>
-      <c r="BX21" s="54"/>
-      <c r="BY21" s="54"/>
-      <c r="BZ21" s="54"/>
-      <c r="CA21" s="54"/>
-      <c r="CB21" s="54"/>
-      <c r="CC21" s="54"/>
-      <c r="CD21" s="54"/>
-      <c r="CE21" s="54"/>
-      <c r="CF21" s="54"/>
-      <c r="CG21" s="54"/>
-      <c r="CH21" s="54"/>
-      <c r="CI21" s="54"/>
-      <c r="CJ21" s="54"/>
-      <c r="CK21" s="54"/>
-      <c r="CL21" s="54"/>
-      <c r="CM21" s="54"/>
-      <c r="CN21" s="54"/>
-      <c r="CO21" s="54"/>
-      <c r="CP21" s="54"/>
-      <c r="CQ21" s="54"/>
-      <c r="CR21" s="54"/>
-      <c r="CS21" s="54"/>
-      <c r="CT21" s="54"/>
-      <c r="CU21" s="54"/>
-      <c r="CV21" s="54"/>
+      <c r="S21" s="20"/>
+      <c r="T21" s="20"/>
+      <c r="U21" s="20"/>
+      <c r="V21" s="20"/>
+      <c r="W21" s="20"/>
+      <c r="X21" s="20"/>
+      <c r="Y21" s="20"/>
+      <c r="Z21" s="20"/>
+      <c r="AA21" s="20"/>
+      <c r="AB21" s="20"/>
+      <c r="AC21" s="20"/>
+      <c r="AD21" s="20"/>
+      <c r="AE21" s="20"/>
+      <c r="AF21" s="20"/>
+      <c r="AG21" s="20"/>
+      <c r="AH21" s="20"/>
+      <c r="AI21" s="20"/>
+      <c r="AJ21" s="20"/>
+      <c r="AK21" s="20"/>
+      <c r="AL21" s="20"/>
+      <c r="AM21" s="20"/>
+      <c r="AN21" s="20"/>
+      <c r="AO21" s="20"/>
+      <c r="AP21" s="20"/>
+      <c r="AQ21" s="20"/>
+      <c r="AR21" s="20"/>
+      <c r="AS21" s="20"/>
+      <c r="AT21" s="20"/>
+      <c r="AU21" s="20"/>
+      <c r="AV21" s="20"/>
+      <c r="AW21" s="20"/>
+      <c r="AX21" s="20"/>
+      <c r="AY21" s="20"/>
+      <c r="AZ21" s="20"/>
+      <c r="BA21" s="20"/>
+      <c r="BB21" s="20"/>
+      <c r="BC21" s="20"/>
+      <c r="BD21" s="20"/>
+      <c r="BE21" s="20"/>
+      <c r="BF21" s="20"/>
+      <c r="BG21" s="20"/>
+      <c r="BH21" s="20"/>
+      <c r="BI21" s="20"/>
+      <c r="BJ21" s="20"/>
+      <c r="BK21" s="20"/>
+      <c r="BL21" s="20"/>
+      <c r="BM21" s="20"/>
+      <c r="BN21" s="20"/>
+      <c r="BO21" s="20"/>
+      <c r="BP21" s="20"/>
+      <c r="BQ21" s="20"/>
+      <c r="BR21" s="20"/>
+      <c r="BS21" s="20"/>
+      <c r="BT21" s="20"/>
+      <c r="BU21" s="20"/>
+      <c r="BV21" s="20"/>
+      <c r="BW21" s="20"/>
+      <c r="BX21" s="20"/>
+      <c r="BY21" s="20"/>
+      <c r="BZ21" s="20"/>
+      <c r="CA21" s="20"/>
+      <c r="CB21" s="20"/>
+      <c r="CC21" s="20"/>
+      <c r="CD21" s="20"/>
+      <c r="CE21" s="20"/>
+      <c r="CF21" s="20"/>
+      <c r="CG21" s="20"/>
+      <c r="CH21" s="20"/>
+      <c r="CI21" s="20"/>
+      <c r="CJ21" s="20"/>
+      <c r="CK21" s="20"/>
+      <c r="CL21" s="20"/>
+      <c r="CM21" s="20"/>
+      <c r="CN21" s="20"/>
+      <c r="CO21" s="20"/>
+      <c r="CP21" s="20"/>
+      <c r="CQ21" s="20"/>
+      <c r="CR21" s="20"/>
+      <c r="CS21" s="20"/>
+      <c r="CT21" s="20"/>
+      <c r="CU21" s="20"/>
+      <c r="CV21" s="20"/>
       <c r="CW21" s="2"/>
     </row>
     <row r="22" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2433,91 +2439,91 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-      <c r="R22" s="55" t="s">
+      <c r="R22" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="S22" s="55"/>
-      <c r="T22" s="55"/>
-      <c r="U22" s="55"/>
-      <c r="V22" s="55"/>
-      <c r="W22" s="55"/>
-      <c r="X22" s="55"/>
-      <c r="Y22" s="55"/>
-      <c r="Z22" s="55"/>
-      <c r="AA22" s="55"/>
-      <c r="AB22" s="55"/>
-      <c r="AC22" s="55"/>
-      <c r="AD22" s="55"/>
-      <c r="AE22" s="55"/>
-      <c r="AF22" s="55"/>
-      <c r="AG22" s="55"/>
-      <c r="AH22" s="55"/>
-      <c r="AI22" s="55"/>
-      <c r="AJ22" s="55"/>
-      <c r="AK22" s="55"/>
-      <c r="AL22" s="55"/>
-      <c r="AM22" s="55"/>
-      <c r="AN22" s="55"/>
-      <c r="AO22" s="55"/>
-      <c r="AP22" s="55"/>
-      <c r="AQ22" s="55"/>
-      <c r="AR22" s="55"/>
-      <c r="AS22" s="55"/>
-      <c r="AT22" s="55"/>
-      <c r="AU22" s="55"/>
-      <c r="AV22" s="55"/>
-      <c r="AW22" s="55"/>
-      <c r="AX22" s="55"/>
-      <c r="AY22" s="55"/>
-      <c r="AZ22" s="55"/>
-      <c r="BA22" s="55"/>
-      <c r="BB22" s="55"/>
-      <c r="BC22" s="55"/>
-      <c r="BD22" s="55"/>
-      <c r="BE22" s="55"/>
-      <c r="BF22" s="55"/>
-      <c r="BG22" s="55"/>
-      <c r="BH22" s="55"/>
-      <c r="BI22" s="55"/>
-      <c r="BJ22" s="55"/>
-      <c r="BK22" s="55"/>
-      <c r="BL22" s="55"/>
-      <c r="BM22" s="55"/>
-      <c r="BN22" s="55"/>
-      <c r="BO22" s="55"/>
-      <c r="BP22" s="55"/>
-      <c r="BQ22" s="55"/>
-      <c r="BR22" s="55"/>
-      <c r="BS22" s="55"/>
-      <c r="BT22" s="55"/>
-      <c r="BU22" s="55"/>
-      <c r="BV22" s="55"/>
-      <c r="BW22" s="55"/>
-      <c r="BX22" s="55"/>
-      <c r="BY22" s="55"/>
-      <c r="BZ22" s="55"/>
-      <c r="CA22" s="55"/>
-      <c r="CB22" s="55"/>
-      <c r="CC22" s="55"/>
-      <c r="CD22" s="55"/>
-      <c r="CE22" s="55"/>
-      <c r="CF22" s="55"/>
-      <c r="CG22" s="55"/>
-      <c r="CH22" s="55"/>
-      <c r="CI22" s="55"/>
-      <c r="CJ22" s="55"/>
-      <c r="CK22" s="55"/>
-      <c r="CL22" s="55"/>
-      <c r="CM22" s="55"/>
-      <c r="CN22" s="55"/>
-      <c r="CO22" s="55"/>
-      <c r="CP22" s="55"/>
-      <c r="CQ22" s="55"/>
-      <c r="CR22" s="55"/>
-      <c r="CS22" s="55"/>
-      <c r="CT22" s="55"/>
-      <c r="CU22" s="55"/>
-      <c r="CV22" s="55"/>
+      <c r="S22" s="21"/>
+      <c r="T22" s="21"/>
+      <c r="U22" s="21"/>
+      <c r="V22" s="21"/>
+      <c r="W22" s="21"/>
+      <c r="X22" s="21"/>
+      <c r="Y22" s="21"/>
+      <c r="Z22" s="21"/>
+      <c r="AA22" s="21"/>
+      <c r="AB22" s="21"/>
+      <c r="AC22" s="21"/>
+      <c r="AD22" s="21"/>
+      <c r="AE22" s="21"/>
+      <c r="AF22" s="21"/>
+      <c r="AG22" s="21"/>
+      <c r="AH22" s="21"/>
+      <c r="AI22" s="21"/>
+      <c r="AJ22" s="21"/>
+      <c r="AK22" s="21"/>
+      <c r="AL22" s="21"/>
+      <c r="AM22" s="21"/>
+      <c r="AN22" s="21"/>
+      <c r="AO22" s="21"/>
+      <c r="AP22" s="21"/>
+      <c r="AQ22" s="21"/>
+      <c r="AR22" s="21"/>
+      <c r="AS22" s="21"/>
+      <c r="AT22" s="21"/>
+      <c r="AU22" s="21"/>
+      <c r="AV22" s="21"/>
+      <c r="AW22" s="21"/>
+      <c r="AX22" s="21"/>
+      <c r="AY22" s="21"/>
+      <c r="AZ22" s="21"/>
+      <c r="BA22" s="21"/>
+      <c r="BB22" s="21"/>
+      <c r="BC22" s="21"/>
+      <c r="BD22" s="21"/>
+      <c r="BE22" s="21"/>
+      <c r="BF22" s="21"/>
+      <c r="BG22" s="21"/>
+      <c r="BH22" s="21"/>
+      <c r="BI22" s="21"/>
+      <c r="BJ22" s="21"/>
+      <c r="BK22" s="21"/>
+      <c r="BL22" s="21"/>
+      <c r="BM22" s="21"/>
+      <c r="BN22" s="21"/>
+      <c r="BO22" s="21"/>
+      <c r="BP22" s="21"/>
+      <c r="BQ22" s="21"/>
+      <c r="BR22" s="21"/>
+      <c r="BS22" s="21"/>
+      <c r="BT22" s="21"/>
+      <c r="BU22" s="21"/>
+      <c r="BV22" s="21"/>
+      <c r="BW22" s="21"/>
+      <c r="BX22" s="21"/>
+      <c r="BY22" s="21"/>
+      <c r="BZ22" s="21"/>
+      <c r="CA22" s="21"/>
+      <c r="CB22" s="21"/>
+      <c r="CC22" s="21"/>
+      <c r="CD22" s="21"/>
+      <c r="CE22" s="21"/>
+      <c r="CF22" s="21"/>
+      <c r="CG22" s="21"/>
+      <c r="CH22" s="21"/>
+      <c r="CI22" s="21"/>
+      <c r="CJ22" s="21"/>
+      <c r="CK22" s="21"/>
+      <c r="CL22" s="21"/>
+      <c r="CM22" s="21"/>
+      <c r="CN22" s="21"/>
+      <c r="CO22" s="21"/>
+      <c r="CP22" s="21"/>
+      <c r="CQ22" s="21"/>
+      <c r="CR22" s="21"/>
+      <c r="CS22" s="21"/>
+      <c r="CT22" s="21"/>
+      <c r="CU22" s="21"/>
+      <c r="CV22" s="21"/>
     </row>
     <row r="23" spans="1:173" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
@@ -2622,108 +2628,108 @@
       <c r="CV23" s="6"/>
     </row>
     <row r="24" spans="1:173" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="53" t="s">
+      <c r="A24" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="53"/>
-      <c r="C24" s="53"/>
-      <c r="D24" s="53"/>
-      <c r="E24" s="53"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="53"/>
-      <c r="H24" s="53"/>
-      <c r="I24" s="53"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="53"/>
-      <c r="L24" s="53"/>
-      <c r="M24" s="53"/>
-      <c r="N24" s="53"/>
-      <c r="O24" s="53"/>
-      <c r="P24" s="53"/>
-      <c r="Q24" s="53"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+      <c r="L24" s="19"/>
+      <c r="M24" s="19"/>
+      <c r="N24" s="19"/>
+      <c r="O24" s="19"/>
+      <c r="P24" s="19"/>
+      <c r="Q24" s="19"/>
       <c r="R24" s="1"/>
       <c r="S24" s="4"/>
-      <c r="T24" s="54"/>
-      <c r="U24" s="54"/>
-      <c r="V24" s="54"/>
-      <c r="W24" s="54"/>
-      <c r="X24" s="54"/>
-      <c r="Y24" s="54"/>
-      <c r="Z24" s="54"/>
-      <c r="AA24" s="54"/>
-      <c r="AB24" s="54"/>
-      <c r="AC24" s="54"/>
-      <c r="AD24" s="54"/>
-      <c r="AE24" s="54"/>
-      <c r="AF24" s="54"/>
-      <c r="AG24" s="54"/>
-      <c r="AH24" s="54"/>
-      <c r="AI24" s="54"/>
-      <c r="AJ24" s="54"/>
-      <c r="AK24" s="54"/>
-      <c r="AL24" s="54"/>
-      <c r="AM24" s="54"/>
-      <c r="AN24" s="54"/>
-      <c r="AO24" s="54"/>
-      <c r="AP24" s="54"/>
-      <c r="AQ24" s="54"/>
-      <c r="AR24" s="54"/>
-      <c r="AS24" s="54"/>
-      <c r="AT24" s="54"/>
-      <c r="AU24" s="54"/>
-      <c r="AV24" s="54"/>
-      <c r="AW24" s="54"/>
-      <c r="AX24" s="54"/>
-      <c r="AY24" s="54"/>
-      <c r="AZ24" s="54"/>
-      <c r="BA24" s="54"/>
-      <c r="BB24" s="54"/>
-      <c r="BC24" s="54"/>
-      <c r="BD24" s="54"/>
-      <c r="BE24" s="54"/>
-      <c r="BF24" s="54"/>
-      <c r="BG24" s="54"/>
-      <c r="BH24" s="54"/>
-      <c r="BI24" s="54"/>
-      <c r="BJ24" s="54"/>
-      <c r="BK24" s="54"/>
-      <c r="BL24" s="54"/>
-      <c r="BM24" s="54"/>
-      <c r="BN24" s="54"/>
-      <c r="BO24" s="54"/>
-      <c r="BP24" s="54"/>
-      <c r="BQ24" s="54"/>
-      <c r="BR24" s="54"/>
-      <c r="BS24" s="54"/>
-      <c r="BT24" s="54"/>
-      <c r="BU24" s="54"/>
-      <c r="BV24" s="54"/>
-      <c r="BW24" s="54"/>
-      <c r="BX24" s="54"/>
-      <c r="BY24" s="54"/>
-      <c r="BZ24" s="54"/>
-      <c r="CA24" s="54"/>
-      <c r="CB24" s="54"/>
-      <c r="CC24" s="54"/>
-      <c r="CD24" s="54"/>
-      <c r="CE24" s="54"/>
-      <c r="CF24" s="54"/>
-      <c r="CG24" s="54"/>
-      <c r="CH24" s="54"/>
-      <c r="CI24" s="54"/>
-      <c r="CJ24" s="54"/>
-      <c r="CK24" s="54"/>
-      <c r="CL24" s="54"/>
-      <c r="CM24" s="54"/>
-      <c r="CN24" s="54"/>
-      <c r="CO24" s="54"/>
-      <c r="CP24" s="54"/>
-      <c r="CQ24" s="54"/>
-      <c r="CR24" s="54"/>
-      <c r="CS24" s="54"/>
-      <c r="CT24" s="54"/>
-      <c r="CU24" s="54"/>
-      <c r="CV24" s="54"/>
+      <c r="T24" s="20"/>
+      <c r="U24" s="20"/>
+      <c r="V24" s="20"/>
+      <c r="W24" s="20"/>
+      <c r="X24" s="20"/>
+      <c r="Y24" s="20"/>
+      <c r="Z24" s="20"/>
+      <c r="AA24" s="20"/>
+      <c r="AB24" s="20"/>
+      <c r="AC24" s="20"/>
+      <c r="AD24" s="20"/>
+      <c r="AE24" s="20"/>
+      <c r="AF24" s="20"/>
+      <c r="AG24" s="20"/>
+      <c r="AH24" s="20"/>
+      <c r="AI24" s="20"/>
+      <c r="AJ24" s="20"/>
+      <c r="AK24" s="20"/>
+      <c r="AL24" s="20"/>
+      <c r="AM24" s="20"/>
+      <c r="AN24" s="20"/>
+      <c r="AO24" s="20"/>
+      <c r="AP24" s="20"/>
+      <c r="AQ24" s="20"/>
+      <c r="AR24" s="20"/>
+      <c r="AS24" s="20"/>
+      <c r="AT24" s="20"/>
+      <c r="AU24" s="20"/>
+      <c r="AV24" s="20"/>
+      <c r="AW24" s="20"/>
+      <c r="AX24" s="20"/>
+      <c r="AY24" s="20"/>
+      <c r="AZ24" s="20"/>
+      <c r="BA24" s="20"/>
+      <c r="BB24" s="20"/>
+      <c r="BC24" s="20"/>
+      <c r="BD24" s="20"/>
+      <c r="BE24" s="20"/>
+      <c r="BF24" s="20"/>
+      <c r="BG24" s="20"/>
+      <c r="BH24" s="20"/>
+      <c r="BI24" s="20"/>
+      <c r="BJ24" s="20"/>
+      <c r="BK24" s="20"/>
+      <c r="BL24" s="20"/>
+      <c r="BM24" s="20"/>
+      <c r="BN24" s="20"/>
+      <c r="BO24" s="20"/>
+      <c r="BP24" s="20"/>
+      <c r="BQ24" s="20"/>
+      <c r="BR24" s="20"/>
+      <c r="BS24" s="20"/>
+      <c r="BT24" s="20"/>
+      <c r="BU24" s="20"/>
+      <c r="BV24" s="20"/>
+      <c r="BW24" s="20"/>
+      <c r="BX24" s="20"/>
+      <c r="BY24" s="20"/>
+      <c r="BZ24" s="20"/>
+      <c r="CA24" s="20"/>
+      <c r="CB24" s="20"/>
+      <c r="CC24" s="20"/>
+      <c r="CD24" s="20"/>
+      <c r="CE24" s="20"/>
+      <c r="CF24" s="20"/>
+      <c r="CG24" s="20"/>
+      <c r="CH24" s="20"/>
+      <c r="CI24" s="20"/>
+      <c r="CJ24" s="20"/>
+      <c r="CK24" s="20"/>
+      <c r="CL24" s="20"/>
+      <c r="CM24" s="20"/>
+      <c r="CN24" s="20"/>
+      <c r="CO24" s="20"/>
+      <c r="CP24" s="20"/>
+      <c r="CQ24" s="20"/>
+      <c r="CR24" s="20"/>
+      <c r="CS24" s="20"/>
+      <c r="CT24" s="20"/>
+      <c r="CU24" s="20"/>
+      <c r="CV24" s="20"/>
     </row>
     <row r="25" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
@@ -2745,89 +2751,89 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
-      <c r="T25" s="55" t="s">
+      <c r="T25" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="U25" s="55"/>
-      <c r="V25" s="55"/>
-      <c r="W25" s="55"/>
-      <c r="X25" s="55"/>
-      <c r="Y25" s="55"/>
-      <c r="Z25" s="55"/>
-      <c r="AA25" s="55"/>
-      <c r="AB25" s="55"/>
-      <c r="AC25" s="55"/>
-      <c r="AD25" s="55"/>
-      <c r="AE25" s="55"/>
-      <c r="AF25" s="55"/>
-      <c r="AG25" s="55"/>
-      <c r="AH25" s="55"/>
-      <c r="AI25" s="55"/>
-      <c r="AJ25" s="55"/>
-      <c r="AK25" s="55"/>
-      <c r="AL25" s="55"/>
-      <c r="AM25" s="55"/>
-      <c r="AN25" s="55"/>
-      <c r="AO25" s="55"/>
-      <c r="AP25" s="55"/>
-      <c r="AQ25" s="55"/>
-      <c r="AR25" s="55"/>
-      <c r="AS25" s="55"/>
-      <c r="AT25" s="55"/>
-      <c r="AU25" s="55"/>
-      <c r="AV25" s="55"/>
-      <c r="AW25" s="55"/>
-      <c r="AX25" s="55"/>
-      <c r="AY25" s="55"/>
-      <c r="AZ25" s="55"/>
-      <c r="BA25" s="55"/>
-      <c r="BB25" s="55"/>
-      <c r="BC25" s="55"/>
-      <c r="BD25" s="55"/>
-      <c r="BE25" s="55"/>
-      <c r="BF25" s="55"/>
-      <c r="BG25" s="55"/>
-      <c r="BH25" s="55"/>
-      <c r="BI25" s="55"/>
-      <c r="BJ25" s="55"/>
-      <c r="BK25" s="55"/>
-      <c r="BL25" s="55"/>
-      <c r="BM25" s="55"/>
-      <c r="BN25" s="55"/>
-      <c r="BO25" s="55"/>
-      <c r="BP25" s="55"/>
-      <c r="BQ25" s="55"/>
-      <c r="BR25" s="55"/>
-      <c r="BS25" s="55"/>
-      <c r="BT25" s="55"/>
-      <c r="BU25" s="55"/>
-      <c r="BV25" s="55"/>
-      <c r="BW25" s="55"/>
-      <c r="BX25" s="55"/>
-      <c r="BY25" s="55"/>
-      <c r="BZ25" s="55"/>
-      <c r="CA25" s="55"/>
-      <c r="CB25" s="55"/>
-      <c r="CC25" s="55"/>
-      <c r="CD25" s="55"/>
-      <c r="CE25" s="55"/>
-      <c r="CF25" s="55"/>
-      <c r="CG25" s="55"/>
-      <c r="CH25" s="55"/>
-      <c r="CI25" s="55"/>
-      <c r="CJ25" s="55"/>
-      <c r="CK25" s="55"/>
-      <c r="CL25" s="55"/>
-      <c r="CM25" s="55"/>
-      <c r="CN25" s="55"/>
-      <c r="CO25" s="55"/>
-      <c r="CP25" s="55"/>
-      <c r="CQ25" s="55"/>
-      <c r="CR25" s="55"/>
-      <c r="CS25" s="55"/>
-      <c r="CT25" s="55"/>
-      <c r="CU25" s="55"/>
-      <c r="CV25" s="55"/>
+      <c r="U25" s="21"/>
+      <c r="V25" s="21"/>
+      <c r="W25" s="21"/>
+      <c r="X25" s="21"/>
+      <c r="Y25" s="21"/>
+      <c r="Z25" s="21"/>
+      <c r="AA25" s="21"/>
+      <c r="AB25" s="21"/>
+      <c r="AC25" s="21"/>
+      <c r="AD25" s="21"/>
+      <c r="AE25" s="21"/>
+      <c r="AF25" s="21"/>
+      <c r="AG25" s="21"/>
+      <c r="AH25" s="21"/>
+      <c r="AI25" s="21"/>
+      <c r="AJ25" s="21"/>
+      <c r="AK25" s="21"/>
+      <c r="AL25" s="21"/>
+      <c r="AM25" s="21"/>
+      <c r="AN25" s="21"/>
+      <c r="AO25" s="21"/>
+      <c r="AP25" s="21"/>
+      <c r="AQ25" s="21"/>
+      <c r="AR25" s="21"/>
+      <c r="AS25" s="21"/>
+      <c r="AT25" s="21"/>
+      <c r="AU25" s="21"/>
+      <c r="AV25" s="21"/>
+      <c r="AW25" s="21"/>
+      <c r="AX25" s="21"/>
+      <c r="AY25" s="21"/>
+      <c r="AZ25" s="21"/>
+      <c r="BA25" s="21"/>
+      <c r="BB25" s="21"/>
+      <c r="BC25" s="21"/>
+      <c r="BD25" s="21"/>
+      <c r="BE25" s="21"/>
+      <c r="BF25" s="21"/>
+      <c r="BG25" s="21"/>
+      <c r="BH25" s="21"/>
+      <c r="BI25" s="21"/>
+      <c r="BJ25" s="21"/>
+      <c r="BK25" s="21"/>
+      <c r="BL25" s="21"/>
+      <c r="BM25" s="21"/>
+      <c r="BN25" s="21"/>
+      <c r="BO25" s="21"/>
+      <c r="BP25" s="21"/>
+      <c r="BQ25" s="21"/>
+      <c r="BR25" s="21"/>
+      <c r="BS25" s="21"/>
+      <c r="BT25" s="21"/>
+      <c r="BU25" s="21"/>
+      <c r="BV25" s="21"/>
+      <c r="BW25" s="21"/>
+      <c r="BX25" s="21"/>
+      <c r="BY25" s="21"/>
+      <c r="BZ25" s="21"/>
+      <c r="CA25" s="21"/>
+      <c r="CB25" s="21"/>
+      <c r="CC25" s="21"/>
+      <c r="CD25" s="21"/>
+      <c r="CE25" s="21"/>
+      <c r="CF25" s="21"/>
+      <c r="CG25" s="21"/>
+      <c r="CH25" s="21"/>
+      <c r="CI25" s="21"/>
+      <c r="CJ25" s="21"/>
+      <c r="CK25" s="21"/>
+      <c r="CL25" s="21"/>
+      <c r="CM25" s="21"/>
+      <c r="CN25" s="21"/>
+      <c r="CO25" s="21"/>
+      <c r="CP25" s="21"/>
+      <c r="CQ25" s="21"/>
+      <c r="CR25" s="21"/>
+      <c r="CS25" s="21"/>
+      <c r="CT25" s="21"/>
+      <c r="CU25" s="21"/>
+      <c r="CV25" s="21"/>
     </row>
     <row r="26" spans="1:173" s="3" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
@@ -3005,108 +3011,108 @@
       <c r="FQ26" s="2"/>
     </row>
     <row r="27" spans="1:173" s="3" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="50" t="s">
+      <c r="A27" s="32" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
-      <c r="L27" s="50"/>
-      <c r="M27" s="50"/>
-      <c r="N27" s="50"/>
-      <c r="O27" s="50"/>
-      <c r="P27" s="50"/>
-      <c r="Q27" s="50"/>
-      <c r="R27" s="50"/>
-      <c r="S27" s="50"/>
-      <c r="T27" s="50"/>
-      <c r="U27" s="50"/>
-      <c r="V27" s="50"/>
-      <c r="W27" s="50"/>
-      <c r="X27" s="50"/>
-      <c r="Y27" s="50"/>
-      <c r="Z27" s="50"/>
-      <c r="AA27" s="50"/>
-      <c r="AB27" s="50"/>
-      <c r="AC27" s="50"/>
-      <c r="AD27" s="50"/>
-      <c r="AE27" s="50"/>
-      <c r="AF27" s="50"/>
-      <c r="AG27" s="50"/>
-      <c r="AH27" s="50"/>
-      <c r="AI27" s="50"/>
-      <c r="AJ27" s="50"/>
-      <c r="AK27" s="50"/>
-      <c r="AL27" s="50"/>
-      <c r="AM27" s="50"/>
-      <c r="AN27" s="50"/>
-      <c r="AO27" s="50"/>
-      <c r="AP27" s="50"/>
-      <c r="AQ27" s="50"/>
-      <c r="AR27" s="50"/>
-      <c r="AS27" s="50"/>
-      <c r="AT27" s="50"/>
-      <c r="AU27" s="50"/>
-      <c r="AV27" s="50"/>
-      <c r="AW27" s="50"/>
-      <c r="AX27" s="50"/>
-      <c r="AY27" s="50"/>
-      <c r="AZ27" s="50"/>
-      <c r="BA27" s="50"/>
-      <c r="BB27" s="50"/>
-      <c r="BC27" s="50"/>
-      <c r="BD27" s="50"/>
-      <c r="BE27" s="50"/>
-      <c r="BF27" s="50"/>
-      <c r="BG27" s="50"/>
-      <c r="BH27" s="50"/>
-      <c r="BI27" s="50"/>
-      <c r="BJ27" s="50"/>
-      <c r="BK27" s="50"/>
-      <c r="BL27" s="50"/>
-      <c r="BM27" s="50"/>
-      <c r="BN27" s="50"/>
-      <c r="BO27" s="50"/>
-      <c r="BP27" s="50"/>
-      <c r="BQ27" s="50"/>
-      <c r="BR27" s="50"/>
-      <c r="BS27" s="50"/>
-      <c r="BT27" s="50"/>
-      <c r="BU27" s="50"/>
-      <c r="BV27" s="50"/>
-      <c r="BW27" s="50"/>
-      <c r="BX27" s="50"/>
-      <c r="BY27" s="50"/>
-      <c r="BZ27" s="50"/>
-      <c r="CA27" s="50"/>
-      <c r="CB27" s="50"/>
-      <c r="CC27" s="50"/>
-      <c r="CD27" s="50"/>
-      <c r="CE27" s="50"/>
-      <c r="CF27" s="50"/>
-      <c r="CG27" s="50"/>
-      <c r="CH27" s="50"/>
-      <c r="CI27" s="50"/>
-      <c r="CJ27" s="50"/>
-      <c r="CK27" s="50"/>
-      <c r="CL27" s="50"/>
-      <c r="CM27" s="50"/>
-      <c r="CN27" s="50"/>
-      <c r="CO27" s="50"/>
-      <c r="CP27" s="50"/>
-      <c r="CQ27" s="50"/>
-      <c r="CR27" s="50"/>
-      <c r="CS27" s="50"/>
-      <c r="CT27" s="50"/>
-      <c r="CU27" s="50"/>
-      <c r="CV27" s="50"/>
+      <c r="B27" s="32"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
+      <c r="L27" s="32"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="32"/>
+      <c r="O27" s="32"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="32"/>
+      <c r="R27" s="32"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="32"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
+      <c r="AA27" s="32"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="32"/>
+      <c r="AD27" s="32"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="32"/>
+      <c r="AG27" s="32"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="32"/>
+      <c r="AJ27" s="32"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="32"/>
+      <c r="AM27" s="32"/>
+      <c r="AN27" s="32"/>
+      <c r="AO27" s="32"/>
+      <c r="AP27" s="32"/>
+      <c r="AQ27" s="32"/>
+      <c r="AR27" s="32"/>
+      <c r="AS27" s="32"/>
+      <c r="AT27" s="32"/>
+      <c r="AU27" s="32"/>
+      <c r="AV27" s="32"/>
+      <c r="AW27" s="32"/>
+      <c r="AX27" s="32"/>
+      <c r="AY27" s="32"/>
+      <c r="AZ27" s="32"/>
+      <c r="BA27" s="32"/>
+      <c r="BB27" s="32"/>
+      <c r="BC27" s="32"/>
+      <c r="BD27" s="32"/>
+      <c r="BE27" s="32"/>
+      <c r="BF27" s="32"/>
+      <c r="BG27" s="32"/>
+      <c r="BH27" s="32"/>
+      <c r="BI27" s="32"/>
+      <c r="BJ27" s="32"/>
+      <c r="BK27" s="32"/>
+      <c r="BL27" s="32"/>
+      <c r="BM27" s="32"/>
+      <c r="BN27" s="32"/>
+      <c r="BO27" s="32"/>
+      <c r="BP27" s="32"/>
+      <c r="BQ27" s="32"/>
+      <c r="BR27" s="32"/>
+      <c r="BS27" s="32"/>
+      <c r="BT27" s="32"/>
+      <c r="BU27" s="32"/>
+      <c r="BV27" s="32"/>
+      <c r="BW27" s="32"/>
+      <c r="BX27" s="32"/>
+      <c r="BY27" s="32"/>
+      <c r="BZ27" s="32"/>
+      <c r="CA27" s="32"/>
+      <c r="CB27" s="32"/>
+      <c r="CC27" s="32"/>
+      <c r="CD27" s="32"/>
+      <c r="CE27" s="32"/>
+      <c r="CF27" s="32"/>
+      <c r="CG27" s="32"/>
+      <c r="CH27" s="32"/>
+      <c r="CI27" s="32"/>
+      <c r="CJ27" s="32"/>
+      <c r="CK27" s="32"/>
+      <c r="CL27" s="32"/>
+      <c r="CM27" s="32"/>
+      <c r="CN27" s="32"/>
+      <c r="CO27" s="32"/>
+      <c r="CP27" s="32"/>
+      <c r="CQ27" s="32"/>
+      <c r="CR27" s="32"/>
+      <c r="CS27" s="32"/>
+      <c r="CT27" s="32"/>
+      <c r="CU27" s="32"/>
+      <c r="CV27" s="32"/>
       <c r="CX27" s="2"/>
       <c r="CY27" s="2"/>
       <c r="CZ27" s="2"/>
@@ -3181,124 +3187,124 @@
       <c r="FQ27" s="2"/>
     </row>
     <row r="28" spans="1:173" s="3" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="50" t="s">
+      <c r="A28" s="32" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
-      <c r="K28" s="50"/>
-      <c r="L28" s="50"/>
-      <c r="M28" s="50"/>
-      <c r="N28" s="50"/>
-      <c r="O28" s="50"/>
-      <c r="P28" s="50"/>
-      <c r="Q28" s="50"/>
-      <c r="R28" s="50"/>
-      <c r="S28" s="50"/>
-      <c r="T28" s="50"/>
-      <c r="U28" s="50"/>
-      <c r="V28" s="50"/>
-      <c r="W28" s="50" t="s">
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="32"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="32"/>
+      <c r="L28" s="32"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="32"/>
+      <c r="O28" s="32"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="32"/>
+      <c r="R28" s="32"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="32"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="X28" s="50"/>
-      <c r="Y28" s="50"/>
-      <c r="Z28" s="50"/>
-      <c r="AA28" s="50"/>
-      <c r="AB28" s="50"/>
-      <c r="AC28" s="50"/>
-      <c r="AD28" s="50"/>
-      <c r="AE28" s="50"/>
-      <c r="AF28" s="50"/>
-      <c r="AG28" s="50" t="s">
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
+      <c r="AA28" s="32"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="32"/>
+      <c r="AD28" s="32"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="32"/>
+      <c r="AG28" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="AH28" s="50"/>
-      <c r="AI28" s="50"/>
-      <c r="AJ28" s="50"/>
-      <c r="AK28" s="50"/>
-      <c r="AL28" s="50"/>
-      <c r="AM28" s="50"/>
-      <c r="AN28" s="50"/>
-      <c r="AO28" s="50"/>
-      <c r="AP28" s="50" t="s">
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="32"/>
+      <c r="AJ28" s="32"/>
+      <c r="AK28" s="32"/>
+      <c r="AL28" s="32"/>
+      <c r="AM28" s="32"/>
+      <c r="AN28" s="32"/>
+      <c r="AO28" s="32"/>
+      <c r="AP28" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="AQ28" s="50"/>
-      <c r="AR28" s="50"/>
-      <c r="AS28" s="50"/>
-      <c r="AT28" s="50"/>
-      <c r="AU28" s="50"/>
-      <c r="AV28" s="50"/>
-      <c r="AW28" s="50"/>
-      <c r="AX28" s="50"/>
-      <c r="AY28" s="50"/>
-      <c r="AZ28" s="50" t="s">
+      <c r="AQ28" s="32"/>
+      <c r="AR28" s="32"/>
+      <c r="AS28" s="32"/>
+      <c r="AT28" s="32"/>
+      <c r="AU28" s="32"/>
+      <c r="AV28" s="32"/>
+      <c r="AW28" s="32"/>
+      <c r="AX28" s="32"/>
+      <c r="AY28" s="32"/>
+      <c r="AZ28" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="BA28" s="50"/>
-      <c r="BB28" s="50"/>
-      <c r="BC28" s="50"/>
-      <c r="BD28" s="50"/>
-      <c r="BE28" s="50"/>
-      <c r="BF28" s="50"/>
-      <c r="BG28" s="50"/>
-      <c r="BH28" s="50"/>
-      <c r="BI28" s="50"/>
-      <c r="BJ28" s="50"/>
-      <c r="BK28" s="50" t="s">
+      <c r="BA28" s="32"/>
+      <c r="BB28" s="32"/>
+      <c r="BC28" s="32"/>
+      <c r="BD28" s="32"/>
+      <c r="BE28" s="32"/>
+      <c r="BF28" s="32"/>
+      <c r="BG28" s="32"/>
+      <c r="BH28" s="32"/>
+      <c r="BI28" s="32"/>
+      <c r="BJ28" s="32"/>
+      <c r="BK28" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="BL28" s="50"/>
-      <c r="BM28" s="50"/>
-      <c r="BN28" s="50"/>
-      <c r="BO28" s="50"/>
-      <c r="BP28" s="50"/>
-      <c r="BQ28" s="50"/>
-      <c r="BR28" s="50"/>
-      <c r="BS28" s="50"/>
-      <c r="BT28" s="50" t="s">
+      <c r="BL28" s="32"/>
+      <c r="BM28" s="32"/>
+      <c r="BN28" s="32"/>
+      <c r="BO28" s="32"/>
+      <c r="BP28" s="32"/>
+      <c r="BQ28" s="32"/>
+      <c r="BR28" s="32"/>
+      <c r="BS28" s="32"/>
+      <c r="BT28" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="BU28" s="50"/>
-      <c r="BV28" s="50"/>
-      <c r="BW28" s="50"/>
-      <c r="BX28" s="50"/>
-      <c r="BY28" s="50"/>
-      <c r="BZ28" s="50"/>
-      <c r="CA28" s="50"/>
-      <c r="CB28" s="50"/>
-      <c r="CC28" s="50" t="s">
+      <c r="BU28" s="32"/>
+      <c r="BV28" s="32"/>
+      <c r="BW28" s="32"/>
+      <c r="BX28" s="32"/>
+      <c r="BY28" s="32"/>
+      <c r="BZ28" s="32"/>
+      <c r="CA28" s="32"/>
+      <c r="CB28" s="32"/>
+      <c r="CC28" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="CD28" s="50"/>
-      <c r="CE28" s="50"/>
-      <c r="CF28" s="50"/>
-      <c r="CG28" s="50"/>
-      <c r="CH28" s="50"/>
-      <c r="CI28" s="50"/>
-      <c r="CJ28" s="50"/>
-      <c r="CK28" s="50"/>
-      <c r="CL28" s="50"/>
-      <c r="CM28" s="50"/>
-      <c r="CN28" s="50" t="s">
+      <c r="CD28" s="32"/>
+      <c r="CE28" s="32"/>
+      <c r="CF28" s="32"/>
+      <c r="CG28" s="32"/>
+      <c r="CH28" s="32"/>
+      <c r="CI28" s="32"/>
+      <c r="CJ28" s="32"/>
+      <c r="CK28" s="32"/>
+      <c r="CL28" s="32"/>
+      <c r="CM28" s="32"/>
+      <c r="CN28" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="CO28" s="50"/>
-      <c r="CP28" s="50"/>
-      <c r="CQ28" s="50"/>
-      <c r="CR28" s="50"/>
-      <c r="CS28" s="50"/>
-      <c r="CT28" s="50"/>
-      <c r="CU28" s="50"/>
-      <c r="CV28" s="50"/>
+      <c r="CO28" s="32"/>
+      <c r="CP28" s="32"/>
+      <c r="CQ28" s="32"/>
+      <c r="CR28" s="32"/>
+      <c r="CS28" s="32"/>
+      <c r="CT28" s="32"/>
+      <c r="CU28" s="32"/>
+      <c r="CV28" s="32"/>
       <c r="CX28" s="2"/>
       <c r="CY28" s="2"/>
       <c r="CZ28" s="2"/>
@@ -3373,124 +3379,124 @@
       <c r="FQ28" s="2"/>
     </row>
     <row r="29" spans="1:173" s="3" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="50">
+      <c r="A29" s="32">
         <v>1</v>
       </c>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="50"/>
-      <c r="J29" s="50"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="50"/>
-      <c r="M29" s="50"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="50"/>
-      <c r="P29" s="50"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="50"/>
-      <c r="S29" s="50"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="50"/>
-      <c r="V29" s="50"/>
-      <c r="W29" s="50">
+      <c r="B29" s="32"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="32"/>
+      <c r="L29" s="32"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
+      <c r="O29" s="32"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="32"/>
+      <c r="R29" s="32"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="32"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="32">
         <v>2</v>
       </c>
-      <c r="X29" s="50"/>
-      <c r="Y29" s="50"/>
-      <c r="Z29" s="50"/>
-      <c r="AA29" s="50"/>
-      <c r="AB29" s="50"/>
-      <c r="AC29" s="50"/>
-      <c r="AD29" s="50"/>
-      <c r="AE29" s="50"/>
-      <c r="AF29" s="50"/>
-      <c r="AG29" s="50">
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="32"/>
+      <c r="AA29" s="32"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="32"/>
+      <c r="AD29" s="32"/>
+      <c r="AE29" s="32"/>
+      <c r="AF29" s="32"/>
+      <c r="AG29" s="32">
         <v>3</v>
       </c>
-      <c r="AH29" s="50"/>
-      <c r="AI29" s="50"/>
-      <c r="AJ29" s="50"/>
-      <c r="AK29" s="50"/>
-      <c r="AL29" s="50"/>
-      <c r="AM29" s="50"/>
-      <c r="AN29" s="50"/>
-      <c r="AO29" s="50"/>
-      <c r="AP29" s="50">
+      <c r="AH29" s="32"/>
+      <c r="AI29" s="32"/>
+      <c r="AJ29" s="32"/>
+      <c r="AK29" s="32"/>
+      <c r="AL29" s="32"/>
+      <c r="AM29" s="32"/>
+      <c r="AN29" s="32"/>
+      <c r="AO29" s="32"/>
+      <c r="AP29" s="32">
         <v>4</v>
       </c>
-      <c r="AQ29" s="50"/>
-      <c r="AR29" s="50"/>
-      <c r="AS29" s="50"/>
-      <c r="AT29" s="50"/>
-      <c r="AU29" s="50"/>
-      <c r="AV29" s="50"/>
-      <c r="AW29" s="50"/>
-      <c r="AX29" s="50"/>
-      <c r="AY29" s="50"/>
-      <c r="AZ29" s="50">
+      <c r="AQ29" s="32"/>
+      <c r="AR29" s="32"/>
+      <c r="AS29" s="32"/>
+      <c r="AT29" s="32"/>
+      <c r="AU29" s="32"/>
+      <c r="AV29" s="32"/>
+      <c r="AW29" s="32"/>
+      <c r="AX29" s="32"/>
+      <c r="AY29" s="32"/>
+      <c r="AZ29" s="32">
         <v>5</v>
       </c>
-      <c r="BA29" s="50"/>
-      <c r="BB29" s="50"/>
-      <c r="BC29" s="50"/>
-      <c r="BD29" s="50"/>
-      <c r="BE29" s="50"/>
-      <c r="BF29" s="50"/>
-      <c r="BG29" s="50"/>
-      <c r="BH29" s="50"/>
-      <c r="BI29" s="50"/>
-      <c r="BJ29" s="50"/>
-      <c r="BK29" s="50">
+      <c r="BA29" s="32"/>
+      <c r="BB29" s="32"/>
+      <c r="BC29" s="32"/>
+      <c r="BD29" s="32"/>
+      <c r="BE29" s="32"/>
+      <c r="BF29" s="32"/>
+      <c r="BG29" s="32"/>
+      <c r="BH29" s="32"/>
+      <c r="BI29" s="32"/>
+      <c r="BJ29" s="32"/>
+      <c r="BK29" s="32">
         <v>6</v>
       </c>
-      <c r="BL29" s="50"/>
-      <c r="BM29" s="50"/>
-      <c r="BN29" s="50"/>
-      <c r="BO29" s="50"/>
-      <c r="BP29" s="50"/>
-      <c r="BQ29" s="50"/>
-      <c r="BR29" s="50"/>
-      <c r="BS29" s="50"/>
-      <c r="BT29" s="50">
+      <c r="BL29" s="32"/>
+      <c r="BM29" s="32"/>
+      <c r="BN29" s="32"/>
+      <c r="BO29" s="32"/>
+      <c r="BP29" s="32"/>
+      <c r="BQ29" s="32"/>
+      <c r="BR29" s="32"/>
+      <c r="BS29" s="32"/>
+      <c r="BT29" s="32">
         <v>7</v>
       </c>
-      <c r="BU29" s="50"/>
-      <c r="BV29" s="50"/>
-      <c r="BW29" s="50"/>
-      <c r="BX29" s="50"/>
-      <c r="BY29" s="50"/>
-      <c r="BZ29" s="50"/>
-      <c r="CA29" s="50"/>
-      <c r="CB29" s="50"/>
-      <c r="CC29" s="50">
+      <c r="BU29" s="32"/>
+      <c r="BV29" s="32"/>
+      <c r="BW29" s="32"/>
+      <c r="BX29" s="32"/>
+      <c r="BY29" s="32"/>
+      <c r="BZ29" s="32"/>
+      <c r="CA29" s="32"/>
+      <c r="CB29" s="32"/>
+      <c r="CC29" s="32">
         <v>8</v>
       </c>
-      <c r="CD29" s="50"/>
-      <c r="CE29" s="50"/>
-      <c r="CF29" s="50"/>
-      <c r="CG29" s="50"/>
-      <c r="CH29" s="50"/>
-      <c r="CI29" s="50"/>
-      <c r="CJ29" s="50"/>
-      <c r="CK29" s="50"/>
-      <c r="CL29" s="50"/>
-      <c r="CM29" s="50"/>
-      <c r="CN29" s="50">
+      <c r="CD29" s="32"/>
+      <c r="CE29" s="32"/>
+      <c r="CF29" s="32"/>
+      <c r="CG29" s="32"/>
+      <c r="CH29" s="32"/>
+      <c r="CI29" s="32"/>
+      <c r="CJ29" s="32"/>
+      <c r="CK29" s="32"/>
+      <c r="CL29" s="32"/>
+      <c r="CM29" s="32"/>
+      <c r="CN29" s="32">
         <v>9</v>
       </c>
-      <c r="CO29" s="50"/>
-      <c r="CP29" s="50"/>
-      <c r="CQ29" s="50"/>
-      <c r="CR29" s="50"/>
-      <c r="CS29" s="50"/>
-      <c r="CT29" s="50"/>
-      <c r="CU29" s="50"/>
-      <c r="CV29" s="50"/>
+      <c r="CO29" s="32"/>
+      <c r="CP29" s="32"/>
+      <c r="CQ29" s="32"/>
+      <c r="CR29" s="32"/>
+      <c r="CS29" s="32"/>
+      <c r="CT29" s="32"/>
+      <c r="CU29" s="32"/>
+      <c r="CV29" s="32"/>
       <c r="CX29" s="2"/>
       <c r="CY29" s="2"/>
       <c r="CZ29" s="2"/>
@@ -3565,122 +3571,122 @@
       <c r="FQ29" s="2"/>
     </row>
     <row r="30" spans="1:173" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="60" t="s">
+      <c r="A30" s="28" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="61"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
-      <c r="K30" s="61"/>
-      <c r="L30" s="61"/>
-      <c r="M30" s="61"/>
-      <c r="N30" s="61"/>
-      <c r="O30" s="61"/>
-      <c r="P30" s="61"/>
-      <c r="Q30" s="61"/>
-      <c r="R30" s="61"/>
-      <c r="S30" s="61"/>
-      <c r="T30" s="61"/>
-      <c r="U30" s="61"/>
-      <c r="V30" s="62"/>
-      <c r="W30" s="63" t="s">
+      <c r="B30" s="29"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="29"/>
+      <c r="E30" s="29"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="29"/>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="29"/>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="31" t="s">
         <v>47</v>
       </c>
-      <c r="X30" s="63"/>
-      <c r="Y30" s="63"/>
-      <c r="Z30" s="63"/>
-      <c r="AA30" s="63"/>
-      <c r="AB30" s="63"/>
-      <c r="AC30" s="63"/>
-      <c r="AD30" s="63"/>
-      <c r="AE30" s="63"/>
-      <c r="AF30" s="63"/>
-      <c r="AG30" s="48" t="s">
+      <c r="X30" s="31"/>
+      <c r="Y30" s="31"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="31"/>
+      <c r="AB30" s="31"/>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="31"/>
+      <c r="AE30" s="31"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="AH30" s="48"/>
-      <c r="AI30" s="48"/>
-      <c r="AJ30" s="48"/>
-      <c r="AK30" s="48"/>
-      <c r="AL30" s="48"/>
-      <c r="AM30" s="48"/>
-      <c r="AN30" s="48"/>
-      <c r="AO30" s="48"/>
-      <c r="AP30" s="48" t="s">
+      <c r="AH30" s="25"/>
+      <c r="AI30" s="25"/>
+      <c r="AJ30" s="25"/>
+      <c r="AK30" s="25"/>
+      <c r="AL30" s="25"/>
+      <c r="AM30" s="25"/>
+      <c r="AN30" s="25"/>
+      <c r="AO30" s="25"/>
+      <c r="AP30" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="AQ30" s="48"/>
-      <c r="AR30" s="48"/>
-      <c r="AS30" s="48"/>
-      <c r="AT30" s="48"/>
-      <c r="AU30" s="48"/>
-      <c r="AV30" s="48"/>
-      <c r="AW30" s="48"/>
-      <c r="AX30" s="48"/>
-      <c r="AY30" s="48"/>
-      <c r="AZ30" s="48" t="s">
+      <c r="AQ30" s="25"/>
+      <c r="AR30" s="25"/>
+      <c r="AS30" s="25"/>
+      <c r="AT30" s="25"/>
+      <c r="AU30" s="25"/>
+      <c r="AV30" s="25"/>
+      <c r="AW30" s="25"/>
+      <c r="AX30" s="25"/>
+      <c r="AY30" s="25"/>
+      <c r="AZ30" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="BA30" s="48"/>
-      <c r="BB30" s="48"/>
-      <c r="BC30" s="48"/>
-      <c r="BD30" s="48"/>
-      <c r="BE30" s="48"/>
-      <c r="BF30" s="48"/>
-      <c r="BG30" s="48"/>
-      <c r="BH30" s="48"/>
-      <c r="BI30" s="48"/>
-      <c r="BJ30" s="48"/>
-      <c r="BK30" s="49" t="s">
+      <c r="BA30" s="25"/>
+      <c r="BB30" s="25"/>
+      <c r="BC30" s="25"/>
+      <c r="BD30" s="25"/>
+      <c r="BE30" s="25"/>
+      <c r="BF30" s="25"/>
+      <c r="BG30" s="25"/>
+      <c r="BH30" s="25"/>
+      <c r="BI30" s="25"/>
+      <c r="BJ30" s="25"/>
+      <c r="BK30" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="BL30" s="49"/>
-      <c r="BM30" s="49"/>
-      <c r="BN30" s="49"/>
-      <c r="BO30" s="49"/>
-      <c r="BP30" s="49"/>
-      <c r="BQ30" s="49"/>
-      <c r="BR30" s="49"/>
-      <c r="BS30" s="49"/>
-      <c r="BT30" s="51" t="s">
+      <c r="BL30" s="34"/>
+      <c r="BM30" s="34"/>
+      <c r="BN30" s="34"/>
+      <c r="BO30" s="34"/>
+      <c r="BP30" s="34"/>
+      <c r="BQ30" s="34"/>
+      <c r="BR30" s="34"/>
+      <c r="BS30" s="34"/>
+      <c r="BT30" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="BU30" s="48"/>
-      <c r="BV30" s="48"/>
-      <c r="BW30" s="48"/>
-      <c r="BX30" s="48"/>
-      <c r="BY30" s="48"/>
-      <c r="BZ30" s="48"/>
-      <c r="CA30" s="48"/>
-      <c r="CB30" s="48"/>
-      <c r="CC30" s="59" t="s">
+      <c r="BU30" s="25"/>
+      <c r="BV30" s="25"/>
+      <c r="BW30" s="25"/>
+      <c r="BX30" s="25"/>
+      <c r="BY30" s="25"/>
+      <c r="BZ30" s="25"/>
+      <c r="CA30" s="25"/>
+      <c r="CB30" s="25"/>
+      <c r="CC30" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="CD30" s="48"/>
-      <c r="CE30" s="48"/>
-      <c r="CF30" s="48"/>
-      <c r="CG30" s="48"/>
-      <c r="CH30" s="48"/>
-      <c r="CI30" s="48"/>
-      <c r="CJ30" s="48"/>
-      <c r="CK30" s="48"/>
-      <c r="CL30" s="48"/>
-      <c r="CM30" s="48"/>
-      <c r="CN30" s="46"/>
-      <c r="CO30" s="46"/>
-      <c r="CP30" s="46"/>
-      <c r="CQ30" s="46"/>
-      <c r="CR30" s="46"/>
-      <c r="CS30" s="46"/>
-      <c r="CT30" s="46"/>
-      <c r="CU30" s="46"/>
-      <c r="CV30" s="46"/>
+      <c r="CD30" s="25"/>
+      <c r="CE30" s="25"/>
+      <c r="CF30" s="25"/>
+      <c r="CG30" s="25"/>
+      <c r="CH30" s="25"/>
+      <c r="CI30" s="25"/>
+      <c r="CJ30" s="25"/>
+      <c r="CK30" s="25"/>
+      <c r="CL30" s="25"/>
+      <c r="CM30" s="25"/>
+      <c r="CN30" s="36"/>
+      <c r="CO30" s="36"/>
+      <c r="CP30" s="36"/>
+      <c r="CQ30" s="36"/>
+      <c r="CR30" s="36"/>
+      <c r="CS30" s="36"/>
+      <c r="CT30" s="36"/>
+      <c r="CU30" s="36"/>
+      <c r="CV30" s="36"/>
       <c r="CX30" s="2"/>
       <c r="CY30" s="2"/>
       <c r="CZ30" s="2"/>
@@ -3755,124 +3761,124 @@
       <c r="FQ30" s="2"/>
     </row>
     <row r="31" spans="1:173" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="52" t="s">
+      <c r="A31" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="52"/>
-      <c r="I31" s="52"/>
-      <c r="J31" s="52"/>
-      <c r="K31" s="52"/>
-      <c r="L31" s="52"/>
-      <c r="M31" s="52"/>
-      <c r="N31" s="52"/>
-      <c r="O31" s="52"/>
-      <c r="P31" s="52"/>
-      <c r="Q31" s="52"/>
-      <c r="R31" s="52"/>
-      <c r="S31" s="52"/>
-      <c r="T31" s="52"/>
-      <c r="U31" s="52"/>
-      <c r="V31" s="52"/>
-      <c r="W31" s="46" t="s">
+      <c r="B31" s="35"/>
+      <c r="C31" s="35"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="35"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="X31" s="46"/>
-      <c r="Y31" s="46"/>
-      <c r="Z31" s="46"/>
-      <c r="AA31" s="46"/>
-      <c r="AB31" s="46"/>
-      <c r="AC31" s="46"/>
-      <c r="AD31" s="46"/>
-      <c r="AE31" s="46"/>
-      <c r="AF31" s="46"/>
-      <c r="AG31" s="48" t="s">
+      <c r="X31" s="36"/>
+      <c r="Y31" s="36"/>
+      <c r="Z31" s="36"/>
+      <c r="AA31" s="36"/>
+      <c r="AB31" s="36"/>
+      <c r="AC31" s="36"/>
+      <c r="AD31" s="36"/>
+      <c r="AE31" s="36"/>
+      <c r="AF31" s="36"/>
+      <c r="AG31" s="25" t="s">
         <v>57</v>
       </c>
-      <c r="AH31" s="48"/>
-      <c r="AI31" s="48"/>
-      <c r="AJ31" s="48"/>
-      <c r="AK31" s="48"/>
-      <c r="AL31" s="48"/>
-      <c r="AM31" s="48"/>
-      <c r="AN31" s="48"/>
-      <c r="AO31" s="48"/>
-      <c r="AP31" s="46" t="s">
+      <c r="AH31" s="25"/>
+      <c r="AI31" s="25"/>
+      <c r="AJ31" s="25"/>
+      <c r="AK31" s="25"/>
+      <c r="AL31" s="25"/>
+      <c r="AM31" s="25"/>
+      <c r="AN31" s="25"/>
+      <c r="AO31" s="25"/>
+      <c r="AP31" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="AQ31" s="46"/>
-      <c r="AR31" s="46"/>
-      <c r="AS31" s="46"/>
-      <c r="AT31" s="46"/>
-      <c r="AU31" s="46"/>
-      <c r="AV31" s="46"/>
-      <c r="AW31" s="46"/>
-      <c r="AX31" s="46"/>
-      <c r="AY31" s="46"/>
-      <c r="AZ31" s="48" t="s">
+      <c r="AQ31" s="36"/>
+      <c r="AR31" s="36"/>
+      <c r="AS31" s="36"/>
+      <c r="AT31" s="36"/>
+      <c r="AU31" s="36"/>
+      <c r="AV31" s="36"/>
+      <c r="AW31" s="36"/>
+      <c r="AX31" s="36"/>
+      <c r="AY31" s="36"/>
+      <c r="AZ31" s="25" t="s">
         <v>56</v>
       </c>
-      <c r="BA31" s="48"/>
-      <c r="BB31" s="48"/>
-      <c r="BC31" s="48"/>
-      <c r="BD31" s="48"/>
-      <c r="BE31" s="48"/>
-      <c r="BF31" s="48"/>
-      <c r="BG31" s="48"/>
-      <c r="BH31" s="48"/>
-      <c r="BI31" s="48"/>
-      <c r="BJ31" s="48"/>
-      <c r="BK31" s="49" t="s">
+      <c r="BA31" s="25"/>
+      <c r="BB31" s="25"/>
+      <c r="BC31" s="25"/>
+      <c r="BD31" s="25"/>
+      <c r="BE31" s="25"/>
+      <c r="BF31" s="25"/>
+      <c r="BG31" s="25"/>
+      <c r="BH31" s="25"/>
+      <c r="BI31" s="25"/>
+      <c r="BJ31" s="25"/>
+      <c r="BK31" s="34" t="s">
         <v>24</v>
       </c>
-      <c r="BL31" s="49"/>
-      <c r="BM31" s="49"/>
-      <c r="BN31" s="49"/>
-      <c r="BO31" s="49"/>
-      <c r="BP31" s="49"/>
-      <c r="BQ31" s="49"/>
-      <c r="BR31" s="49"/>
-      <c r="BS31" s="49"/>
-      <c r="BT31" s="51" t="s">
+      <c r="BL31" s="34"/>
+      <c r="BM31" s="34"/>
+      <c r="BN31" s="34"/>
+      <c r="BO31" s="34"/>
+      <c r="BP31" s="34"/>
+      <c r="BQ31" s="34"/>
+      <c r="BR31" s="34"/>
+      <c r="BS31" s="34"/>
+      <c r="BT31" s="26" t="s">
         <v>55</v>
       </c>
-      <c r="BU31" s="48"/>
-      <c r="BV31" s="48"/>
-      <c r="BW31" s="48"/>
-      <c r="BX31" s="48"/>
-      <c r="BY31" s="48"/>
-      <c r="BZ31" s="48"/>
-      <c r="CA31" s="48"/>
-      <c r="CB31" s="48"/>
-      <c r="CC31" s="48" t="s">
+      <c r="BU31" s="25"/>
+      <c r="BV31" s="25"/>
+      <c r="BW31" s="25"/>
+      <c r="BX31" s="25"/>
+      <c r="BY31" s="25"/>
+      <c r="BZ31" s="25"/>
+      <c r="CA31" s="25"/>
+      <c r="CB31" s="25"/>
+      <c r="CC31" s="25" t="s">
         <v>54</v>
       </c>
-      <c r="CD31" s="48"/>
-      <c r="CE31" s="48"/>
-      <c r="CF31" s="48"/>
-      <c r="CG31" s="48"/>
-      <c r="CH31" s="48"/>
-      <c r="CI31" s="48"/>
-      <c r="CJ31" s="48"/>
-      <c r="CK31" s="48"/>
-      <c r="CL31" s="48"/>
-      <c r="CM31" s="48"/>
-      <c r="CN31" s="46" t="s">
+      <c r="CD31" s="25"/>
+      <c r="CE31" s="25"/>
+      <c r="CF31" s="25"/>
+      <c r="CG31" s="25"/>
+      <c r="CH31" s="25"/>
+      <c r="CI31" s="25"/>
+      <c r="CJ31" s="25"/>
+      <c r="CK31" s="25"/>
+      <c r="CL31" s="25"/>
+      <c r="CM31" s="25"/>
+      <c r="CN31" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="CO31" s="46"/>
-      <c r="CP31" s="46"/>
-      <c r="CQ31" s="46"/>
-      <c r="CR31" s="46"/>
-      <c r="CS31" s="46"/>
-      <c r="CT31" s="46"/>
-      <c r="CU31" s="46"/>
-      <c r="CV31" s="46"/>
+      <c r="CO31" s="36"/>
+      <c r="CP31" s="36"/>
+      <c r="CQ31" s="36"/>
+      <c r="CR31" s="36"/>
+      <c r="CS31" s="36"/>
+      <c r="CT31" s="36"/>
+      <c r="CU31" s="36"/>
+      <c r="CV31" s="36"/>
       <c r="CX31" s="2"/>
       <c r="CY31" s="2"/>
       <c r="CZ31" s="2"/>
@@ -3947,106 +3953,106 @@
       <c r="FQ31" s="2"/>
     </row>
     <row r="32" spans="1:173" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="65"/>
-      <c r="B32" s="65"/>
-      <c r="C32" s="65"/>
-      <c r="D32" s="65"/>
-      <c r="E32" s="65"/>
-      <c r="F32" s="65"/>
-      <c r="G32" s="65"/>
-      <c r="H32" s="65"/>
-      <c r="I32" s="65"/>
-      <c r="J32" s="65"/>
-      <c r="K32" s="65"/>
-      <c r="L32" s="65"/>
-      <c r="M32" s="65"/>
-      <c r="N32" s="65"/>
-      <c r="O32" s="65"/>
-      <c r="P32" s="65"/>
-      <c r="Q32" s="65"/>
-      <c r="R32" s="65"/>
-      <c r="S32" s="65"/>
-      <c r="T32" s="65"/>
-      <c r="U32" s="65"/>
-      <c r="V32" s="65"/>
-      <c r="W32" s="65"/>
-      <c r="X32" s="65"/>
-      <c r="Y32" s="65"/>
-      <c r="Z32" s="65"/>
-      <c r="AA32" s="65"/>
-      <c r="AB32" s="65"/>
-      <c r="AC32" s="65"/>
-      <c r="AD32" s="65"/>
-      <c r="AE32" s="65"/>
-      <c r="AF32" s="65"/>
-      <c r="AG32" s="65"/>
-      <c r="AH32" s="65"/>
-      <c r="AI32" s="65"/>
-      <c r="AJ32" s="65"/>
-      <c r="AK32" s="65"/>
-      <c r="AL32" s="65"/>
-      <c r="AM32" s="65"/>
-      <c r="AN32" s="65"/>
-      <c r="AO32" s="65"/>
-      <c r="AP32" s="65"/>
-      <c r="AQ32" s="65"/>
-      <c r="AR32" s="65"/>
-      <c r="AS32" s="65"/>
-      <c r="AT32" s="65"/>
-      <c r="AU32" s="65"/>
-      <c r="AV32" s="65"/>
-      <c r="AW32" s="65"/>
-      <c r="AX32" s="65"/>
-      <c r="AY32" s="65"/>
-      <c r="AZ32" s="65"/>
-      <c r="BA32" s="65"/>
-      <c r="BB32" s="65"/>
-      <c r="BC32" s="65"/>
-      <c r="BD32" s="65"/>
-      <c r="BE32" s="65"/>
-      <c r="BF32" s="65"/>
-      <c r="BG32" s="65"/>
-      <c r="BH32" s="65"/>
-      <c r="BI32" s="65"/>
-      <c r="BJ32" s="65"/>
-      <c r="BK32" s="65"/>
-      <c r="BL32" s="65"/>
-      <c r="BM32" s="65"/>
-      <c r="BN32" s="65"/>
-      <c r="BO32" s="65"/>
-      <c r="BP32" s="65"/>
-      <c r="BQ32" s="65"/>
-      <c r="BR32" s="65"/>
-      <c r="BS32" s="65"/>
-      <c r="BT32" s="65"/>
-      <c r="BU32" s="65"/>
-      <c r="BV32" s="65"/>
-      <c r="BW32" s="65"/>
-      <c r="BX32" s="65"/>
-      <c r="BY32" s="65"/>
-      <c r="BZ32" s="65"/>
-      <c r="CA32" s="65"/>
-      <c r="CB32" s="65"/>
-      <c r="CC32" s="65"/>
-      <c r="CD32" s="65"/>
-      <c r="CE32" s="65"/>
-      <c r="CF32" s="65"/>
-      <c r="CG32" s="65"/>
-      <c r="CH32" s="65"/>
-      <c r="CI32" s="65"/>
-      <c r="CJ32" s="65"/>
-      <c r="CK32" s="65"/>
-      <c r="CL32" s="65"/>
-      <c r="CM32" s="65"/>
-      <c r="CN32" s="65"/>
-      <c r="CO32" s="65"/>
-      <c r="CP32" s="65"/>
-      <c r="CQ32" s="65"/>
-      <c r="CR32" s="65"/>
-      <c r="CS32" s="65"/>
-      <c r="CT32" s="65"/>
-      <c r="CU32" s="65"/>
-      <c r="CV32" s="65"/>
+      <c r="A32" s="22"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="22"/>
+      <c r="N32" s="22"/>
+      <c r="O32" s="22"/>
+      <c r="P32" s="22"/>
+      <c r="Q32" s="22"/>
+      <c r="R32" s="22"/>
+      <c r="S32" s="22"/>
+      <c r="T32" s="22"/>
+      <c r="U32" s="22"/>
+      <c r="V32" s="22"/>
+      <c r="W32" s="22"/>
+      <c r="X32" s="22"/>
+      <c r="Y32" s="22"/>
+      <c r="Z32" s="22"/>
+      <c r="AA32" s="22"/>
+      <c r="AB32" s="22"/>
+      <c r="AC32" s="22"/>
+      <c r="AD32" s="22"/>
+      <c r="AE32" s="22"/>
+      <c r="AF32" s="22"/>
+      <c r="AG32" s="22"/>
+      <c r="AH32" s="22"/>
+      <c r="AI32" s="22"/>
+      <c r="AJ32" s="22"/>
+      <c r="AK32" s="22"/>
+      <c r="AL32" s="22"/>
+      <c r="AM32" s="22"/>
+      <c r="AN32" s="22"/>
+      <c r="AO32" s="22"/>
+      <c r="AP32" s="22"/>
+      <c r="AQ32" s="22"/>
+      <c r="AR32" s="22"/>
+      <c r="AS32" s="22"/>
+      <c r="AT32" s="22"/>
+      <c r="AU32" s="22"/>
+      <c r="AV32" s="22"/>
+      <c r="AW32" s="22"/>
+      <c r="AX32" s="22"/>
+      <c r="AY32" s="22"/>
+      <c r="AZ32" s="22"/>
+      <c r="BA32" s="22"/>
+      <c r="BB32" s="22"/>
+      <c r="BC32" s="22"/>
+      <c r="BD32" s="22"/>
+      <c r="BE32" s="22"/>
+      <c r="BF32" s="22"/>
+      <c r="BG32" s="22"/>
+      <c r="BH32" s="22"/>
+      <c r="BI32" s="22"/>
+      <c r="BJ32" s="22"/>
+      <c r="BK32" s="22"/>
+      <c r="BL32" s="22"/>
+      <c r="BM32" s="22"/>
+      <c r="BN32" s="22"/>
+      <c r="BO32" s="22"/>
+      <c r="BP32" s="22"/>
+      <c r="BQ32" s="22"/>
+      <c r="BR32" s="22"/>
+      <c r="BS32" s="22"/>
+      <c r="BT32" s="22"/>
+      <c r="BU32" s="22"/>
+      <c r="BV32" s="22"/>
+      <c r="BW32" s="22"/>
+      <c r="BX32" s="22"/>
+      <c r="BY32" s="22"/>
+      <c r="BZ32" s="22"/>
+      <c r="CA32" s="22"/>
+      <c r="CB32" s="22"/>
+      <c r="CC32" s="22"/>
+      <c r="CD32" s="22"/>
+      <c r="CE32" s="22"/>
+      <c r="CF32" s="22"/>
+      <c r="CG32" s="22"/>
+      <c r="CH32" s="22"/>
+      <c r="CI32" s="22"/>
+      <c r="CJ32" s="22"/>
+      <c r="CK32" s="22"/>
+      <c r="CL32" s="22"/>
+      <c r="CM32" s="22"/>
+      <c r="CN32" s="22"/>
+      <c r="CO32" s="22"/>
+      <c r="CP32" s="22"/>
+      <c r="CQ32" s="22"/>
+      <c r="CR32" s="22"/>
+      <c r="CS32" s="22"/>
+      <c r="CT32" s="22"/>
+      <c r="CU32" s="22"/>
+      <c r="CV32" s="22"/>
       <c r="CX32" s="2"/>
       <c r="CY32" s="2"/>
       <c r="CZ32" s="2"/>
@@ -4121,78 +4127,78 @@
       <c r="FQ32" s="2"/>
     </row>
     <row r="33" spans="1:173" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="67" t="s">
+      <c r="A33" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="67"/>
-      <c r="C33" s="67"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="67"/>
-      <c r="G33" s="67"/>
-      <c r="H33" s="67"/>
-      <c r="I33" s="67"/>
-      <c r="J33" s="67"/>
-      <c r="K33" s="67"/>
-      <c r="L33" s="67"/>
-      <c r="M33" s="67"/>
-      <c r="N33" s="67"/>
-      <c r="O33" s="67"/>
-      <c r="P33" s="67"/>
-      <c r="Q33" s="67"/>
+      <c r="B33" s="24"/>
+      <c r="C33" s="24"/>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24"/>
+      <c r="Q33" s="24"/>
       <c r="R33" s="8"/>
-      <c r="S33" s="66" t="s">
+      <c r="S33" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="T33" s="66"/>
-      <c r="U33" s="66"/>
-      <c r="V33" s="66"/>
-      <c r="W33" s="66"/>
-      <c r="X33" s="66"/>
-      <c r="Y33" s="66"/>
-      <c r="Z33" s="66"/>
-      <c r="AA33" s="66"/>
-      <c r="AB33" s="66"/>
-      <c r="AC33" s="66"/>
-      <c r="AD33" s="66"/>
-      <c r="AE33" s="66"/>
-      <c r="AF33" s="66"/>
-      <c r="AG33" s="66"/>
-      <c r="AH33" s="66"/>
-      <c r="AI33" s="66"/>
-      <c r="AJ33" s="66"/>
-      <c r="AK33" s="66"/>
-      <c r="AL33" s="66"/>
-      <c r="AM33" s="66"/>
-      <c r="AN33" s="66"/>
-      <c r="AO33" s="66"/>
-      <c r="AP33" s="66"/>
-      <c r="AQ33" s="66"/>
-      <c r="AR33" s="66"/>
-      <c r="AS33" s="66"/>
-      <c r="AT33" s="66"/>
-      <c r="AU33" s="66"/>
-      <c r="AV33" s="66"/>
-      <c r="AW33" s="66"/>
-      <c r="AX33" s="66"/>
-      <c r="AY33" s="66"/>
-      <c r="AZ33" s="66"/>
-      <c r="BA33" s="66"/>
-      <c r="BB33" s="66"/>
-      <c r="BC33" s="66"/>
-      <c r="BD33" s="66"/>
-      <c r="BE33" s="66"/>
-      <c r="BF33" s="66"/>
-      <c r="BG33" s="66"/>
-      <c r="BH33" s="66"/>
-      <c r="BI33" s="66"/>
-      <c r="BJ33" s="66"/>
-      <c r="BK33" s="66"/>
-      <c r="BL33" s="66"/>
-      <c r="BM33" s="66"/>
-      <c r="BN33" s="66"/>
-      <c r="BO33" s="66"/>
-      <c r="BP33" s="66"/>
+      <c r="T33" s="17"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="17"/>
+      <c r="W33" s="17"/>
+      <c r="X33" s="17"/>
+      <c r="Y33" s="17"/>
+      <c r="Z33" s="17"/>
+      <c r="AA33" s="17"/>
+      <c r="AB33" s="17"/>
+      <c r="AC33" s="17"/>
+      <c r="AD33" s="17"/>
+      <c r="AE33" s="17"/>
+      <c r="AF33" s="17"/>
+      <c r="AG33" s="17"/>
+      <c r="AH33" s="17"/>
+      <c r="AI33" s="17"/>
+      <c r="AJ33" s="17"/>
+      <c r="AK33" s="17"/>
+      <c r="AL33" s="17"/>
+      <c r="AM33" s="17"/>
+      <c r="AN33" s="17"/>
+      <c r="AO33" s="17"/>
+      <c r="AP33" s="17"/>
+      <c r="AQ33" s="17"/>
+      <c r="AR33" s="17"/>
+      <c r="AS33" s="17"/>
+      <c r="AT33" s="17"/>
+      <c r="AU33" s="17"/>
+      <c r="AV33" s="17"/>
+      <c r="AW33" s="17"/>
+      <c r="AX33" s="17"/>
+      <c r="AY33" s="17"/>
+      <c r="AZ33" s="17"/>
+      <c r="BA33" s="17"/>
+      <c r="BB33" s="17"/>
+      <c r="BC33" s="17"/>
+      <c r="BD33" s="17"/>
+      <c r="BE33" s="17"/>
+      <c r="BF33" s="17"/>
+      <c r="BG33" s="17"/>
+      <c r="BH33" s="17"/>
+      <c r="BI33" s="17"/>
+      <c r="BJ33" s="17"/>
+      <c r="BK33" s="17"/>
+      <c r="BL33" s="17"/>
+      <c r="BM33" s="17"/>
+      <c r="BN33" s="17"/>
+      <c r="BO33" s="17"/>
+      <c r="BP33" s="17"/>
       <c r="BQ33" s="8"/>
       <c r="BR33" s="8" t="s">
         <v>29</v>
@@ -4202,25 +4208,25 @@
       <c r="BU33" s="8"/>
       <c r="BV33" s="8"/>
       <c r="BW33" s="8"/>
-      <c r="BX33" s="66"/>
-      <c r="BY33" s="66"/>
-      <c r="BZ33" s="66"/>
-      <c r="CA33" s="66"/>
-      <c r="CB33" s="66"/>
-      <c r="CC33" s="66"/>
-      <c r="CD33" s="66"/>
-      <c r="CE33" s="66"/>
-      <c r="CF33" s="66"/>
-      <c r="CG33" s="66"/>
-      <c r="CH33" s="66"/>
-      <c r="CI33" s="66"/>
-      <c r="CJ33" s="66"/>
-      <c r="CK33" s="66"/>
-      <c r="CL33" s="66"/>
-      <c r="CM33" s="66"/>
-      <c r="CN33" s="66"/>
-      <c r="CO33" s="66"/>
-      <c r="CP33" s="66"/>
+      <c r="BX33" s="17"/>
+      <c r="BY33" s="17"/>
+      <c r="BZ33" s="17"/>
+      <c r="CA33" s="17"/>
+      <c r="CB33" s="17"/>
+      <c r="CC33" s="17"/>
+      <c r="CD33" s="17"/>
+      <c r="CE33" s="17"/>
+      <c r="CF33" s="17"/>
+      <c r="CG33" s="17"/>
+      <c r="CH33" s="17"/>
+      <c r="CI33" s="17"/>
+      <c r="CJ33" s="17"/>
+      <c r="CK33" s="17"/>
+      <c r="CL33" s="17"/>
+      <c r="CM33" s="17"/>
+      <c r="CN33" s="17"/>
+      <c r="CO33" s="17"/>
+      <c r="CP33" s="17"/>
       <c r="CQ33" s="8"/>
       <c r="CR33" s="8" t="s">
         <v>28</v>
@@ -4321,58 +4327,58 @@
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="10"/>
-      <c r="S34" s="17" t="s">
+      <c r="S34" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="T34" s="17"/>
-      <c r="U34" s="17"/>
-      <c r="V34" s="17"/>
-      <c r="W34" s="17"/>
-      <c r="X34" s="17"/>
-      <c r="Y34" s="17"/>
-      <c r="Z34" s="17"/>
-      <c r="AA34" s="17"/>
-      <c r="AB34" s="17"/>
-      <c r="AC34" s="17"/>
-      <c r="AD34" s="17"/>
-      <c r="AE34" s="17"/>
-      <c r="AF34" s="17"/>
-      <c r="AG34" s="17"/>
-      <c r="AH34" s="17"/>
-      <c r="AI34" s="17"/>
-      <c r="AJ34" s="17"/>
-      <c r="AK34" s="17"/>
-      <c r="AL34" s="17"/>
-      <c r="AM34" s="17"/>
-      <c r="AN34" s="17"/>
-      <c r="AO34" s="17"/>
-      <c r="AP34" s="17"/>
-      <c r="AQ34" s="17"/>
-      <c r="AR34" s="17"/>
-      <c r="AS34" s="17"/>
-      <c r="AT34" s="17"/>
-      <c r="AU34" s="17"/>
-      <c r="AV34" s="17"/>
-      <c r="AW34" s="17"/>
-      <c r="AX34" s="17"/>
-      <c r="AY34" s="17"/>
-      <c r="AZ34" s="17"/>
-      <c r="BA34" s="17"/>
-      <c r="BB34" s="17"/>
-      <c r="BC34" s="17"/>
-      <c r="BD34" s="17"/>
-      <c r="BE34" s="17"/>
-      <c r="BF34" s="17"/>
-      <c r="BG34" s="17"/>
-      <c r="BH34" s="17"/>
-      <c r="BI34" s="17"/>
-      <c r="BJ34" s="17"/>
-      <c r="BK34" s="17"/>
-      <c r="BL34" s="17"/>
-      <c r="BM34" s="17"/>
-      <c r="BN34" s="17"/>
-      <c r="BO34" s="17"/>
-      <c r="BP34" s="17"/>
+      <c r="T34" s="16"/>
+      <c r="U34" s="16"/>
+      <c r="V34" s="16"/>
+      <c r="W34" s="16"/>
+      <c r="X34" s="16"/>
+      <c r="Y34" s="16"/>
+      <c r="Z34" s="16"/>
+      <c r="AA34" s="16"/>
+      <c r="AB34" s="16"/>
+      <c r="AC34" s="16"/>
+      <c r="AD34" s="16"/>
+      <c r="AE34" s="16"/>
+      <c r="AF34" s="16"/>
+      <c r="AG34" s="16"/>
+      <c r="AH34" s="16"/>
+      <c r="AI34" s="16"/>
+      <c r="AJ34" s="16"/>
+      <c r="AK34" s="16"/>
+      <c r="AL34" s="16"/>
+      <c r="AM34" s="16"/>
+      <c r="AN34" s="16"/>
+      <c r="AO34" s="16"/>
+      <c r="AP34" s="16"/>
+      <c r="AQ34" s="16"/>
+      <c r="AR34" s="16"/>
+      <c r="AS34" s="16"/>
+      <c r="AT34" s="16"/>
+      <c r="AU34" s="16"/>
+      <c r="AV34" s="16"/>
+      <c r="AW34" s="16"/>
+      <c r="AX34" s="16"/>
+      <c r="AY34" s="16"/>
+      <c r="AZ34" s="16"/>
+      <c r="BA34" s="16"/>
+      <c r="BB34" s="16"/>
+      <c r="BC34" s="16"/>
+      <c r="BD34" s="16"/>
+      <c r="BE34" s="16"/>
+      <c r="BF34" s="16"/>
+      <c r="BG34" s="16"/>
+      <c r="BH34" s="16"/>
+      <c r="BI34" s="16"/>
+      <c r="BJ34" s="16"/>
+      <c r="BK34" s="16"/>
+      <c r="BL34" s="16"/>
+      <c r="BM34" s="16"/>
+      <c r="BN34" s="16"/>
+      <c r="BO34" s="16"/>
+      <c r="BP34" s="16"/>
       <c r="BQ34" s="10"/>
       <c r="BR34" s="10"/>
       <c r="BS34" s="10"/>
@@ -4380,27 +4386,27 @@
       <c r="BU34" s="10"/>
       <c r="BV34" s="10"/>
       <c r="BW34" s="10"/>
-      <c r="BX34" s="17" t="s">
+      <c r="BX34" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BY34" s="17"/>
-      <c r="BZ34" s="17"/>
-      <c r="CA34" s="17"/>
-      <c r="CB34" s="17"/>
-      <c r="CC34" s="17"/>
-      <c r="CD34" s="17"/>
-      <c r="CE34" s="17"/>
-      <c r="CF34" s="17"/>
-      <c r="CG34" s="17"/>
-      <c r="CH34" s="17"/>
-      <c r="CI34" s="17"/>
-      <c r="CJ34" s="17"/>
-      <c r="CK34" s="17"/>
-      <c r="CL34" s="17"/>
-      <c r="CM34" s="17"/>
-      <c r="CN34" s="17"/>
-      <c r="CO34" s="17"/>
-      <c r="CP34" s="17"/>
+      <c r="BY34" s="16"/>
+      <c r="BZ34" s="16"/>
+      <c r="CA34" s="16"/>
+      <c r="CB34" s="16"/>
+      <c r="CC34" s="16"/>
+      <c r="CD34" s="16"/>
+      <c r="CE34" s="16"/>
+      <c r="CF34" s="16"/>
+      <c r="CG34" s="16"/>
+      <c r="CH34" s="16"/>
+      <c r="CI34" s="16"/>
+      <c r="CJ34" s="16"/>
+      <c r="CK34" s="16"/>
+      <c r="CL34" s="16"/>
+      <c r="CM34" s="16"/>
+      <c r="CN34" s="16"/>
+      <c r="CO34" s="16"/>
+      <c r="CP34" s="16"/>
       <c r="CQ34" s="10"/>
       <c r="CR34" s="10"/>
       <c r="CS34" s="10"/>
@@ -4535,54 +4541,54 @@
       <c r="T36" s="12"/>
       <c r="U36" s="12"/>
       <c r="V36" s="12"/>
-      <c r="W36" s="66" t="s">
+      <c r="W36" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="X36" s="66"/>
-      <c r="Y36" s="66"/>
-      <c r="Z36" s="66"/>
-      <c r="AA36" s="66"/>
-      <c r="AB36" s="66"/>
-      <c r="AC36" s="66"/>
-      <c r="AD36" s="66"/>
-      <c r="AE36" s="66"/>
-      <c r="AF36" s="66"/>
-      <c r="AG36" s="66"/>
-      <c r="AH36" s="66"/>
-      <c r="AI36" s="66"/>
-      <c r="AJ36" s="66"/>
-      <c r="AK36" s="66"/>
-      <c r="AL36" s="66"/>
-      <c r="AM36" s="66"/>
-      <c r="AN36" s="66"/>
-      <c r="AO36" s="66"/>
-      <c r="AP36" s="66"/>
-      <c r="AQ36" s="66"/>
-      <c r="AR36" s="66"/>
-      <c r="AS36" s="66"/>
-      <c r="AT36" s="66"/>
-      <c r="AU36" s="66"/>
-      <c r="AV36" s="66"/>
-      <c r="AW36" s="66"/>
-      <c r="AX36" s="66"/>
-      <c r="AY36" s="66"/>
-      <c r="AZ36" s="66"/>
-      <c r="BA36" s="66"/>
-      <c r="BB36" s="66"/>
-      <c r="BC36" s="66"/>
-      <c r="BD36" s="66"/>
-      <c r="BE36" s="66"/>
-      <c r="BF36" s="66"/>
-      <c r="BG36" s="66"/>
-      <c r="BH36" s="66"/>
-      <c r="BI36" s="66"/>
-      <c r="BJ36" s="66"/>
-      <c r="BK36" s="66"/>
-      <c r="BL36" s="66"/>
-      <c r="BM36" s="66"/>
-      <c r="BN36" s="66"/>
-      <c r="BO36" s="66"/>
-      <c r="BP36" s="66"/>
+      <c r="X36" s="17"/>
+      <c r="Y36" s="17"/>
+      <c r="Z36" s="17"/>
+      <c r="AA36" s="17"/>
+      <c r="AB36" s="17"/>
+      <c r="AC36" s="17"/>
+      <c r="AD36" s="17"/>
+      <c r="AE36" s="17"/>
+      <c r="AF36" s="17"/>
+      <c r="AG36" s="17"/>
+      <c r="AH36" s="17"/>
+      <c r="AI36" s="17"/>
+      <c r="AJ36" s="17"/>
+      <c r="AK36" s="17"/>
+      <c r="AL36" s="17"/>
+      <c r="AM36" s="17"/>
+      <c r="AN36" s="17"/>
+      <c r="AO36" s="17"/>
+      <c r="AP36" s="17"/>
+      <c r="AQ36" s="17"/>
+      <c r="AR36" s="17"/>
+      <c r="AS36" s="17"/>
+      <c r="AT36" s="17"/>
+      <c r="AU36" s="17"/>
+      <c r="AV36" s="17"/>
+      <c r="AW36" s="17"/>
+      <c r="AX36" s="17"/>
+      <c r="AY36" s="17"/>
+      <c r="AZ36" s="17"/>
+      <c r="BA36" s="17"/>
+      <c r="BB36" s="17"/>
+      <c r="BC36" s="17"/>
+      <c r="BD36" s="17"/>
+      <c r="BE36" s="17"/>
+      <c r="BF36" s="17"/>
+      <c r="BG36" s="17"/>
+      <c r="BH36" s="17"/>
+      <c r="BI36" s="17"/>
+      <c r="BJ36" s="17"/>
+      <c r="BK36" s="17"/>
+      <c r="BL36" s="17"/>
+      <c r="BM36" s="17"/>
+      <c r="BN36" s="17"/>
+      <c r="BO36" s="17"/>
+      <c r="BP36" s="17"/>
       <c r="BQ36" s="8"/>
       <c r="BR36" s="8" t="s">
         <v>29</v>
@@ -4592,25 +4598,25 @@
       <c r="BU36" s="8"/>
       <c r="BV36" s="8"/>
       <c r="BW36" s="8"/>
-      <c r="BX36" s="66"/>
-      <c r="BY36" s="66"/>
-      <c r="BZ36" s="66"/>
-      <c r="CA36" s="66"/>
-      <c r="CB36" s="66"/>
-      <c r="CC36" s="66"/>
-      <c r="CD36" s="66"/>
-      <c r="CE36" s="66"/>
-      <c r="CF36" s="66"/>
-      <c r="CG36" s="66"/>
-      <c r="CH36" s="66"/>
-      <c r="CI36" s="66"/>
-      <c r="CJ36" s="66"/>
-      <c r="CK36" s="66"/>
-      <c r="CL36" s="66"/>
-      <c r="CM36" s="66"/>
-      <c r="CN36" s="66"/>
-      <c r="CO36" s="66"/>
-      <c r="CP36" s="66"/>
+      <c r="BX36" s="17"/>
+      <c r="BY36" s="17"/>
+      <c r="BZ36" s="17"/>
+      <c r="CA36" s="17"/>
+      <c r="CB36" s="17"/>
+      <c r="CC36" s="17"/>
+      <c r="CD36" s="17"/>
+      <c r="CE36" s="17"/>
+      <c r="CF36" s="17"/>
+      <c r="CG36" s="17"/>
+      <c r="CH36" s="17"/>
+      <c r="CI36" s="17"/>
+      <c r="CJ36" s="17"/>
+      <c r="CK36" s="17"/>
+      <c r="CL36" s="17"/>
+      <c r="CM36" s="17"/>
+      <c r="CN36" s="17"/>
+      <c r="CO36" s="17"/>
+      <c r="CP36" s="17"/>
       <c r="CQ36" s="8"/>
       <c r="CR36" s="8" t="s">
         <v>28</v>
@@ -4642,54 +4648,54 @@
       <c r="T37" s="13"/>
       <c r="U37" s="13"/>
       <c r="V37" s="13"/>
-      <c r="W37" s="17" t="s">
+      <c r="W37" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="X37" s="17"/>
-      <c r="Y37" s="17"/>
-      <c r="Z37" s="17"/>
-      <c r="AA37" s="17"/>
-      <c r="AB37" s="17"/>
-      <c r="AC37" s="17"/>
-      <c r="AD37" s="17"/>
-      <c r="AE37" s="17"/>
-      <c r="AF37" s="17"/>
-      <c r="AG37" s="17"/>
-      <c r="AH37" s="17"/>
-      <c r="AI37" s="17"/>
-      <c r="AJ37" s="17"/>
-      <c r="AK37" s="17"/>
-      <c r="AL37" s="17"/>
-      <c r="AM37" s="17"/>
-      <c r="AN37" s="17"/>
-      <c r="AO37" s="17"/>
-      <c r="AP37" s="17"/>
-      <c r="AQ37" s="17"/>
-      <c r="AR37" s="17"/>
-      <c r="AS37" s="17"/>
-      <c r="AT37" s="17"/>
-      <c r="AU37" s="17"/>
-      <c r="AV37" s="17"/>
-      <c r="AW37" s="17"/>
-      <c r="AX37" s="17"/>
-      <c r="AY37" s="17"/>
-      <c r="AZ37" s="17"/>
-      <c r="BA37" s="17"/>
-      <c r="BB37" s="17"/>
-      <c r="BC37" s="17"/>
-      <c r="BD37" s="17"/>
-      <c r="BE37" s="17"/>
-      <c r="BF37" s="17"/>
-      <c r="BG37" s="17"/>
-      <c r="BH37" s="17"/>
-      <c r="BI37" s="17"/>
-      <c r="BJ37" s="17"/>
-      <c r="BK37" s="17"/>
-      <c r="BL37" s="17"/>
-      <c r="BM37" s="17"/>
-      <c r="BN37" s="17"/>
-      <c r="BO37" s="17"/>
-      <c r="BP37" s="17"/>
+      <c r="X37" s="16"/>
+      <c r="Y37" s="16"/>
+      <c r="Z37" s="16"/>
+      <c r="AA37" s="16"/>
+      <c r="AB37" s="16"/>
+      <c r="AC37" s="16"/>
+      <c r="AD37" s="16"/>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="16"/>
+      <c r="AG37" s="16"/>
+      <c r="AH37" s="16"/>
+      <c r="AI37" s="16"/>
+      <c r="AJ37" s="16"/>
+      <c r="AK37" s="16"/>
+      <c r="AL37" s="16"/>
+      <c r="AM37" s="16"/>
+      <c r="AN37" s="16"/>
+      <c r="AO37" s="16"/>
+      <c r="AP37" s="16"/>
+      <c r="AQ37" s="16"/>
+      <c r="AR37" s="16"/>
+      <c r="AS37" s="16"/>
+      <c r="AT37" s="16"/>
+      <c r="AU37" s="16"/>
+      <c r="AV37" s="16"/>
+      <c r="AW37" s="16"/>
+      <c r="AX37" s="16"/>
+      <c r="AY37" s="16"/>
+      <c r="AZ37" s="16"/>
+      <c r="BA37" s="16"/>
+      <c r="BB37" s="16"/>
+      <c r="BC37" s="16"/>
+      <c r="BD37" s="16"/>
+      <c r="BE37" s="16"/>
+      <c r="BF37" s="16"/>
+      <c r="BG37" s="16"/>
+      <c r="BH37" s="16"/>
+      <c r="BI37" s="16"/>
+      <c r="BJ37" s="16"/>
+      <c r="BK37" s="16"/>
+      <c r="BL37" s="16"/>
+      <c r="BM37" s="16"/>
+      <c r="BN37" s="16"/>
+      <c r="BO37" s="16"/>
+      <c r="BP37" s="16"/>
       <c r="BQ37" s="10"/>
       <c r="BR37" s="10"/>
       <c r="BS37" s="10"/>
@@ -4697,27 +4703,27 @@
       <c r="BU37" s="10"/>
       <c r="BV37" s="10"/>
       <c r="BW37" s="10"/>
-      <c r="BX37" s="17" t="s">
+      <c r="BX37" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="BY37" s="17"/>
-      <c r="BZ37" s="17"/>
-      <c r="CA37" s="17"/>
-      <c r="CB37" s="17"/>
-      <c r="CC37" s="17"/>
-      <c r="CD37" s="17"/>
-      <c r="CE37" s="17"/>
-      <c r="CF37" s="17"/>
-      <c r="CG37" s="17"/>
-      <c r="CH37" s="17"/>
-      <c r="CI37" s="17"/>
-      <c r="CJ37" s="17"/>
-      <c r="CK37" s="17"/>
-      <c r="CL37" s="17"/>
-      <c r="CM37" s="17"/>
-      <c r="CN37" s="17"/>
-      <c r="CO37" s="17"/>
-      <c r="CP37" s="17"/>
+      <c r="BY37" s="16"/>
+      <c r="BZ37" s="16"/>
+      <c r="CA37" s="16"/>
+      <c r="CB37" s="16"/>
+      <c r="CC37" s="16"/>
+      <c r="CD37" s="16"/>
+      <c r="CE37" s="16"/>
+      <c r="CF37" s="16"/>
+      <c r="CG37" s="16"/>
+      <c r="CH37" s="16"/>
+      <c r="CI37" s="16"/>
+      <c r="CJ37" s="16"/>
+      <c r="CK37" s="16"/>
+      <c r="CL37" s="16"/>
+      <c r="CM37" s="16"/>
+      <c r="CN37" s="16"/>
+      <c r="CO37" s="16"/>
+      <c r="CP37" s="16"/>
       <c r="CQ37" s="10"/>
       <c r="CR37" s="10"/>
       <c r="CS37" s="10"/>
@@ -4828,110 +4834,110 @@
       <c r="CV38" s="1"/>
     </row>
     <row r="39" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="53" t="s">
+      <c r="A39" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="53"/>
-      <c r="C39" s="53"/>
-      <c r="D39" s="53"/>
-      <c r="E39" s="53"/>
-      <c r="F39" s="53"/>
-      <c r="G39" s="53"/>
-      <c r="H39" s="53"/>
-      <c r="I39" s="53"/>
-      <c r="J39" s="53"/>
-      <c r="K39" s="53"/>
-      <c r="L39" s="53"/>
-      <c r="M39" s="53"/>
-      <c r="N39" s="53"/>
-      <c r="O39" s="53"/>
-      <c r="P39" s="53"/>
+      <c r="B39" s="19"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="19"/>
+      <c r="E39" s="19"/>
+      <c r="F39" s="19"/>
+      <c r="G39" s="19"/>
+      <c r="H39" s="19"/>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19"/>
+      <c r="K39" s="19"/>
+      <c r="L39" s="19"/>
+      <c r="M39" s="19"/>
+      <c r="N39" s="19"/>
+      <c r="O39" s="19"/>
+      <c r="P39" s="19"/>
       <c r="Q39" s="1"/>
-      <c r="R39" s="54" t="s">
+      <c r="R39" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="S39" s="54"/>
-      <c r="T39" s="54"/>
-      <c r="U39" s="54"/>
-      <c r="V39" s="54"/>
-      <c r="W39" s="54"/>
-      <c r="X39" s="54"/>
-      <c r="Y39" s="54"/>
-      <c r="Z39" s="54"/>
-      <c r="AA39" s="54"/>
-      <c r="AB39" s="54"/>
-      <c r="AC39" s="54"/>
-      <c r="AD39" s="54"/>
-      <c r="AE39" s="54"/>
-      <c r="AF39" s="54"/>
-      <c r="AG39" s="54"/>
-      <c r="AH39" s="54"/>
-      <c r="AI39" s="54"/>
-      <c r="AJ39" s="54"/>
-      <c r="AK39" s="54"/>
-      <c r="AL39" s="54"/>
-      <c r="AM39" s="54"/>
-      <c r="AN39" s="54"/>
-      <c r="AO39" s="54"/>
-      <c r="AP39" s="54"/>
-      <c r="AQ39" s="54"/>
-      <c r="AR39" s="54"/>
-      <c r="AS39" s="54"/>
-      <c r="AT39" s="54"/>
-      <c r="AU39" s="54"/>
-      <c r="AV39" s="54"/>
-      <c r="AW39" s="54"/>
-      <c r="AX39" s="54"/>
-      <c r="AY39" s="54"/>
-      <c r="AZ39" s="54"/>
-      <c r="BA39" s="54"/>
-      <c r="BB39" s="54"/>
-      <c r="BC39" s="54"/>
-      <c r="BD39" s="54"/>
-      <c r="BE39" s="54"/>
-      <c r="BF39" s="54"/>
-      <c r="BG39" s="54"/>
-      <c r="BH39" s="54"/>
-      <c r="BI39" s="54"/>
-      <c r="BJ39" s="54"/>
-      <c r="BK39" s="54"/>
-      <c r="BL39" s="54"/>
-      <c r="BM39" s="54"/>
-      <c r="BN39" s="54"/>
-      <c r="BO39" s="54"/>
-      <c r="BP39" s="54"/>
-      <c r="BQ39" s="54"/>
-      <c r="BR39" s="54"/>
-      <c r="BS39" s="54"/>
-      <c r="BT39" s="54"/>
-      <c r="BU39" s="54"/>
-      <c r="BV39" s="54"/>
-      <c r="BW39" s="54"/>
-      <c r="BX39" s="54"/>
-      <c r="BY39" s="54"/>
-      <c r="BZ39" s="54"/>
-      <c r="CA39" s="54"/>
-      <c r="CB39" s="54"/>
-      <c r="CC39" s="54"/>
-      <c r="CD39" s="54"/>
-      <c r="CE39" s="54"/>
-      <c r="CF39" s="54"/>
-      <c r="CG39" s="54"/>
-      <c r="CH39" s="54"/>
-      <c r="CI39" s="54"/>
-      <c r="CJ39" s="54"/>
-      <c r="CK39" s="54"/>
-      <c r="CL39" s="54"/>
-      <c r="CM39" s="54"/>
-      <c r="CN39" s="54"/>
-      <c r="CO39" s="54"/>
-      <c r="CP39" s="54"/>
-      <c r="CQ39" s="54"/>
-      <c r="CR39" s="54"/>
-      <c r="CS39" s="54"/>
-      <c r="CT39" s="54"/>
-      <c r="CU39" s="54"/>
-      <c r="CV39" s="54"/>
+      <c r="S39" s="20"/>
+      <c r="T39" s="20"/>
+      <c r="U39" s="20"/>
+      <c r="V39" s="20"/>
+      <c r="W39" s="20"/>
+      <c r="X39" s="20"/>
+      <c r="Y39" s="20"/>
+      <c r="Z39" s="20"/>
+      <c r="AA39" s="20"/>
+      <c r="AB39" s="20"/>
+      <c r="AC39" s="20"/>
+      <c r="AD39" s="20"/>
+      <c r="AE39" s="20"/>
+      <c r="AF39" s="20"/>
+      <c r="AG39" s="20"/>
+      <c r="AH39" s="20"/>
+      <c r="AI39" s="20"/>
+      <c r="AJ39" s="20"/>
+      <c r="AK39" s="20"/>
+      <c r="AL39" s="20"/>
+      <c r="AM39" s="20"/>
+      <c r="AN39" s="20"/>
+      <c r="AO39" s="20"/>
+      <c r="AP39" s="20"/>
+      <c r="AQ39" s="20"/>
+      <c r="AR39" s="20"/>
+      <c r="AS39" s="20"/>
+      <c r="AT39" s="20"/>
+      <c r="AU39" s="20"/>
+      <c r="AV39" s="20"/>
+      <c r="AW39" s="20"/>
+      <c r="AX39" s="20"/>
+      <c r="AY39" s="20"/>
+      <c r="AZ39" s="20"/>
+      <c r="BA39" s="20"/>
+      <c r="BB39" s="20"/>
+      <c r="BC39" s="20"/>
+      <c r="BD39" s="20"/>
+      <c r="BE39" s="20"/>
+      <c r="BF39" s="20"/>
+      <c r="BG39" s="20"/>
+      <c r="BH39" s="20"/>
+      <c r="BI39" s="20"/>
+      <c r="BJ39" s="20"/>
+      <c r="BK39" s="20"/>
+      <c r="BL39" s="20"/>
+      <c r="BM39" s="20"/>
+      <c r="BN39" s="20"/>
+      <c r="BO39" s="20"/>
+      <c r="BP39" s="20"/>
+      <c r="BQ39" s="20"/>
+      <c r="BR39" s="20"/>
+      <c r="BS39" s="20"/>
+      <c r="BT39" s="20"/>
+      <c r="BU39" s="20"/>
+      <c r="BV39" s="20"/>
+      <c r="BW39" s="20"/>
+      <c r="BX39" s="20"/>
+      <c r="BY39" s="20"/>
+      <c r="BZ39" s="20"/>
+      <c r="CA39" s="20"/>
+      <c r="CB39" s="20"/>
+      <c r="CC39" s="20"/>
+      <c r="CD39" s="20"/>
+      <c r="CE39" s="20"/>
+      <c r="CF39" s="20"/>
+      <c r="CG39" s="20"/>
+      <c r="CH39" s="20"/>
+      <c r="CI39" s="20"/>
+      <c r="CJ39" s="20"/>
+      <c r="CK39" s="20"/>
+      <c r="CL39" s="20"/>
+      <c r="CM39" s="20"/>
+      <c r="CN39" s="20"/>
+      <c r="CO39" s="20"/>
+      <c r="CP39" s="20"/>
+      <c r="CQ39" s="20"/>
+      <c r="CR39" s="20"/>
+      <c r="CS39" s="20"/>
+      <c r="CT39" s="20"/>
+      <c r="CU39" s="20"/>
+      <c r="CV39" s="20"/>
     </row>
     <row r="40" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
@@ -4951,91 +4957,91 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-      <c r="R40" s="64" t="s">
+      <c r="R40" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="S40" s="64"/>
-      <c r="T40" s="64"/>
-      <c r="U40" s="64"/>
-      <c r="V40" s="64"/>
-      <c r="W40" s="64"/>
-      <c r="X40" s="64"/>
-      <c r="Y40" s="64"/>
-      <c r="Z40" s="64"/>
-      <c r="AA40" s="64"/>
-      <c r="AB40" s="64"/>
-      <c r="AC40" s="64"/>
-      <c r="AD40" s="64"/>
-      <c r="AE40" s="64"/>
-      <c r="AF40" s="64"/>
-      <c r="AG40" s="64"/>
-      <c r="AH40" s="64"/>
-      <c r="AI40" s="64"/>
-      <c r="AJ40" s="64"/>
-      <c r="AK40" s="64"/>
-      <c r="AL40" s="64"/>
-      <c r="AM40" s="64"/>
-      <c r="AN40" s="64"/>
-      <c r="AO40" s="64"/>
-      <c r="AP40" s="64"/>
-      <c r="AQ40" s="64"/>
-      <c r="AR40" s="64"/>
-      <c r="AS40" s="64"/>
-      <c r="AT40" s="64"/>
-      <c r="AU40" s="64"/>
-      <c r="AV40" s="64"/>
-      <c r="AW40" s="64"/>
-      <c r="AX40" s="64"/>
-      <c r="AY40" s="64"/>
-      <c r="AZ40" s="64"/>
-      <c r="BA40" s="64"/>
-      <c r="BB40" s="64"/>
-      <c r="BC40" s="64"/>
-      <c r="BD40" s="64"/>
-      <c r="BE40" s="64"/>
-      <c r="BF40" s="64"/>
-      <c r="BG40" s="64"/>
-      <c r="BH40" s="64"/>
-      <c r="BI40" s="64"/>
-      <c r="BJ40" s="64"/>
-      <c r="BK40" s="64"/>
-      <c r="BL40" s="64"/>
-      <c r="BM40" s="64"/>
-      <c r="BN40" s="64"/>
-      <c r="BO40" s="64"/>
-      <c r="BP40" s="64"/>
-      <c r="BQ40" s="64"/>
-      <c r="BR40" s="64"/>
-      <c r="BS40" s="64"/>
-      <c r="BT40" s="64"/>
-      <c r="BU40" s="64"/>
-      <c r="BV40" s="64"/>
-      <c r="BW40" s="64"/>
-      <c r="BX40" s="64"/>
-      <c r="BY40" s="64"/>
-      <c r="BZ40" s="64"/>
-      <c r="CA40" s="64"/>
-      <c r="CB40" s="64"/>
-      <c r="CC40" s="64"/>
-      <c r="CD40" s="64"/>
-      <c r="CE40" s="64"/>
-      <c r="CF40" s="64"/>
-      <c r="CG40" s="64"/>
-      <c r="CH40" s="64"/>
-      <c r="CI40" s="64"/>
-      <c r="CJ40" s="64"/>
-      <c r="CK40" s="64"/>
-      <c r="CL40" s="64"/>
-      <c r="CM40" s="64"/>
-      <c r="CN40" s="64"/>
-      <c r="CO40" s="64"/>
-      <c r="CP40" s="64"/>
-      <c r="CQ40" s="64"/>
-      <c r="CR40" s="64"/>
-      <c r="CS40" s="64"/>
-      <c r="CT40" s="64"/>
-      <c r="CU40" s="64"/>
-      <c r="CV40" s="64"/>
+      <c r="S40" s="18"/>
+      <c r="T40" s="18"/>
+      <c r="U40" s="18"/>
+      <c r="V40" s="18"/>
+      <c r="W40" s="18"/>
+      <c r="X40" s="18"/>
+      <c r="Y40" s="18"/>
+      <c r="Z40" s="18"/>
+      <c r="AA40" s="18"/>
+      <c r="AB40" s="18"/>
+      <c r="AC40" s="18"/>
+      <c r="AD40" s="18"/>
+      <c r="AE40" s="18"/>
+      <c r="AF40" s="18"/>
+      <c r="AG40" s="18"/>
+      <c r="AH40" s="18"/>
+      <c r="AI40" s="18"/>
+      <c r="AJ40" s="18"/>
+      <c r="AK40" s="18"/>
+      <c r="AL40" s="18"/>
+      <c r="AM40" s="18"/>
+      <c r="AN40" s="18"/>
+      <c r="AO40" s="18"/>
+      <c r="AP40" s="18"/>
+      <c r="AQ40" s="18"/>
+      <c r="AR40" s="18"/>
+      <c r="AS40" s="18"/>
+      <c r="AT40" s="18"/>
+      <c r="AU40" s="18"/>
+      <c r="AV40" s="18"/>
+      <c r="AW40" s="18"/>
+      <c r="AX40" s="18"/>
+      <c r="AY40" s="18"/>
+      <c r="AZ40" s="18"/>
+      <c r="BA40" s="18"/>
+      <c r="BB40" s="18"/>
+      <c r="BC40" s="18"/>
+      <c r="BD40" s="18"/>
+      <c r="BE40" s="18"/>
+      <c r="BF40" s="18"/>
+      <c r="BG40" s="18"/>
+      <c r="BH40" s="18"/>
+      <c r="BI40" s="18"/>
+      <c r="BJ40" s="18"/>
+      <c r="BK40" s="18"/>
+      <c r="BL40" s="18"/>
+      <c r="BM40" s="18"/>
+      <c r="BN40" s="18"/>
+      <c r="BO40" s="18"/>
+      <c r="BP40" s="18"/>
+      <c r="BQ40" s="18"/>
+      <c r="BR40" s="18"/>
+      <c r="BS40" s="18"/>
+      <c r="BT40" s="18"/>
+      <c r="BU40" s="18"/>
+      <c r="BV40" s="18"/>
+      <c r="BW40" s="18"/>
+      <c r="BX40" s="18"/>
+      <c r="BY40" s="18"/>
+      <c r="BZ40" s="18"/>
+      <c r="CA40" s="18"/>
+      <c r="CB40" s="18"/>
+      <c r="CC40" s="18"/>
+      <c r="CD40" s="18"/>
+      <c r="CE40" s="18"/>
+      <c r="CF40" s="18"/>
+      <c r="CG40" s="18"/>
+      <c r="CH40" s="18"/>
+      <c r="CI40" s="18"/>
+      <c r="CJ40" s="18"/>
+      <c r="CK40" s="18"/>
+      <c r="CL40" s="18"/>
+      <c r="CM40" s="18"/>
+      <c r="CN40" s="18"/>
+      <c r="CO40" s="18"/>
+      <c r="CP40" s="18"/>
+      <c r="CQ40" s="18"/>
+      <c r="CR40" s="18"/>
+      <c r="CS40" s="18"/>
+      <c r="CT40" s="18"/>
+      <c r="CU40" s="18"/>
+      <c r="CV40" s="18"/>
     </row>
     <row r="41" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
@@ -5140,193 +5146,193 @@
       <c r="CV41" s="1"/>
     </row>
     <row r="42" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="53" t="s">
+      <c r="A42" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="53"/>
-      <c r="C42" s="53"/>
-      <c r="D42" s="53"/>
-      <c r="E42" s="53"/>
-      <c r="F42" s="53"/>
-      <c r="G42" s="53"/>
-      <c r="H42" s="53"/>
-      <c r="I42" s="53"/>
-      <c r="J42" s="53"/>
-      <c r="K42" s="53"/>
-      <c r="L42" s="53"/>
-      <c r="M42" s="53"/>
-      <c r="N42" s="53"/>
-      <c r="O42" s="53"/>
-      <c r="P42" s="53"/>
-      <c r="Q42" s="53"/>
-      <c r="R42" s="53"/>
-      <c r="S42" s="53"/>
-      <c r="T42" s="53"/>
+      <c r="B42" s="19"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="19"/>
+      <c r="E42" s="19"/>
+      <c r="F42" s="19"/>
+      <c r="G42" s="19"/>
+      <c r="H42" s="19"/>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19"/>
+      <c r="K42" s="19"/>
+      <c r="L42" s="19"/>
+      <c r="M42" s="19"/>
+      <c r="N42" s="19"/>
+      <c r="O42" s="19"/>
+      <c r="P42" s="19"/>
+      <c r="Q42" s="19"/>
+      <c r="R42" s="19"/>
+      <c r="S42" s="19"/>
+      <c r="T42" s="19"/>
       <c r="U42" s="1"/>
-      <c r="V42" s="54" t="s">
+      <c r="V42" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="W42" s="54"/>
-      <c r="X42" s="54"/>
-      <c r="Y42" s="54"/>
-      <c r="Z42" s="54"/>
-      <c r="AA42" s="54"/>
-      <c r="AB42" s="54"/>
-      <c r="AC42" s="54"/>
-      <c r="AD42" s="54"/>
-      <c r="AE42" s="54"/>
-      <c r="AF42" s="54"/>
-      <c r="AG42" s="54"/>
-      <c r="AH42" s="54"/>
-      <c r="AI42" s="54"/>
-      <c r="AJ42" s="54"/>
-      <c r="AK42" s="54"/>
-      <c r="AL42" s="54"/>
-      <c r="AM42" s="54"/>
-      <c r="AN42" s="54"/>
-      <c r="AO42" s="54"/>
-      <c r="AP42" s="54"/>
-      <c r="AQ42" s="54"/>
-      <c r="AR42" s="54"/>
-      <c r="AS42" s="54"/>
-      <c r="AT42" s="54"/>
-      <c r="AU42" s="54"/>
-      <c r="AV42" s="54"/>
-      <c r="AW42" s="54"/>
-      <c r="AX42" s="54"/>
-      <c r="AY42" s="54"/>
-      <c r="AZ42" s="54"/>
-      <c r="BA42" s="54"/>
-      <c r="BB42" s="54"/>
-      <c r="BC42" s="54"/>
-      <c r="BD42" s="54"/>
-      <c r="BE42" s="54"/>
-      <c r="BF42" s="54"/>
-      <c r="BG42" s="54"/>
-      <c r="BH42" s="54"/>
-      <c r="BI42" s="54"/>
-      <c r="BJ42" s="54"/>
-      <c r="BK42" s="54"/>
-      <c r="BL42" s="54"/>
-      <c r="BM42" s="54"/>
-      <c r="BN42" s="54"/>
-      <c r="BO42" s="54"/>
-      <c r="BP42" s="54"/>
-      <c r="BQ42" s="54"/>
-      <c r="BR42" s="54"/>
-      <c r="BS42" s="54"/>
-      <c r="BT42" s="54"/>
-      <c r="BU42" s="54"/>
-      <c r="BV42" s="54"/>
-      <c r="BW42" s="54"/>
-      <c r="BX42" s="54"/>
-      <c r="BY42" s="54"/>
-      <c r="BZ42" s="54"/>
-      <c r="CA42" s="54"/>
-      <c r="CB42" s="54"/>
-      <c r="CC42" s="54"/>
-      <c r="CD42" s="54"/>
-      <c r="CE42" s="54"/>
-      <c r="CF42" s="54"/>
-      <c r="CG42" s="54"/>
-      <c r="CH42" s="54"/>
-      <c r="CI42" s="54"/>
-      <c r="CJ42" s="54"/>
-      <c r="CK42" s="54"/>
-      <c r="CL42" s="54"/>
-      <c r="CM42" s="54"/>
-      <c r="CN42" s="54"/>
-      <c r="CO42" s="54"/>
-      <c r="CP42" s="54"/>
-      <c r="CQ42" s="54"/>
-      <c r="CR42" s="54"/>
-      <c r="CS42" s="54"/>
-      <c r="CT42" s="54"/>
-      <c r="CU42" s="54"/>
-      <c r="CV42" s="54"/>
+      <c r="W42" s="20"/>
+      <c r="X42" s="20"/>
+      <c r="Y42" s="20"/>
+      <c r="Z42" s="20"/>
+      <c r="AA42" s="20"/>
+      <c r="AB42" s="20"/>
+      <c r="AC42" s="20"/>
+      <c r="AD42" s="20"/>
+      <c r="AE42" s="20"/>
+      <c r="AF42" s="20"/>
+      <c r="AG42" s="20"/>
+      <c r="AH42" s="20"/>
+      <c r="AI42" s="20"/>
+      <c r="AJ42" s="20"/>
+      <c r="AK42" s="20"/>
+      <c r="AL42" s="20"/>
+      <c r="AM42" s="20"/>
+      <c r="AN42" s="20"/>
+      <c r="AO42" s="20"/>
+      <c r="AP42" s="20"/>
+      <c r="AQ42" s="20"/>
+      <c r="AR42" s="20"/>
+      <c r="AS42" s="20"/>
+      <c r="AT42" s="20"/>
+      <c r="AU42" s="20"/>
+      <c r="AV42" s="20"/>
+      <c r="AW42" s="20"/>
+      <c r="AX42" s="20"/>
+      <c r="AY42" s="20"/>
+      <c r="AZ42" s="20"/>
+      <c r="BA42" s="20"/>
+      <c r="BB42" s="20"/>
+      <c r="BC42" s="20"/>
+      <c r="BD42" s="20"/>
+      <c r="BE42" s="20"/>
+      <c r="BF42" s="20"/>
+      <c r="BG42" s="20"/>
+      <c r="BH42" s="20"/>
+      <c r="BI42" s="20"/>
+      <c r="BJ42" s="20"/>
+      <c r="BK42" s="20"/>
+      <c r="BL42" s="20"/>
+      <c r="BM42" s="20"/>
+      <c r="BN42" s="20"/>
+      <c r="BO42" s="20"/>
+      <c r="BP42" s="20"/>
+      <c r="BQ42" s="20"/>
+      <c r="BR42" s="20"/>
+      <c r="BS42" s="20"/>
+      <c r="BT42" s="20"/>
+      <c r="BU42" s="20"/>
+      <c r="BV42" s="20"/>
+      <c r="BW42" s="20"/>
+      <c r="BX42" s="20"/>
+      <c r="BY42" s="20"/>
+      <c r="BZ42" s="20"/>
+      <c r="CA42" s="20"/>
+      <c r="CB42" s="20"/>
+      <c r="CC42" s="20"/>
+      <c r="CD42" s="20"/>
+      <c r="CE42" s="20"/>
+      <c r="CF42" s="20"/>
+      <c r="CG42" s="20"/>
+      <c r="CH42" s="20"/>
+      <c r="CI42" s="20"/>
+      <c r="CJ42" s="20"/>
+      <c r="CK42" s="20"/>
+      <c r="CL42" s="20"/>
+      <c r="CM42" s="20"/>
+      <c r="CN42" s="20"/>
+      <c r="CO42" s="20"/>
+      <c r="CP42" s="20"/>
+      <c r="CQ42" s="20"/>
+      <c r="CR42" s="20"/>
+      <c r="CS42" s="20"/>
+      <c r="CT42" s="20"/>
+      <c r="CU42" s="20"/>
+      <c r="CV42" s="20"/>
     </row>
     <row r="43" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="V43" s="64" t="s">
+      <c r="V43" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="W43" s="64"/>
-      <c r="X43" s="64"/>
-      <c r="Y43" s="64"/>
-      <c r="Z43" s="64"/>
-      <c r="AA43" s="64"/>
-      <c r="AB43" s="64"/>
-      <c r="AC43" s="64"/>
-      <c r="AD43" s="64"/>
-      <c r="AE43" s="64"/>
-      <c r="AF43" s="64"/>
-      <c r="AG43" s="64"/>
-      <c r="AH43" s="64"/>
-      <c r="AI43" s="64"/>
-      <c r="AJ43" s="64"/>
-      <c r="AK43" s="64"/>
-      <c r="AL43" s="64"/>
-      <c r="AM43" s="64"/>
-      <c r="AN43" s="64"/>
-      <c r="AO43" s="64"/>
-      <c r="AP43" s="64"/>
-      <c r="AQ43" s="64"/>
-      <c r="AR43" s="64"/>
-      <c r="AS43" s="64"/>
-      <c r="AT43" s="64"/>
-      <c r="AU43" s="64"/>
-      <c r="AV43" s="64"/>
-      <c r="AW43" s="64"/>
-      <c r="AX43" s="64"/>
-      <c r="AY43" s="64"/>
-      <c r="AZ43" s="64"/>
-      <c r="BA43" s="64"/>
-      <c r="BB43" s="64"/>
-      <c r="BC43" s="64"/>
-      <c r="BD43" s="64"/>
-      <c r="BE43" s="64"/>
-      <c r="BF43" s="64"/>
-      <c r="BG43" s="64"/>
-      <c r="BH43" s="64"/>
-      <c r="BI43" s="64"/>
-      <c r="BJ43" s="64"/>
-      <c r="BK43" s="64"/>
-      <c r="BL43" s="64"/>
-      <c r="BM43" s="64"/>
-      <c r="BN43" s="64"/>
-      <c r="BO43" s="64"/>
-      <c r="BP43" s="64"/>
-      <c r="BQ43" s="64"/>
-      <c r="BR43" s="64"/>
-      <c r="BS43" s="64"/>
-      <c r="BT43" s="64"/>
-      <c r="BU43" s="64"/>
-      <c r="BV43" s="64"/>
-      <c r="BW43" s="64"/>
-      <c r="BX43" s="64"/>
-      <c r="BY43" s="64"/>
-      <c r="BZ43" s="64"/>
-      <c r="CA43" s="64"/>
-      <c r="CB43" s="64"/>
-      <c r="CC43" s="64"/>
-      <c r="CD43" s="64"/>
-      <c r="CE43" s="64"/>
-      <c r="CF43" s="64"/>
-      <c r="CG43" s="64"/>
-      <c r="CH43" s="64"/>
-      <c r="CI43" s="64"/>
-      <c r="CJ43" s="64"/>
-      <c r="CK43" s="64"/>
-      <c r="CL43" s="64"/>
-      <c r="CM43" s="64"/>
-      <c r="CN43" s="64"/>
-      <c r="CO43" s="64"/>
-      <c r="CP43" s="64"/>
-      <c r="CQ43" s="64"/>
-      <c r="CR43" s="64"/>
-      <c r="CS43" s="64"/>
-      <c r="CT43" s="64"/>
-      <c r="CU43" s="64"/>
-      <c r="CV43" s="64"/>
+      <c r="W43" s="18"/>
+      <c r="X43" s="18"/>
+      <c r="Y43" s="18"/>
+      <c r="Z43" s="18"/>
+      <c r="AA43" s="18"/>
+      <c r="AB43" s="18"/>
+      <c r="AC43" s="18"/>
+      <c r="AD43" s="18"/>
+      <c r="AE43" s="18"/>
+      <c r="AF43" s="18"/>
+      <c r="AG43" s="18"/>
+      <c r="AH43" s="18"/>
+      <c r="AI43" s="18"/>
+      <c r="AJ43" s="18"/>
+      <c r="AK43" s="18"/>
+      <c r="AL43" s="18"/>
+      <c r="AM43" s="18"/>
+      <c r="AN43" s="18"/>
+      <c r="AO43" s="18"/>
+      <c r="AP43" s="18"/>
+      <c r="AQ43" s="18"/>
+      <c r="AR43" s="18"/>
+      <c r="AS43" s="18"/>
+      <c r="AT43" s="18"/>
+      <c r="AU43" s="18"/>
+      <c r="AV43" s="18"/>
+      <c r="AW43" s="18"/>
+      <c r="AX43" s="18"/>
+      <c r="AY43" s="18"/>
+      <c r="AZ43" s="18"/>
+      <c r="BA43" s="18"/>
+      <c r="BB43" s="18"/>
+      <c r="BC43" s="18"/>
+      <c r="BD43" s="18"/>
+      <c r="BE43" s="18"/>
+      <c r="BF43" s="18"/>
+      <c r="BG43" s="18"/>
+      <c r="BH43" s="18"/>
+      <c r="BI43" s="18"/>
+      <c r="BJ43" s="18"/>
+      <c r="BK43" s="18"/>
+      <c r="BL43" s="18"/>
+      <c r="BM43" s="18"/>
+      <c r="BN43" s="18"/>
+      <c r="BO43" s="18"/>
+      <c r="BP43" s="18"/>
+      <c r="BQ43" s="18"/>
+      <c r="BR43" s="18"/>
+      <c r="BS43" s="18"/>
+      <c r="BT43" s="18"/>
+      <c r="BU43" s="18"/>
+      <c r="BV43" s="18"/>
+      <c r="BW43" s="18"/>
+      <c r="BX43" s="18"/>
+      <c r="BY43" s="18"/>
+      <c r="BZ43" s="18"/>
+      <c r="CA43" s="18"/>
+      <c r="CB43" s="18"/>
+      <c r="CC43" s="18"/>
+      <c r="CD43" s="18"/>
+      <c r="CE43" s="18"/>
+      <c r="CF43" s="18"/>
+      <c r="CG43" s="18"/>
+      <c r="CH43" s="18"/>
+      <c r="CI43" s="18"/>
+      <c r="CJ43" s="18"/>
+      <c r="CK43" s="18"/>
+      <c r="CL43" s="18"/>
+      <c r="CM43" s="18"/>
+      <c r="CN43" s="18"/>
+      <c r="CO43" s="18"/>
+      <c r="CP43" s="18"/>
+      <c r="CQ43" s="18"/>
+      <c r="CR43" s="18"/>
+      <c r="CS43" s="18"/>
+      <c r="CT43" s="18"/>
+      <c r="CU43" s="18"/>
+      <c r="CV43" s="18"/>
     </row>
     <row r="44" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="14"/>
@@ -5431,56 +5437,56 @@
       <c r="CV44" s="14"/>
     </row>
     <row r="45" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="53" t="s">
+      <c r="A45" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B45" s="53"/>
-      <c r="C45" s="53"/>
-      <c r="D45" s="53"/>
-      <c r="E45" s="53"/>
-      <c r="F45" s="53"/>
-      <c r="G45" s="53"/>
-      <c r="H45" s="53"/>
-      <c r="I45" s="53"/>
-      <c r="J45" s="53"/>
-      <c r="K45" s="53"/>
-      <c r="L45" s="53"/>
-      <c r="M45" s="53"/>
-      <c r="N45" s="53"/>
-      <c r="O45" s="53"/>
-      <c r="P45" s="53"/>
-      <c r="Q45" s="53"/>
-      <c r="R45" s="53"/>
-      <c r="S45" s="53"/>
-      <c r="T45" s="53"/>
-      <c r="U45" s="53"/>
-      <c r="V45" s="53"/>
-      <c r="X45" s="20"/>
-      <c r="Y45" s="20"/>
-      <c r="Z45" s="20"/>
-      <c r="AA45" s="20"/>
-      <c r="AB45" s="20"/>
-      <c r="AC45" s="20"/>
-      <c r="AD45" s="20"/>
-      <c r="AE45" s="20"/>
-      <c r="AF45" s="20"/>
-      <c r="AG45" s="20"/>
-      <c r="AH45" s="20"/>
-      <c r="AI45" s="20"/>
-      <c r="AJ45" s="20"/>
-      <c r="AK45" s="20"/>
-      <c r="AL45" s="20"/>
-      <c r="AM45" s="20"/>
-      <c r="AN45" s="20"/>
-      <c r="AO45" s="20"/>
-      <c r="AP45" s="20"/>
-      <c r="AQ45" s="20"/>
-      <c r="AR45" s="20"/>
-      <c r="AS45" s="20"/>
-      <c r="AT45" s="20"/>
-      <c r="AU45" s="20"/>
-      <c r="AV45" s="20"/>
-      <c r="AW45" s="20"/>
+      <c r="B45" s="19"/>
+      <c r="C45" s="19"/>
+      <c r="D45" s="19"/>
+      <c r="E45" s="19"/>
+      <c r="F45" s="19"/>
+      <c r="G45" s="19"/>
+      <c r="H45" s="19"/>
+      <c r="I45" s="19"/>
+      <c r="J45" s="19"/>
+      <c r="K45" s="19"/>
+      <c r="L45" s="19"/>
+      <c r="M45" s="19"/>
+      <c r="N45" s="19"/>
+      <c r="O45" s="19"/>
+      <c r="P45" s="19"/>
+      <c r="Q45" s="19"/>
+      <c r="R45" s="19"/>
+      <c r="S45" s="19"/>
+      <c r="T45" s="19"/>
+      <c r="U45" s="19"/>
+      <c r="V45" s="19"/>
+      <c r="X45" s="66"/>
+      <c r="Y45" s="66"/>
+      <c r="Z45" s="66"/>
+      <c r="AA45" s="66"/>
+      <c r="AB45" s="66"/>
+      <c r="AC45" s="66"/>
+      <c r="AD45" s="66"/>
+      <c r="AE45" s="66"/>
+      <c r="AF45" s="66"/>
+      <c r="AG45" s="66"/>
+      <c r="AH45" s="66"/>
+      <c r="AI45" s="66"/>
+      <c r="AJ45" s="66"/>
+      <c r="AK45" s="66"/>
+      <c r="AL45" s="66"/>
+      <c r="AM45" s="66"/>
+      <c r="AN45" s="66"/>
+      <c r="AO45" s="66"/>
+      <c r="AP45" s="66"/>
+      <c r="AQ45" s="66"/>
+      <c r="AR45" s="66"/>
+      <c r="AS45" s="66"/>
+      <c r="AT45" s="66"/>
+      <c r="AU45" s="66"/>
+      <c r="AV45" s="66"/>
+      <c r="AW45" s="66"/>
       <c r="AX45" s="12" t="s">
         <v>12</v>
       </c>
@@ -5512,61 +5518,61 @@
       <c r="BX45" s="7"/>
       <c r="BY45" s="7"/>
       <c r="BZ45" s="7"/>
-      <c r="CA45" s="21" t="s">
+      <c r="CA45" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="CB45" s="21"/>
-      <c r="CC45" s="21"/>
-      <c r="CD45" s="21"/>
-      <c r="CE45" s="21"/>
-      <c r="CF45" s="21"/>
-      <c r="CG45" s="21"/>
-      <c r="CH45" s="21"/>
-      <c r="CI45" s="21"/>
-      <c r="CJ45" s="21"/>
-      <c r="CK45" s="16"/>
-      <c r="CL45" s="16"/>
-      <c r="CM45" s="16"/>
-      <c r="CN45" s="16"/>
-      <c r="CO45" s="16"/>
-      <c r="CP45" s="16"/>
-      <c r="CQ45" s="16"/>
-      <c r="CR45" s="16"/>
-      <c r="CS45" s="16"/>
-      <c r="CT45" s="16"/>
-      <c r="CU45" s="16"/>
-      <c r="CV45" s="16"/>
+      <c r="CB45" s="67"/>
+      <c r="CC45" s="67"/>
+      <c r="CD45" s="67"/>
+      <c r="CE45" s="67"/>
+      <c r="CF45" s="67"/>
+      <c r="CG45" s="67"/>
+      <c r="CH45" s="67"/>
+      <c r="CI45" s="67"/>
+      <c r="CJ45" s="67"/>
+      <c r="CK45" s="63"/>
+      <c r="CL45" s="63"/>
+      <c r="CM45" s="63"/>
+      <c r="CN45" s="63"/>
+      <c r="CO45" s="63"/>
+      <c r="CP45" s="63"/>
+      <c r="CQ45" s="63"/>
+      <c r="CR45" s="63"/>
+      <c r="CS45" s="63"/>
+      <c r="CT45" s="63"/>
+      <c r="CU45" s="63"/>
+      <c r="CV45" s="63"/>
     </row>
     <row r="46" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="W46" s="18" t="s">
+      <c r="W46" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="X46" s="18"/>
-      <c r="Y46" s="18"/>
-      <c r="Z46" s="18"/>
-      <c r="AA46" s="18"/>
-      <c r="AB46" s="18"/>
-      <c r="AC46" s="18"/>
-      <c r="AD46" s="18"/>
-      <c r="AE46" s="18"/>
-      <c r="AF46" s="18"/>
-      <c r="AG46" s="18"/>
-      <c r="AH46" s="18"/>
-      <c r="AI46" s="18"/>
-      <c r="AJ46" s="18"/>
-      <c r="AK46" s="18"/>
-      <c r="AL46" s="18"/>
-      <c r="AM46" s="18"/>
-      <c r="AN46" s="18"/>
-      <c r="AO46" s="18"/>
-      <c r="AP46" s="18"/>
-      <c r="AQ46" s="18"/>
-      <c r="AR46" s="18"/>
-      <c r="AS46" s="18"/>
-      <c r="AT46" s="18"/>
-      <c r="AU46" s="18"/>
-      <c r="AV46" s="18"/>
-      <c r="AW46" s="18"/>
+      <c r="X46" s="64"/>
+      <c r="Y46" s="64"/>
+      <c r="Z46" s="64"/>
+      <c r="AA46" s="64"/>
+      <c r="AB46" s="64"/>
+      <c r="AC46" s="64"/>
+      <c r="AD46" s="64"/>
+      <c r="AE46" s="64"/>
+      <c r="AF46" s="64"/>
+      <c r="AG46" s="64"/>
+      <c r="AH46" s="64"/>
+      <c r="AI46" s="64"/>
+      <c r="AJ46" s="64"/>
+      <c r="AK46" s="64"/>
+      <c r="AL46" s="64"/>
+      <c r="AM46" s="64"/>
+      <c r="AN46" s="64"/>
+      <c r="AO46" s="64"/>
+      <c r="AP46" s="64"/>
+      <c r="AQ46" s="64"/>
+      <c r="AR46" s="64"/>
+      <c r="AS46" s="64"/>
+      <c r="AT46" s="64"/>
+      <c r="AU46" s="64"/>
+      <c r="AV46" s="64"/>
+      <c r="AW46" s="64"/>
       <c r="AX46" s="5"/>
       <c r="AY46" s="5"/>
       <c r="AZ46" s="5"/>
@@ -5584,20 +5590,20 @@
       <c r="BL46" s="5"/>
       <c r="BM46" s="5"/>
       <c r="BN46" s="5"/>
-      <c r="BO46" s="17" t="s">
+      <c r="BO46" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="BP46" s="17"/>
-      <c r="BQ46" s="17"/>
-      <c r="BR46" s="17"/>
-      <c r="BS46" s="17"/>
-      <c r="BT46" s="17"/>
-      <c r="BU46" s="17"/>
-      <c r="BV46" s="17"/>
-      <c r="BW46" s="17"/>
-      <c r="BX46" s="17"/>
-      <c r="BY46" s="17"/>
-      <c r="BZ46" s="17"/>
+      <c r="BP46" s="16"/>
+      <c r="BQ46" s="16"/>
+      <c r="BR46" s="16"/>
+      <c r="BS46" s="16"/>
+      <c r="BT46" s="16"/>
+      <c r="BU46" s="16"/>
+      <c r="BV46" s="16"/>
+      <c r="BW46" s="16"/>
+      <c r="BX46" s="16"/>
+      <c r="BY46" s="16"/>
+      <c r="BZ46" s="16"/>
       <c r="CA46" s="5"/>
       <c r="CB46" s="5"/>
       <c r="CC46" s="5"/>
@@ -5608,54 +5614,54 @@
       <c r="CH46" s="5"/>
       <c r="CI46" s="5"/>
       <c r="CJ46" s="5"/>
-      <c r="CK46" s="17" t="s">
+      <c r="CK46" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="CL46" s="17"/>
-      <c r="CM46" s="17"/>
-      <c r="CN46" s="17"/>
-      <c r="CO46" s="17"/>
-      <c r="CP46" s="17"/>
-      <c r="CQ46" s="17"/>
-      <c r="CR46" s="17"/>
-      <c r="CS46" s="17"/>
-      <c r="CT46" s="17"/>
-      <c r="CU46" s="17"/>
-      <c r="CV46" s="17"/>
+      <c r="CL46" s="16"/>
+      <c r="CM46" s="16"/>
+      <c r="CN46" s="16"/>
+      <c r="CO46" s="16"/>
+      <c r="CP46" s="16"/>
+      <c r="CQ46" s="16"/>
+      <c r="CR46" s="16"/>
+      <c r="CS46" s="16"/>
+      <c r="CT46" s="16"/>
+      <c r="CU46" s="16"/>
+      <c r="CV46" s="16"/>
       <c r="CW46" s="14"/>
       <c r="CX46" s="14"/>
       <c r="CY46" s="14"/>
     </row>
     <row r="47" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="W47" s="18" t="s">
+      <c r="W47" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="X47" s="18"/>
-      <c r="Y47" s="18"/>
-      <c r="Z47" s="18"/>
-      <c r="AA47" s="18"/>
-      <c r="AB47" s="18"/>
-      <c r="AC47" s="18"/>
-      <c r="AD47" s="18"/>
-      <c r="AE47" s="18"/>
-      <c r="AF47" s="18"/>
-      <c r="AG47" s="18"/>
-      <c r="AH47" s="18"/>
-      <c r="AI47" s="18"/>
-      <c r="AJ47" s="18"/>
-      <c r="AK47" s="18"/>
-      <c r="AL47" s="18"/>
-      <c r="AM47" s="18"/>
-      <c r="AN47" s="18"/>
-      <c r="AO47" s="18"/>
-      <c r="AP47" s="18"/>
-      <c r="AQ47" s="18"/>
-      <c r="AR47" s="18"/>
-      <c r="AS47" s="18"/>
-      <c r="AT47" s="18"/>
-      <c r="AU47" s="18"/>
-      <c r="AV47" s="18"/>
-      <c r="AW47" s="18"/>
+      <c r="X47" s="64"/>
+      <c r="Y47" s="64"/>
+      <c r="Z47" s="64"/>
+      <c r="AA47" s="64"/>
+      <c r="AB47" s="64"/>
+      <c r="AC47" s="64"/>
+      <c r="AD47" s="64"/>
+      <c r="AE47" s="64"/>
+      <c r="AF47" s="64"/>
+      <c r="AG47" s="64"/>
+      <c r="AH47" s="64"/>
+      <c r="AI47" s="64"/>
+      <c r="AJ47" s="64"/>
+      <c r="AK47" s="64"/>
+      <c r="AL47" s="64"/>
+      <c r="AM47" s="64"/>
+      <c r="AN47" s="64"/>
+      <c r="AO47" s="64"/>
+      <c r="AP47" s="64"/>
+      <c r="AQ47" s="64"/>
+      <c r="AR47" s="64"/>
+      <c r="AS47" s="64"/>
+      <c r="AT47" s="64"/>
+      <c r="AU47" s="64"/>
+      <c r="AV47" s="64"/>
+      <c r="AW47" s="64"/>
       <c r="AX47" s="5"/>
       <c r="AY47" s="5"/>
       <c r="AZ47" s="5"/>
@@ -5695,204 +5701,204 @@
       <c r="CH47" s="5"/>
       <c r="CI47" s="5"/>
       <c r="CJ47" s="5"/>
-      <c r="CK47" s="19" t="s">
+      <c r="CK47" s="65" t="s">
         <v>38</v>
       </c>
-      <c r="CL47" s="19"/>
-      <c r="CM47" s="19"/>
-      <c r="CN47" s="19"/>
-      <c r="CO47" s="19"/>
-      <c r="CP47" s="19"/>
-      <c r="CQ47" s="19"/>
-      <c r="CR47" s="19"/>
-      <c r="CS47" s="19"/>
-      <c r="CT47" s="19"/>
-      <c r="CU47" s="19"/>
-      <c r="CV47" s="19"/>
+      <c r="CL47" s="65"/>
+      <c r="CM47" s="65"/>
+      <c r="CN47" s="65"/>
+      <c r="CO47" s="65"/>
+      <c r="CP47" s="65"/>
+      <c r="CQ47" s="65"/>
+      <c r="CR47" s="65"/>
+      <c r="CS47" s="65"/>
+      <c r="CT47" s="65"/>
+      <c r="CU47" s="65"/>
+      <c r="CV47" s="65"/>
     </row>
     <row r="49" spans="1:100" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="53" t="s">
+      <c r="A49" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="53"/>
-      <c r="C49" s="53"/>
-      <c r="D49" s="53"/>
-      <c r="E49" s="53"/>
-      <c r="F49" s="53"/>
-      <c r="G49" s="53"/>
-      <c r="H49" s="53"/>
-      <c r="I49" s="53"/>
-      <c r="J49" s="53"/>
-      <c r="K49" s="53"/>
-      <c r="L49" s="53"/>
-      <c r="M49" s="53"/>
-      <c r="N49" s="53"/>
-      <c r="O49" s="53"/>
-      <c r="P49" s="53"/>
-      <c r="Q49" s="53"/>
-      <c r="R49" s="53"/>
-      <c r="S49" s="53"/>
-      <c r="T49" s="53"/>
-      <c r="U49" s="53"/>
-      <c r="V49" s="53"/>
-      <c r="X49" s="54"/>
-      <c r="Y49" s="54"/>
-      <c r="Z49" s="54"/>
-      <c r="AA49" s="54"/>
-      <c r="AB49" s="54"/>
-      <c r="AC49" s="54"/>
-      <c r="AD49" s="54"/>
-      <c r="AE49" s="54"/>
-      <c r="AF49" s="54"/>
-      <c r="AG49" s="54"/>
-      <c r="AH49" s="54"/>
-      <c r="AI49" s="54"/>
-      <c r="AJ49" s="54"/>
-      <c r="AK49" s="54"/>
-      <c r="AL49" s="54"/>
-      <c r="AM49" s="54"/>
-      <c r="AN49" s="54"/>
-      <c r="AO49" s="54"/>
-      <c r="AP49" s="54"/>
-      <c r="AQ49" s="54"/>
-      <c r="AR49" s="54"/>
-      <c r="AS49" s="54"/>
-      <c r="AT49" s="54"/>
-      <c r="AU49" s="54"/>
-      <c r="AV49" s="54"/>
-      <c r="AW49" s="54"/>
-      <c r="AX49" s="54"/>
-      <c r="AY49" s="54"/>
-      <c r="AZ49" s="54"/>
-      <c r="BA49" s="54"/>
-      <c r="BB49" s="54"/>
-      <c r="BC49" s="54"/>
-      <c r="BD49" s="54"/>
-      <c r="BE49" s="54"/>
-      <c r="BF49" s="54"/>
-      <c r="BG49" s="54"/>
-      <c r="BH49" s="54"/>
-      <c r="BI49" s="54"/>
-      <c r="BJ49" s="54"/>
-      <c r="BK49" s="54"/>
-      <c r="BL49" s="54"/>
-      <c r="BM49" s="54"/>
-      <c r="BN49" s="54"/>
-      <c r="BO49" s="54"/>
-      <c r="BP49" s="54"/>
-      <c r="BQ49" s="54"/>
-      <c r="BR49" s="54"/>
-      <c r="BS49" s="54"/>
-      <c r="BT49" s="54"/>
-      <c r="BU49" s="54"/>
-      <c r="BV49" s="54"/>
-      <c r="BW49" s="54"/>
-      <c r="BX49" s="54"/>
-      <c r="BY49" s="54"/>
-      <c r="BZ49" s="54"/>
-      <c r="CA49" s="54"/>
-      <c r="CB49" s="54"/>
-      <c r="CC49" s="54"/>
-      <c r="CD49" s="54"/>
-      <c r="CE49" s="54"/>
-      <c r="CF49" s="54"/>
-      <c r="CG49" s="54"/>
-      <c r="CH49" s="54"/>
-      <c r="CI49" s="54"/>
-      <c r="CJ49" s="54"/>
-      <c r="CK49" s="54"/>
-      <c r="CL49" s="54"/>
-      <c r="CM49" s="54"/>
-      <c r="CN49" s="54"/>
-      <c r="CO49" s="54"/>
-      <c r="CP49" s="54"/>
-      <c r="CQ49" s="54"/>
-      <c r="CR49" s="54"/>
-      <c r="CS49" s="54"/>
-      <c r="CT49" s="54"/>
-      <c r="CU49" s="54"/>
-      <c r="CV49" s="54"/>
+      <c r="B49" s="19"/>
+      <c r="C49" s="19"/>
+      <c r="D49" s="19"/>
+      <c r="E49" s="19"/>
+      <c r="F49" s="19"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="19"/>
+      <c r="M49" s="19"/>
+      <c r="N49" s="19"/>
+      <c r="O49" s="19"/>
+      <c r="P49" s="19"/>
+      <c r="Q49" s="19"/>
+      <c r="R49" s="19"/>
+      <c r="S49" s="19"/>
+      <c r="T49" s="19"/>
+      <c r="U49" s="19"/>
+      <c r="V49" s="19"/>
+      <c r="X49" s="20"/>
+      <c r="Y49" s="20"/>
+      <c r="Z49" s="20"/>
+      <c r="AA49" s="20"/>
+      <c r="AB49" s="20"/>
+      <c r="AC49" s="20"/>
+      <c r="AD49" s="20"/>
+      <c r="AE49" s="20"/>
+      <c r="AF49" s="20"/>
+      <c r="AG49" s="20"/>
+      <c r="AH49" s="20"/>
+      <c r="AI49" s="20"/>
+      <c r="AJ49" s="20"/>
+      <c r="AK49" s="20"/>
+      <c r="AL49" s="20"/>
+      <c r="AM49" s="20"/>
+      <c r="AN49" s="20"/>
+      <c r="AO49" s="20"/>
+      <c r="AP49" s="20"/>
+      <c r="AQ49" s="20"/>
+      <c r="AR49" s="20"/>
+      <c r="AS49" s="20"/>
+      <c r="AT49" s="20"/>
+      <c r="AU49" s="20"/>
+      <c r="AV49" s="20"/>
+      <c r="AW49" s="20"/>
+      <c r="AX49" s="20"/>
+      <c r="AY49" s="20"/>
+      <c r="AZ49" s="20"/>
+      <c r="BA49" s="20"/>
+      <c r="BB49" s="20"/>
+      <c r="BC49" s="20"/>
+      <c r="BD49" s="20"/>
+      <c r="BE49" s="20"/>
+      <c r="BF49" s="20"/>
+      <c r="BG49" s="20"/>
+      <c r="BH49" s="20"/>
+      <c r="BI49" s="20"/>
+      <c r="BJ49" s="20"/>
+      <c r="BK49" s="20"/>
+      <c r="BL49" s="20"/>
+      <c r="BM49" s="20"/>
+      <c r="BN49" s="20"/>
+      <c r="BO49" s="20"/>
+      <c r="BP49" s="20"/>
+      <c r="BQ49" s="20"/>
+      <c r="BR49" s="20"/>
+      <c r="BS49" s="20"/>
+      <c r="BT49" s="20"/>
+      <c r="BU49" s="20"/>
+      <c r="BV49" s="20"/>
+      <c r="BW49" s="20"/>
+      <c r="BX49" s="20"/>
+      <c r="BY49" s="20"/>
+      <c r="BZ49" s="20"/>
+      <c r="CA49" s="20"/>
+      <c r="CB49" s="20"/>
+      <c r="CC49" s="20"/>
+      <c r="CD49" s="20"/>
+      <c r="CE49" s="20"/>
+      <c r="CF49" s="20"/>
+      <c r="CG49" s="20"/>
+      <c r="CH49" s="20"/>
+      <c r="CI49" s="20"/>
+      <c r="CJ49" s="20"/>
+      <c r="CK49" s="20"/>
+      <c r="CL49" s="20"/>
+      <c r="CM49" s="20"/>
+      <c r="CN49" s="20"/>
+      <c r="CO49" s="20"/>
+      <c r="CP49" s="20"/>
+      <c r="CQ49" s="20"/>
+      <c r="CR49" s="20"/>
+      <c r="CS49" s="20"/>
+      <c r="CT49" s="20"/>
+      <c r="CU49" s="20"/>
+      <c r="CV49" s="20"/>
     </row>
     <row r="50" spans="1:100" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="X50" s="64" t="s">
+      <c r="X50" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="Y50" s="64"/>
-      <c r="Z50" s="64"/>
-      <c r="AA50" s="64"/>
-      <c r="AB50" s="64"/>
-      <c r="AC50" s="64"/>
-      <c r="AD50" s="64"/>
-      <c r="AE50" s="64"/>
-      <c r="AF50" s="64"/>
-      <c r="AG50" s="64"/>
-      <c r="AH50" s="64"/>
-      <c r="AI50" s="64"/>
-      <c r="AJ50" s="64"/>
-      <c r="AK50" s="64"/>
-      <c r="AL50" s="64"/>
-      <c r="AM50" s="64"/>
-      <c r="AN50" s="64"/>
-      <c r="AO50" s="64"/>
-      <c r="AP50" s="64"/>
-      <c r="AQ50" s="64"/>
-      <c r="AR50" s="64"/>
-      <c r="AS50" s="64"/>
-      <c r="AT50" s="64"/>
-      <c r="AU50" s="64"/>
-      <c r="AV50" s="64"/>
-      <c r="AW50" s="64"/>
-      <c r="AX50" s="64"/>
-      <c r="AY50" s="64"/>
-      <c r="AZ50" s="64"/>
-      <c r="BA50" s="64"/>
-      <c r="BB50" s="64"/>
-      <c r="BC50" s="64"/>
-      <c r="BD50" s="64"/>
-      <c r="BE50" s="64"/>
-      <c r="BF50" s="64"/>
-      <c r="BG50" s="64"/>
-      <c r="BH50" s="64"/>
-      <c r="BI50" s="64"/>
-      <c r="BJ50" s="64"/>
-      <c r="BK50" s="64"/>
-      <c r="BL50" s="64"/>
-      <c r="BM50" s="64"/>
-      <c r="BN50" s="64"/>
-      <c r="BO50" s="64"/>
-      <c r="BP50" s="64"/>
-      <c r="BQ50" s="64"/>
-      <c r="BR50" s="64"/>
-      <c r="BS50" s="64"/>
-      <c r="BT50" s="64"/>
-      <c r="BU50" s="64"/>
-      <c r="BV50" s="64"/>
-      <c r="BW50" s="64"/>
-      <c r="BX50" s="64"/>
-      <c r="BY50" s="64"/>
-      <c r="BZ50" s="64"/>
-      <c r="CA50" s="64"/>
-      <c r="CB50" s="64"/>
-      <c r="CC50" s="64"/>
-      <c r="CD50" s="64"/>
-      <c r="CE50" s="64"/>
-      <c r="CF50" s="64"/>
-      <c r="CG50" s="64"/>
-      <c r="CH50" s="64"/>
-      <c r="CI50" s="64"/>
-      <c r="CJ50" s="64"/>
-      <c r="CK50" s="64"/>
-      <c r="CL50" s="64"/>
-      <c r="CM50" s="64"/>
-      <c r="CN50" s="64"/>
-      <c r="CO50" s="64"/>
-      <c r="CP50" s="64"/>
-      <c r="CQ50" s="64"/>
-      <c r="CR50" s="64"/>
-      <c r="CS50" s="64"/>
-      <c r="CT50" s="64"/>
-      <c r="CU50" s="64"/>
-      <c r="CV50" s="64"/>
+      <c r="Y50" s="18"/>
+      <c r="Z50" s="18"/>
+      <c r="AA50" s="18"/>
+      <c r="AB50" s="18"/>
+      <c r="AC50" s="18"/>
+      <c r="AD50" s="18"/>
+      <c r="AE50" s="18"/>
+      <c r="AF50" s="18"/>
+      <c r="AG50" s="18"/>
+      <c r="AH50" s="18"/>
+      <c r="AI50" s="18"/>
+      <c r="AJ50" s="18"/>
+      <c r="AK50" s="18"/>
+      <c r="AL50" s="18"/>
+      <c r="AM50" s="18"/>
+      <c r="AN50" s="18"/>
+      <c r="AO50" s="18"/>
+      <c r="AP50" s="18"/>
+      <c r="AQ50" s="18"/>
+      <c r="AR50" s="18"/>
+      <c r="AS50" s="18"/>
+      <c r="AT50" s="18"/>
+      <c r="AU50" s="18"/>
+      <c r="AV50" s="18"/>
+      <c r="AW50" s="18"/>
+      <c r="AX50" s="18"/>
+      <c r="AY50" s="18"/>
+      <c r="AZ50" s="18"/>
+      <c r="BA50" s="18"/>
+      <c r="BB50" s="18"/>
+      <c r="BC50" s="18"/>
+      <c r="BD50" s="18"/>
+      <c r="BE50" s="18"/>
+      <c r="BF50" s="18"/>
+      <c r="BG50" s="18"/>
+      <c r="BH50" s="18"/>
+      <c r="BI50" s="18"/>
+      <c r="BJ50" s="18"/>
+      <c r="BK50" s="18"/>
+      <c r="BL50" s="18"/>
+      <c r="BM50" s="18"/>
+      <c r="BN50" s="18"/>
+      <c r="BO50" s="18"/>
+      <c r="BP50" s="18"/>
+      <c r="BQ50" s="18"/>
+      <c r="BR50" s="18"/>
+      <c r="BS50" s="18"/>
+      <c r="BT50" s="18"/>
+      <c r="BU50" s="18"/>
+      <c r="BV50" s="18"/>
+      <c r="BW50" s="18"/>
+      <c r="BX50" s="18"/>
+      <c r="BY50" s="18"/>
+      <c r="BZ50" s="18"/>
+      <c r="CA50" s="18"/>
+      <c r="CB50" s="18"/>
+      <c r="CC50" s="18"/>
+      <c r="CD50" s="18"/>
+      <c r="CE50" s="18"/>
+      <c r="CF50" s="18"/>
+      <c r="CG50" s="18"/>
+      <c r="CH50" s="18"/>
+      <c r="CI50" s="18"/>
+      <c r="CJ50" s="18"/>
+      <c r="CK50" s="18"/>
+      <c r="CL50" s="18"/>
+      <c r="CM50" s="18"/>
+      <c r="CN50" s="18"/>
+      <c r="CO50" s="18"/>
+      <c r="CP50" s="18"/>
+      <c r="CQ50" s="18"/>
+      <c r="CR50" s="18"/>
+      <c r="CS50" s="18"/>
+      <c r="CT50" s="18"/>
+      <c r="CU50" s="18"/>
+      <c r="CV50" s="18"/>
     </row>
     <row r="51" spans="1:100" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="X51" s="5"/>
@@ -6054,161 +6060,129 @@
     </row>
     <row r="53" spans="1:100" ht="0.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="1:100" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="53" t="s">
+      <c r="A54" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B54" s="53"/>
-      <c r="C54" s="53"/>
-      <c r="D54" s="53"/>
-      <c r="E54" s="53"/>
-      <c r="F54" s="53"/>
-      <c r="G54" s="53"/>
-      <c r="H54" s="53"/>
-      <c r="I54" s="53"/>
-      <c r="J54" s="53"/>
-      <c r="K54" s="53"/>
-      <c r="L54" s="53"/>
-      <c r="M54" s="53"/>
-      <c r="N54" s="53"/>
-      <c r="O54" s="53"/>
-      <c r="P54" s="53"/>
-      <c r="Q54" s="53"/>
-      <c r="R54" s="53"/>
-      <c r="S54" s="53"/>
-      <c r="T54" s="53"/>
-      <c r="U54" s="53"/>
-      <c r="V54" s="53"/>
-      <c r="W54" s="53"/>
-      <c r="X54" s="53"/>
-      <c r="Y54" s="53"/>
-      <c r="Z54" s="53"/>
-      <c r="AA54" s="53"/>
-      <c r="AB54" s="53"/>
-      <c r="AC54" s="53"/>
-      <c r="AE54" s="54"/>
-      <c r="AF54" s="54"/>
-      <c r="AG54" s="54"/>
-      <c r="AH54" s="54"/>
-      <c r="AI54" s="54"/>
-      <c r="AJ54" s="54"/>
-      <c r="AK54" s="54"/>
-      <c r="AL54" s="54"/>
-      <c r="AM54" s="54"/>
-      <c r="AN54" s="54"/>
-      <c r="AO54" s="54"/>
-      <c r="AP54" s="54"/>
-      <c r="AQ54" s="54"/>
-      <c r="AR54" s="54"/>
-      <c r="AS54" s="54"/>
-      <c r="AT54" s="54"/>
-      <c r="AU54" s="54"/>
-      <c r="AV54" s="54"/>
-      <c r="AW54" s="54"/>
-      <c r="AX54" s="54"/>
-      <c r="AY54" s="54"/>
-      <c r="AZ54" s="54"/>
-      <c r="BA54" s="54"/>
-      <c r="BB54" s="54"/>
-      <c r="BC54" s="54"/>
-      <c r="BD54" s="54"/>
-      <c r="BE54" s="54"/>
-      <c r="BF54" s="54"/>
-      <c r="BG54" s="54"/>
-      <c r="BH54" s="54"/>
-      <c r="BI54" s="54"/>
-      <c r="BJ54" s="54"/>
-      <c r="BK54" s="54"/>
-      <c r="BL54" s="54"/>
-      <c r="BM54" s="54"/>
-      <c r="BN54" s="54"/>
-      <c r="BO54" s="54"/>
-      <c r="BP54" s="54"/>
-      <c r="BQ54" s="54"/>
-      <c r="BR54" s="54"/>
-      <c r="BS54" s="54"/>
-      <c r="BT54" s="54"/>
-      <c r="BU54" s="54"/>
-      <c r="BV54" s="54"/>
-      <c r="BW54" s="54"/>
-      <c r="BX54" s="54"/>
-      <c r="BY54" s="54"/>
-      <c r="BZ54" s="54"/>
-      <c r="CA54" s="54"/>
-      <c r="CB54" s="54"/>
-      <c r="CC54" s="54"/>
-      <c r="CD54" s="54"/>
-      <c r="CE54" s="54"/>
-      <c r="CF54" s="54"/>
-      <c r="CG54" s="54"/>
-      <c r="CH54" s="54"/>
-      <c r="CI54" s="54"/>
-      <c r="CJ54" s="54"/>
-      <c r="CK54" s="54"/>
-      <c r="CL54" s="54"/>
-      <c r="CM54" s="54"/>
-      <c r="CN54" s="54"/>
-      <c r="CO54" s="54"/>
-      <c r="CP54" s="54"/>
-      <c r="CQ54" s="54"/>
-      <c r="CR54" s="54"/>
-      <c r="CS54" s="54"/>
-      <c r="CT54" s="54"/>
-      <c r="CU54" s="54"/>
-      <c r="CV54" s="54"/>
+      <c r="B54" s="19"/>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="19"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="19"/>
+      <c r="L54" s="19"/>
+      <c r="M54" s="19"/>
+      <c r="N54" s="19"/>
+      <c r="O54" s="19"/>
+      <c r="P54" s="19"/>
+      <c r="Q54" s="19"/>
+      <c r="R54" s="19"/>
+      <c r="S54" s="19"/>
+      <c r="T54" s="19"/>
+      <c r="U54" s="19"/>
+      <c r="V54" s="19"/>
+      <c r="W54" s="19"/>
+      <c r="X54" s="19"/>
+      <c r="Y54" s="19"/>
+      <c r="Z54" s="19"/>
+      <c r="AA54" s="19"/>
+      <c r="AB54" s="19"/>
+      <c r="AC54" s="19"/>
+      <c r="AE54" s="20"/>
+      <c r="AF54" s="20"/>
+      <c r="AG54" s="20"/>
+      <c r="AH54" s="20"/>
+      <c r="AI54" s="20"/>
+      <c r="AJ54" s="20"/>
+      <c r="AK54" s="20"/>
+      <c r="AL54" s="20"/>
+      <c r="AM54" s="20"/>
+      <c r="AN54" s="20"/>
+      <c r="AO54" s="20"/>
+      <c r="AP54" s="20"/>
+      <c r="AQ54" s="20"/>
+      <c r="AR54" s="20"/>
+      <c r="AS54" s="20"/>
+      <c r="AT54" s="20"/>
+      <c r="AU54" s="20"/>
+      <c r="AV54" s="20"/>
+      <c r="AW54" s="20"/>
+      <c r="AX54" s="20"/>
+      <c r="AY54" s="20"/>
+      <c r="AZ54" s="20"/>
+      <c r="BA54" s="20"/>
+      <c r="BB54" s="20"/>
+      <c r="BC54" s="20"/>
+      <c r="BD54" s="20"/>
+      <c r="BE54" s="20"/>
+      <c r="BF54" s="20"/>
+      <c r="BG54" s="20"/>
+      <c r="BH54" s="20"/>
+      <c r="BI54" s="20"/>
+      <c r="BJ54" s="20"/>
+      <c r="BK54" s="20"/>
+      <c r="BL54" s="20"/>
+      <c r="BM54" s="20"/>
+      <c r="BN54" s="20"/>
+      <c r="BO54" s="20"/>
+      <c r="BP54" s="20"/>
+      <c r="BQ54" s="20"/>
+      <c r="BR54" s="20"/>
+      <c r="BS54" s="20"/>
+      <c r="BT54" s="20"/>
+      <c r="BU54" s="20"/>
+      <c r="BV54" s="20"/>
+      <c r="BW54" s="20"/>
+      <c r="BX54" s="20"/>
+      <c r="BY54" s="20"/>
+      <c r="BZ54" s="20"/>
+      <c r="CA54" s="20"/>
+      <c r="CB54" s="20"/>
+      <c r="CC54" s="20"/>
+      <c r="CD54" s="20"/>
+      <c r="CE54" s="20"/>
+      <c r="CF54" s="20"/>
+      <c r="CG54" s="20"/>
+      <c r="CH54" s="20"/>
+      <c r="CI54" s="20"/>
+      <c r="CJ54" s="20"/>
+      <c r="CK54" s="20"/>
+      <c r="CL54" s="20"/>
+      <c r="CM54" s="20"/>
+      <c r="CN54" s="20"/>
+      <c r="CO54" s="20"/>
+      <c r="CP54" s="20"/>
+      <c r="CQ54" s="20"/>
+      <c r="CR54" s="20"/>
+      <c r="CS54" s="20"/>
+      <c r="CT54" s="20"/>
+      <c r="CU54" s="20"/>
+      <c r="CV54" s="20"/>
     </row>
     <row r="55" spans="1:100" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:100" ht="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="88">
-    <mergeCell ref="S34:BP34"/>
-    <mergeCell ref="BX36:CP36"/>
-    <mergeCell ref="BX37:CP37"/>
-    <mergeCell ref="W36:BP36"/>
-    <mergeCell ref="W37:BP37"/>
-    <mergeCell ref="V43:CV43"/>
-    <mergeCell ref="X50:CV50"/>
-    <mergeCell ref="A54:AC54"/>
-    <mergeCell ref="AE54:CV54"/>
-    <mergeCell ref="A49:V49"/>
-    <mergeCell ref="X49:CV49"/>
-    <mergeCell ref="A45:V45"/>
-    <mergeCell ref="AF16:AG16"/>
-    <mergeCell ref="AI16:BD16"/>
-    <mergeCell ref="A39:P39"/>
-    <mergeCell ref="R39:CV39"/>
-    <mergeCell ref="R40:CV40"/>
-    <mergeCell ref="T25:CV25"/>
-    <mergeCell ref="A32:CV32"/>
-    <mergeCell ref="BM16:BO16"/>
-    <mergeCell ref="BF16:BH16"/>
-    <mergeCell ref="BX33:CP33"/>
-    <mergeCell ref="S33:BP33"/>
-    <mergeCell ref="A33:Q33"/>
-    <mergeCell ref="V42:CV42"/>
-    <mergeCell ref="A42:T42"/>
-    <mergeCell ref="BX34:CP34"/>
-    <mergeCell ref="AZ30:BJ30"/>
-    <mergeCell ref="BT30:CB30"/>
-    <mergeCell ref="CC30:CM30"/>
-    <mergeCell ref="A30:V30"/>
-    <mergeCell ref="W30:AF30"/>
-    <mergeCell ref="A18:P18"/>
-    <mergeCell ref="R18:CV18"/>
-    <mergeCell ref="CC28:CM28"/>
-    <mergeCell ref="BK29:BS29"/>
-    <mergeCell ref="BT29:CB29"/>
-    <mergeCell ref="CC29:CM29"/>
-    <mergeCell ref="A21:P21"/>
-    <mergeCell ref="R19:CV19"/>
-    <mergeCell ref="A27:CV27"/>
-    <mergeCell ref="AZ28:BJ28"/>
-    <mergeCell ref="A24:Q24"/>
-    <mergeCell ref="A29:V29"/>
-    <mergeCell ref="W29:AF29"/>
-    <mergeCell ref="AG29:AO29"/>
-    <mergeCell ref="AP29:AY29"/>
-    <mergeCell ref="AZ29:BJ29"/>
+    <mergeCell ref="Z2:AR4"/>
+    <mergeCell ref="Z5:AR6"/>
+    <mergeCell ref="AS2:BL4"/>
+    <mergeCell ref="AS5:BL6"/>
+    <mergeCell ref="CN31:CV31"/>
+    <mergeCell ref="AG28:AO28"/>
+    <mergeCell ref="AP28:AY28"/>
+    <mergeCell ref="CN30:CV30"/>
+    <mergeCell ref="T24:CV24"/>
+    <mergeCell ref="CN29:CV29"/>
+    <mergeCell ref="BK30:BS30"/>
+    <mergeCell ref="BI16:BK16"/>
+    <mergeCell ref="Z16:AA16"/>
+    <mergeCell ref="AB16:AE16"/>
+    <mergeCell ref="R21:CV21"/>
+    <mergeCell ref="R22:CV22"/>
     <mergeCell ref="T5:X6"/>
     <mergeCell ref="AZ31:BJ31"/>
     <mergeCell ref="BK31:BS31"/>
@@ -6225,22 +6199,49 @@
     <mergeCell ref="AP30:AY30"/>
     <mergeCell ref="A28:V28"/>
     <mergeCell ref="W28:AF28"/>
-    <mergeCell ref="Z2:AR4"/>
-    <mergeCell ref="Z5:AR6"/>
-    <mergeCell ref="AS2:BL4"/>
-    <mergeCell ref="AS5:BL6"/>
-    <mergeCell ref="CN31:CV31"/>
-    <mergeCell ref="AG28:AO28"/>
-    <mergeCell ref="AP28:AY28"/>
-    <mergeCell ref="CN30:CV30"/>
-    <mergeCell ref="T24:CV24"/>
-    <mergeCell ref="CN29:CV29"/>
-    <mergeCell ref="BK30:BS30"/>
-    <mergeCell ref="BI16:BK16"/>
-    <mergeCell ref="Z16:AA16"/>
-    <mergeCell ref="AB16:AE16"/>
-    <mergeCell ref="R21:CV21"/>
-    <mergeCell ref="R22:CV22"/>
+    <mergeCell ref="BT29:CB29"/>
+    <mergeCell ref="CC29:CM29"/>
+    <mergeCell ref="A21:P21"/>
+    <mergeCell ref="R19:CV19"/>
+    <mergeCell ref="A27:CV27"/>
+    <mergeCell ref="AZ28:BJ28"/>
+    <mergeCell ref="A24:Q24"/>
+    <mergeCell ref="A29:V29"/>
+    <mergeCell ref="W29:AF29"/>
+    <mergeCell ref="AG29:AO29"/>
+    <mergeCell ref="AP29:AY29"/>
+    <mergeCell ref="AZ29:BJ29"/>
+    <mergeCell ref="V42:CV42"/>
+    <mergeCell ref="A42:T42"/>
+    <mergeCell ref="BX34:CP34"/>
+    <mergeCell ref="AZ30:BJ30"/>
+    <mergeCell ref="BT30:CB30"/>
+    <mergeCell ref="CC30:CM30"/>
+    <mergeCell ref="A30:V30"/>
+    <mergeCell ref="W30:AF30"/>
+    <mergeCell ref="AF16:AG16"/>
+    <mergeCell ref="AI16:BD16"/>
+    <mergeCell ref="A39:P39"/>
+    <mergeCell ref="R39:CV39"/>
+    <mergeCell ref="R40:CV40"/>
+    <mergeCell ref="T25:CV25"/>
+    <mergeCell ref="A32:CV32"/>
+    <mergeCell ref="BM16:BO16"/>
+    <mergeCell ref="BF16:BH16"/>
+    <mergeCell ref="BX33:CP33"/>
+    <mergeCell ref="S33:BP33"/>
+    <mergeCell ref="A33:Q33"/>
+    <mergeCell ref="A18:P18"/>
+    <mergeCell ref="R18:CV18"/>
+    <mergeCell ref="CC28:CM28"/>
+    <mergeCell ref="BK29:BS29"/>
+    <mergeCell ref="V43:CV43"/>
+    <mergeCell ref="X50:CV50"/>
+    <mergeCell ref="A54:AC54"/>
+    <mergeCell ref="AE54:CV54"/>
+    <mergeCell ref="A49:V49"/>
+    <mergeCell ref="X49:CV49"/>
+    <mergeCell ref="A45:V45"/>
     <mergeCell ref="CK45:CV45"/>
     <mergeCell ref="CK46:CV46"/>
     <mergeCell ref="W47:AW47"/>
@@ -6249,6 +6250,11 @@
     <mergeCell ref="W46:AW46"/>
     <mergeCell ref="BO46:BZ46"/>
     <mergeCell ref="CA45:CJ45"/>
+    <mergeCell ref="S34:BP34"/>
+    <mergeCell ref="BX36:CP36"/>
+    <mergeCell ref="BX37:CP37"/>
+    <mergeCell ref="W36:BP36"/>
+    <mergeCell ref="W37:BP37"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.39370078740157483" bottom="0.19685039370078741" header="0" footer="0"/>

--- a/Template/TN.xlsx
+++ b/Template/TN.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\senkx\OneDrive\Документы\LabsSGK\Дипломное проектирование\Программный продукт\Blank\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3705E14A-D9E8-4161-A07F-9814E2DEEE93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6B5A5A0A-176F-4B63-995E-05E2D4399676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11760" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,146 +541,146 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="5" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="0" xfId="8" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="3" xfId="8" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="5" applyFont="1" applyFill="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="2" borderId="1" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="4" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="3" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="5" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="8" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="9" xfId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="2" xfId="9" applyNumberFormat="1" applyFont="1" applyFill="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1051,7 +1051,7 @@
   <sheetFormatPr defaultColWidth="1" defaultRowHeight="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="15" width="1" style="1" customWidth="1"/>
-    <col min="16" max="16" width="1.83203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="2.5" style="1" customWidth="1"/>
     <col min="17" max="101" width="1" style="1" customWidth="1"/>
     <col min="102" max="173" width="1" style="2" customWidth="1"/>
     <col min="174" max="16384" width="1" style="1"/>
@@ -1086,49 +1086,49 @@
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="37" t="s">
+      <c r="Z2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="AA2" s="38"/>
-      <c r="AB2" s="38"/>
-      <c r="AC2" s="38"/>
-      <c r="AD2" s="38"/>
-      <c r="AE2" s="38"/>
-      <c r="AF2" s="38"/>
-      <c r="AG2" s="38"/>
-      <c r="AH2" s="38"/>
-      <c r="AI2" s="38"/>
-      <c r="AJ2" s="38"/>
-      <c r="AK2" s="38"/>
-      <c r="AL2" s="38"/>
-      <c r="AM2" s="38"/>
-      <c r="AN2" s="38"/>
-      <c r="AO2" s="38"/>
-      <c r="AP2" s="38"/>
-      <c r="AQ2" s="38"/>
-      <c r="AR2" s="39"/>
-      <c r="AS2" s="52" t="s">
+      <c r="AA2" s="17"/>
+      <c r="AB2" s="17"/>
+      <c r="AC2" s="17"/>
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="17"/>
+      <c r="AF2" s="17"/>
+      <c r="AG2" s="17"/>
+      <c r="AH2" s="17"/>
+      <c r="AI2" s="17"/>
+      <c r="AJ2" s="17"/>
+      <c r="AK2" s="17"/>
+      <c r="AL2" s="17"/>
+      <c r="AM2" s="17"/>
+      <c r="AN2" s="17"/>
+      <c r="AO2" s="17"/>
+      <c r="AP2" s="17"/>
+      <c r="AQ2" s="17"/>
+      <c r="AR2" s="18"/>
+      <c r="AS2" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="AT2" s="53"/>
-      <c r="AU2" s="53"/>
-      <c r="AV2" s="53"/>
-      <c r="AW2" s="53"/>
-      <c r="AX2" s="53"/>
-      <c r="AY2" s="53"/>
-      <c r="AZ2" s="53"/>
-      <c r="BA2" s="53"/>
-      <c r="BB2" s="53"/>
-      <c r="BC2" s="53"/>
-      <c r="BD2" s="53"/>
-      <c r="BE2" s="53"/>
-      <c r="BF2" s="53"/>
-      <c r="BG2" s="53"/>
-      <c r="BH2" s="53"/>
-      <c r="BI2" s="53"/>
-      <c r="BJ2" s="53"/>
-      <c r="BK2" s="53"/>
-      <c r="BL2" s="54"/>
+      <c r="AT2" s="32"/>
+      <c r="AU2" s="32"/>
+      <c r="AV2" s="32"/>
+      <c r="AW2" s="32"/>
+      <c r="AX2" s="32"/>
+      <c r="AY2" s="32"/>
+      <c r="AZ2" s="32"/>
+      <c r="BA2" s="32"/>
+      <c r="BB2" s="32"/>
+      <c r="BC2" s="32"/>
+      <c r="BD2" s="32"/>
+      <c r="BE2" s="32"/>
+      <c r="BF2" s="32"/>
+      <c r="BG2" s="32"/>
+      <c r="BH2" s="32"/>
+      <c r="BI2" s="32"/>
+      <c r="BJ2" s="32"/>
+      <c r="BK2" s="32"/>
+      <c r="BL2" s="33"/>
       <c r="BM2" s="1"/>
       <c r="BN2" s="1"/>
       <c r="BO2" s="1"/>
@@ -1265,45 +1265,45 @@
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="40"/>
-      <c r="AA3" s="41"/>
-      <c r="AB3" s="41"/>
-      <c r="AC3" s="41"/>
-      <c r="AD3" s="41"/>
-      <c r="AE3" s="41"/>
-      <c r="AF3" s="41"/>
-      <c r="AG3" s="41"/>
-      <c r="AH3" s="41"/>
-      <c r="AI3" s="41"/>
-      <c r="AJ3" s="41"/>
-      <c r="AK3" s="41"/>
-      <c r="AL3" s="41"/>
-      <c r="AM3" s="41"/>
-      <c r="AN3" s="41"/>
-      <c r="AO3" s="41"/>
-      <c r="AP3" s="41"/>
-      <c r="AQ3" s="41"/>
-      <c r="AR3" s="42"/>
-      <c r="AS3" s="55"/>
-      <c r="AT3" s="56"/>
-      <c r="AU3" s="56"/>
-      <c r="AV3" s="56"/>
-      <c r="AW3" s="56"/>
-      <c r="AX3" s="56"/>
-      <c r="AY3" s="56"/>
-      <c r="AZ3" s="56"/>
-      <c r="BA3" s="56"/>
-      <c r="BB3" s="56"/>
-      <c r="BC3" s="56"/>
-      <c r="BD3" s="56"/>
-      <c r="BE3" s="56"/>
-      <c r="BF3" s="56"/>
-      <c r="BG3" s="56"/>
-      <c r="BH3" s="56"/>
-      <c r="BI3" s="56"/>
-      <c r="BJ3" s="56"/>
-      <c r="BK3" s="56"/>
-      <c r="BL3" s="57"/>
+      <c r="Z3" s="19"/>
+      <c r="AA3" s="20"/>
+      <c r="AB3" s="20"/>
+      <c r="AC3" s="20"/>
+      <c r="AD3" s="20"/>
+      <c r="AE3" s="20"/>
+      <c r="AF3" s="20"/>
+      <c r="AG3" s="20"/>
+      <c r="AH3" s="20"/>
+      <c r="AI3" s="20"/>
+      <c r="AJ3" s="20"/>
+      <c r="AK3" s="20"/>
+      <c r="AL3" s="20"/>
+      <c r="AM3" s="20"/>
+      <c r="AN3" s="20"/>
+      <c r="AO3" s="20"/>
+      <c r="AP3" s="20"/>
+      <c r="AQ3" s="20"/>
+      <c r="AR3" s="21"/>
+      <c r="AS3" s="34"/>
+      <c r="AT3" s="35"/>
+      <c r="AU3" s="35"/>
+      <c r="AV3" s="35"/>
+      <c r="AW3" s="35"/>
+      <c r="AX3" s="35"/>
+      <c r="AY3" s="35"/>
+      <c r="AZ3" s="35"/>
+      <c r="BA3" s="35"/>
+      <c r="BB3" s="35"/>
+      <c r="BC3" s="35"/>
+      <c r="BD3" s="35"/>
+      <c r="BE3" s="35"/>
+      <c r="BF3" s="35"/>
+      <c r="BG3" s="35"/>
+      <c r="BH3" s="35"/>
+      <c r="BI3" s="35"/>
+      <c r="BJ3" s="35"/>
+      <c r="BK3" s="35"/>
+      <c r="BL3" s="36"/>
       <c r="BM3" s="1"/>
       <c r="BN3" s="1"/>
       <c r="BO3" s="1"/>
@@ -1440,45 +1440,45 @@
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="Z4" s="43"/>
-      <c r="AA4" s="44"/>
-      <c r="AB4" s="44"/>
-      <c r="AC4" s="44"/>
-      <c r="AD4" s="44"/>
-      <c r="AE4" s="44"/>
-      <c r="AF4" s="44"/>
-      <c r="AG4" s="44"/>
-      <c r="AH4" s="44"/>
-      <c r="AI4" s="44"/>
-      <c r="AJ4" s="44"/>
-      <c r="AK4" s="44"/>
-      <c r="AL4" s="44"/>
-      <c r="AM4" s="44"/>
-      <c r="AN4" s="44"/>
-      <c r="AO4" s="44"/>
-      <c r="AP4" s="44"/>
-      <c r="AQ4" s="44"/>
-      <c r="AR4" s="45"/>
-      <c r="AS4" s="58"/>
-      <c r="AT4" s="59"/>
-      <c r="AU4" s="59"/>
-      <c r="AV4" s="59"/>
-      <c r="AW4" s="59"/>
-      <c r="AX4" s="59"/>
-      <c r="AY4" s="59"/>
-      <c r="AZ4" s="59"/>
-      <c r="BA4" s="59"/>
-      <c r="BB4" s="59"/>
-      <c r="BC4" s="59"/>
-      <c r="BD4" s="59"/>
-      <c r="BE4" s="59"/>
-      <c r="BF4" s="59"/>
-      <c r="BG4" s="59"/>
-      <c r="BH4" s="59"/>
-      <c r="BI4" s="59"/>
-      <c r="BJ4" s="59"/>
-      <c r="BK4" s="59"/>
-      <c r="BL4" s="60"/>
+      <c r="Z4" s="22"/>
+      <c r="AA4" s="23"/>
+      <c r="AB4" s="23"/>
+      <c r="AC4" s="23"/>
+      <c r="AD4" s="23"/>
+      <c r="AE4" s="23"/>
+      <c r="AF4" s="23"/>
+      <c r="AG4" s="23"/>
+      <c r="AH4" s="23"/>
+      <c r="AI4" s="23"/>
+      <c r="AJ4" s="23"/>
+      <c r="AK4" s="23"/>
+      <c r="AL4" s="23"/>
+      <c r="AM4" s="23"/>
+      <c r="AN4" s="23"/>
+      <c r="AO4" s="23"/>
+      <c r="AP4" s="23"/>
+      <c r="AQ4" s="23"/>
+      <c r="AR4" s="24"/>
+      <c r="AS4" s="37"/>
+      <c r="AT4" s="38"/>
+      <c r="AU4" s="38"/>
+      <c r="AV4" s="38"/>
+      <c r="AW4" s="38"/>
+      <c r="AX4" s="38"/>
+      <c r="AY4" s="38"/>
+      <c r="AZ4" s="38"/>
+      <c r="BA4" s="38"/>
+      <c r="BB4" s="38"/>
+      <c r="BC4" s="38"/>
+      <c r="BD4" s="38"/>
+      <c r="BE4" s="38"/>
+      <c r="BF4" s="38"/>
+      <c r="BG4" s="38"/>
+      <c r="BH4" s="38"/>
+      <c r="BI4" s="38"/>
+      <c r="BJ4" s="38"/>
+      <c r="BK4" s="38"/>
+      <c r="BL4" s="39"/>
       <c r="BM4" s="1"/>
       <c r="BN4" s="1"/>
       <c r="BO4" s="1"/>
@@ -1609,57 +1609,57 @@
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
-      <c r="T5" s="33" t="s">
+      <c r="T5" s="48" t="s">
         <v>25</v>
       </c>
-      <c r="U5" s="33"/>
-      <c r="V5" s="33"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="33"/>
+      <c r="U5" s="48"/>
+      <c r="V5" s="48"/>
+      <c r="W5" s="48"/>
+      <c r="X5" s="48"/>
       <c r="Y5" s="1"/>
-      <c r="Z5" s="46" t="s">
+      <c r="Z5" s="25" t="s">
         <v>58</v>
       </c>
-      <c r="AA5" s="47"/>
-      <c r="AB5" s="47"/>
-      <c r="AC5" s="47"/>
-      <c r="AD5" s="47"/>
-      <c r="AE5" s="47"/>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="47"/>
-      <c r="AL5" s="47"/>
-      <c r="AM5" s="47"/>
-      <c r="AN5" s="47"/>
-      <c r="AO5" s="47"/>
-      <c r="AP5" s="47"/>
-      <c r="AQ5" s="47"/>
-      <c r="AR5" s="48"/>
-      <c r="AS5" s="46" t="s">
+      <c r="AA5" s="26"/>
+      <c r="AB5" s="26"/>
+      <c r="AC5" s="26"/>
+      <c r="AD5" s="26"/>
+      <c r="AE5" s="26"/>
+      <c r="AF5" s="26"/>
+      <c r="AG5" s="26"/>
+      <c r="AH5" s="26"/>
+      <c r="AI5" s="26"/>
+      <c r="AJ5" s="26"/>
+      <c r="AK5" s="26"/>
+      <c r="AL5" s="26"/>
+      <c r="AM5" s="26"/>
+      <c r="AN5" s="26"/>
+      <c r="AO5" s="26"/>
+      <c r="AP5" s="26"/>
+      <c r="AQ5" s="26"/>
+      <c r="AR5" s="27"/>
+      <c r="AS5" s="25" t="s">
         <v>59</v>
       </c>
-      <c r="AT5" s="47"/>
-      <c r="AU5" s="47"/>
-      <c r="AV5" s="47"/>
-      <c r="AW5" s="47"/>
-      <c r="AX5" s="47"/>
-      <c r="AY5" s="47"/>
-      <c r="AZ5" s="47"/>
-      <c r="BA5" s="47"/>
-      <c r="BB5" s="47"/>
-      <c r="BC5" s="47"/>
-      <c r="BD5" s="47"/>
-      <c r="BE5" s="47"/>
-      <c r="BF5" s="47"/>
-      <c r="BG5" s="47"/>
-      <c r="BH5" s="47"/>
-      <c r="BI5" s="47"/>
-      <c r="BJ5" s="47"/>
-      <c r="BK5" s="47"/>
-      <c r="BL5" s="48"/>
+      <c r="AT5" s="26"/>
+      <c r="AU5" s="26"/>
+      <c r="AV5" s="26"/>
+      <c r="AW5" s="26"/>
+      <c r="AX5" s="26"/>
+      <c r="AY5" s="26"/>
+      <c r="AZ5" s="26"/>
+      <c r="BA5" s="26"/>
+      <c r="BB5" s="26"/>
+      <c r="BC5" s="26"/>
+      <c r="BD5" s="26"/>
+      <c r="BE5" s="26"/>
+      <c r="BF5" s="26"/>
+      <c r="BG5" s="26"/>
+      <c r="BH5" s="26"/>
+      <c r="BI5" s="26"/>
+      <c r="BJ5" s="26"/>
+      <c r="BK5" s="26"/>
+      <c r="BL5" s="27"/>
       <c r="BM5" s="1"/>
       <c r="BN5" s="1"/>
       <c r="BO5" s="1"/>
@@ -1790,51 +1790,51 @@
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="33"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="33"/>
+      <c r="T6" s="48"/>
+      <c r="U6" s="48"/>
+      <c r="V6" s="48"/>
+      <c r="W6" s="48"/>
+      <c r="X6" s="48"/>
       <c r="Y6" s="1"/>
-      <c r="Z6" s="49"/>
-      <c r="AA6" s="50"/>
-      <c r="AB6" s="50"/>
-      <c r="AC6" s="50"/>
-      <c r="AD6" s="50"/>
-      <c r="AE6" s="50"/>
-      <c r="AF6" s="50"/>
-      <c r="AG6" s="50"/>
-      <c r="AH6" s="50"/>
-      <c r="AI6" s="50"/>
-      <c r="AJ6" s="50"/>
-      <c r="AK6" s="50"/>
-      <c r="AL6" s="50"/>
-      <c r="AM6" s="50"/>
-      <c r="AN6" s="50"/>
-      <c r="AO6" s="50"/>
-      <c r="AP6" s="50"/>
-      <c r="AQ6" s="50"/>
-      <c r="AR6" s="51"/>
-      <c r="AS6" s="49"/>
-      <c r="AT6" s="50"/>
-      <c r="AU6" s="50"/>
-      <c r="AV6" s="50"/>
-      <c r="AW6" s="50"/>
-      <c r="AX6" s="50"/>
-      <c r="AY6" s="50"/>
-      <c r="AZ6" s="50"/>
-      <c r="BA6" s="50"/>
-      <c r="BB6" s="50"/>
-      <c r="BC6" s="50"/>
-      <c r="BD6" s="50"/>
-      <c r="BE6" s="50"/>
-      <c r="BF6" s="50"/>
-      <c r="BG6" s="50"/>
-      <c r="BH6" s="50"/>
-      <c r="BI6" s="50"/>
-      <c r="BJ6" s="50"/>
-      <c r="BK6" s="50"/>
-      <c r="BL6" s="51"/>
+      <c r="Z6" s="28"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29"/>
+      <c r="AC6" s="29"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="29"/>
+      <c r="AF6" s="29"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="29"/>
+      <c r="AI6" s="29"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="29"/>
+      <c r="AL6" s="29"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="29"/>
+      <c r="AO6" s="29"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="30"/>
+      <c r="AS6" s="28"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
+      <c r="AW6" s="29"/>
+      <c r="AX6" s="29"/>
+      <c r="AY6" s="29"/>
+      <c r="AZ6" s="29"/>
+      <c r="BA6" s="29"/>
+      <c r="BB6" s="29"/>
+      <c r="BC6" s="29"/>
+      <c r="BD6" s="29"/>
+      <c r="BE6" s="29"/>
+      <c r="BF6" s="29"/>
+      <c r="BG6" s="29"/>
+      <c r="BH6" s="29"/>
+      <c r="BI6" s="29"/>
+      <c r="BJ6" s="29"/>
+      <c r="BK6" s="29"/>
+      <c r="BL6" s="30"/>
       <c r="BM6" s="1"/>
       <c r="BN6" s="1"/>
       <c r="BO6" s="1"/>
@@ -1973,256 +1973,256 @@
       <c r="CW15" s="2"/>
     </row>
     <row r="16" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="Z16" s="23" t="s">
+      <c r="Z16" s="45" t="s">
         <v>0</v>
       </c>
-      <c r="AA16" s="23"/>
-      <c r="AB16" s="62"/>
-      <c r="AC16" s="62"/>
-      <c r="AD16" s="62"/>
-      <c r="AE16" s="62"/>
-      <c r="AF16" s="19" t="s">
+      <c r="AA16" s="45"/>
+      <c r="AB16" s="46"/>
+      <c r="AC16" s="46"/>
+      <c r="AD16" s="46"/>
+      <c r="AE16" s="46"/>
+      <c r="AF16" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="AG16" s="19"/>
-      <c r="AI16" s="20" t="s">
+      <c r="AG16" s="52"/>
+      <c r="AI16" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="AJ16" s="20"/>
-      <c r="AK16" s="20"/>
-      <c r="AL16" s="20"/>
-      <c r="AM16" s="20"/>
-      <c r="AN16" s="20"/>
-      <c r="AO16" s="20"/>
-      <c r="AP16" s="20"/>
-      <c r="AQ16" s="20"/>
-      <c r="AR16" s="20"/>
-      <c r="AS16" s="20"/>
-      <c r="AT16" s="20"/>
-      <c r="AU16" s="20"/>
-      <c r="AV16" s="20"/>
-      <c r="AW16" s="20"/>
-      <c r="AX16" s="20"/>
-      <c r="AY16" s="20"/>
-      <c r="AZ16" s="20"/>
-      <c r="BA16" s="20"/>
-      <c r="BB16" s="20"/>
-      <c r="BC16" s="20"/>
-      <c r="BD16" s="20"/>
-      <c r="BF16" s="23">
+      <c r="AJ16" s="42"/>
+      <c r="AK16" s="42"/>
+      <c r="AL16" s="42"/>
+      <c r="AM16" s="42"/>
+      <c r="AN16" s="42"/>
+      <c r="AO16" s="42"/>
+      <c r="AP16" s="42"/>
+      <c r="AQ16" s="42"/>
+      <c r="AR16" s="42"/>
+      <c r="AS16" s="42"/>
+      <c r="AT16" s="42"/>
+      <c r="AU16" s="42"/>
+      <c r="AV16" s="42"/>
+      <c r="AW16" s="42"/>
+      <c r="AX16" s="42"/>
+      <c r="AY16" s="42"/>
+      <c r="AZ16" s="42"/>
+      <c r="BA16" s="42"/>
+      <c r="BB16" s="42"/>
+      <c r="BC16" s="42"/>
+      <c r="BD16" s="42"/>
+      <c r="BF16" s="45">
         <v>20</v>
       </c>
-      <c r="BG16" s="23"/>
-      <c r="BH16" s="23"/>
-      <c r="BI16" s="61"/>
-      <c r="BJ16" s="61"/>
-      <c r="BK16" s="61"/>
-      <c r="BM16" s="19" t="s">
+      <c r="BG16" s="45"/>
+      <c r="BH16" s="45"/>
+      <c r="BI16" s="44"/>
+      <c r="BJ16" s="44"/>
+      <c r="BK16" s="44"/>
+      <c r="BM16" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="BN16" s="19"/>
-      <c r="BO16" s="19"/>
+      <c r="BN16" s="52"/>
+      <c r="BO16" s="52"/>
       <c r="CW16" s="2"/>
     </row>
     <row r="17" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="CW17" s="2"/>
     </row>
     <row r="18" spans="1:173" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="52" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
+      <c r="D18" s="52"/>
+      <c r="E18" s="52"/>
+      <c r="F18" s="52"/>
+      <c r="G18" s="52"/>
+      <c r="H18" s="52"/>
+      <c r="I18" s="52"/>
+      <c r="J18" s="52"/>
+      <c r="K18" s="52"/>
+      <c r="L18" s="52"/>
+      <c r="M18" s="52"/>
+      <c r="N18" s="52"/>
+      <c r="O18" s="52"/>
+      <c r="P18" s="52"/>
       <c r="Q18" s="4"/>
-      <c r="R18" s="20" t="s">
+      <c r="R18" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="S18" s="20"/>
-      <c r="T18" s="20"/>
-      <c r="U18" s="20"/>
-      <c r="V18" s="20"/>
-      <c r="W18" s="20"/>
-      <c r="X18" s="20"/>
-      <c r="Y18" s="20"/>
-      <c r="Z18" s="20"/>
-      <c r="AA18" s="20"/>
-      <c r="AB18" s="20"/>
-      <c r="AC18" s="20"/>
-      <c r="AD18" s="20"/>
-      <c r="AE18" s="20"/>
-      <c r="AF18" s="20"/>
-      <c r="AG18" s="20"/>
-      <c r="AH18" s="20"/>
-      <c r="AI18" s="20"/>
-      <c r="AJ18" s="20"/>
-      <c r="AK18" s="20"/>
-      <c r="AL18" s="20"/>
-      <c r="AM18" s="20"/>
-      <c r="AN18" s="20"/>
-      <c r="AO18" s="20"/>
-      <c r="AP18" s="20"/>
-      <c r="AQ18" s="20"/>
-      <c r="AR18" s="20"/>
-      <c r="AS18" s="20"/>
-      <c r="AT18" s="20"/>
-      <c r="AU18" s="20"/>
-      <c r="AV18" s="20"/>
-      <c r="AW18" s="20"/>
-      <c r="AX18" s="20"/>
-      <c r="AY18" s="20"/>
-      <c r="AZ18" s="20"/>
-      <c r="BA18" s="20"/>
-      <c r="BB18" s="20"/>
-      <c r="BC18" s="20"/>
-      <c r="BD18" s="20"/>
-      <c r="BE18" s="20"/>
-      <c r="BF18" s="20"/>
-      <c r="BG18" s="20"/>
-      <c r="BH18" s="20"/>
-      <c r="BI18" s="20"/>
-      <c r="BJ18" s="20"/>
-      <c r="BK18" s="20"/>
-      <c r="BL18" s="20"/>
-      <c r="BM18" s="20"/>
-      <c r="BN18" s="20"/>
-      <c r="BO18" s="20"/>
-      <c r="BP18" s="20"/>
-      <c r="BQ18" s="20"/>
-      <c r="BR18" s="20"/>
-      <c r="BS18" s="20"/>
-      <c r="BT18" s="20"/>
-      <c r="BU18" s="20"/>
-      <c r="BV18" s="20"/>
-      <c r="BW18" s="20"/>
-      <c r="BX18" s="20"/>
-      <c r="BY18" s="20"/>
-      <c r="BZ18" s="20"/>
-      <c r="CA18" s="20"/>
-      <c r="CB18" s="20"/>
-      <c r="CC18" s="20"/>
-      <c r="CD18" s="20"/>
-      <c r="CE18" s="20"/>
-      <c r="CF18" s="20"/>
-      <c r="CG18" s="20"/>
-      <c r="CH18" s="20"/>
-      <c r="CI18" s="20"/>
-      <c r="CJ18" s="20"/>
-      <c r="CK18" s="20"/>
-      <c r="CL18" s="20"/>
-      <c r="CM18" s="20"/>
-      <c r="CN18" s="20"/>
-      <c r="CO18" s="20"/>
-      <c r="CP18" s="20"/>
-      <c r="CQ18" s="20"/>
-      <c r="CR18" s="20"/>
-      <c r="CS18" s="20"/>
-      <c r="CT18" s="20"/>
-      <c r="CU18" s="20"/>
-      <c r="CV18" s="20"/>
+      <c r="S18" s="42"/>
+      <c r="T18" s="42"/>
+      <c r="U18" s="42"/>
+      <c r="V18" s="42"/>
+      <c r="W18" s="42"/>
+      <c r="X18" s="42"/>
+      <c r="Y18" s="42"/>
+      <c r="Z18" s="42"/>
+      <c r="AA18" s="42"/>
+      <c r="AB18" s="42"/>
+      <c r="AC18" s="42"/>
+      <c r="AD18" s="42"/>
+      <c r="AE18" s="42"/>
+      <c r="AF18" s="42"/>
+      <c r="AG18" s="42"/>
+      <c r="AH18" s="42"/>
+      <c r="AI18" s="42"/>
+      <c r="AJ18" s="42"/>
+      <c r="AK18" s="42"/>
+      <c r="AL18" s="42"/>
+      <c r="AM18" s="42"/>
+      <c r="AN18" s="42"/>
+      <c r="AO18" s="42"/>
+      <c r="AP18" s="42"/>
+      <c r="AQ18" s="42"/>
+      <c r="AR18" s="42"/>
+      <c r="AS18" s="42"/>
+      <c r="AT18" s="42"/>
+      <c r="AU18" s="42"/>
+      <c r="AV18" s="42"/>
+      <c r="AW18" s="42"/>
+      <c r="AX18" s="42"/>
+      <c r="AY18" s="42"/>
+      <c r="AZ18" s="42"/>
+      <c r="BA18" s="42"/>
+      <c r="BB18" s="42"/>
+      <c r="BC18" s="42"/>
+      <c r="BD18" s="42"/>
+      <c r="BE18" s="42"/>
+      <c r="BF18" s="42"/>
+      <c r="BG18" s="42"/>
+      <c r="BH18" s="42"/>
+      <c r="BI18" s="42"/>
+      <c r="BJ18" s="42"/>
+      <c r="BK18" s="42"/>
+      <c r="BL18" s="42"/>
+      <c r="BM18" s="42"/>
+      <c r="BN18" s="42"/>
+      <c r="BO18" s="42"/>
+      <c r="BP18" s="42"/>
+      <c r="BQ18" s="42"/>
+      <c r="BR18" s="42"/>
+      <c r="BS18" s="42"/>
+      <c r="BT18" s="42"/>
+      <c r="BU18" s="42"/>
+      <c r="BV18" s="42"/>
+      <c r="BW18" s="42"/>
+      <c r="BX18" s="42"/>
+      <c r="BY18" s="42"/>
+      <c r="BZ18" s="42"/>
+      <c r="CA18" s="42"/>
+      <c r="CB18" s="42"/>
+      <c r="CC18" s="42"/>
+      <c r="CD18" s="42"/>
+      <c r="CE18" s="42"/>
+      <c r="CF18" s="42"/>
+      <c r="CG18" s="42"/>
+      <c r="CH18" s="42"/>
+      <c r="CI18" s="42"/>
+      <c r="CJ18" s="42"/>
+      <c r="CK18" s="42"/>
+      <c r="CL18" s="42"/>
+      <c r="CM18" s="42"/>
+      <c r="CN18" s="42"/>
+      <c r="CO18" s="42"/>
+      <c r="CP18" s="42"/>
+      <c r="CQ18" s="42"/>
+      <c r="CR18" s="42"/>
+      <c r="CS18" s="42"/>
+      <c r="CT18" s="42"/>
+      <c r="CU18" s="42"/>
+      <c r="CV18" s="42"/>
       <c r="CW18" s="2"/>
     </row>
     <row r="19" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="O19" s="5"/>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
-      <c r="R19" s="21" t="s">
+      <c r="R19" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="S19" s="21"/>
-      <c r="T19" s="21"/>
-      <c r="U19" s="21"/>
-      <c r="V19" s="21"/>
-      <c r="W19" s="21"/>
-      <c r="X19" s="21"/>
-      <c r="Y19" s="21"/>
-      <c r="Z19" s="21"/>
-      <c r="AA19" s="21"/>
-      <c r="AB19" s="21"/>
-      <c r="AC19" s="21"/>
-      <c r="AD19" s="21"/>
-      <c r="AE19" s="21"/>
-      <c r="AF19" s="21"/>
-      <c r="AG19" s="21"/>
-      <c r="AH19" s="21"/>
-      <c r="AI19" s="21"/>
-      <c r="AJ19" s="21"/>
-      <c r="AK19" s="21"/>
-      <c r="AL19" s="21"/>
-      <c r="AM19" s="21"/>
-      <c r="AN19" s="21"/>
-      <c r="AO19" s="21"/>
-      <c r="AP19" s="21"/>
-      <c r="AQ19" s="21"/>
-      <c r="AR19" s="21"/>
-      <c r="AS19" s="21"/>
-      <c r="AT19" s="21"/>
-      <c r="AU19" s="21"/>
-      <c r="AV19" s="21"/>
-      <c r="AW19" s="21"/>
-      <c r="AX19" s="21"/>
-      <c r="AY19" s="21"/>
-      <c r="AZ19" s="21"/>
-      <c r="BA19" s="21"/>
-      <c r="BB19" s="21"/>
-      <c r="BC19" s="21"/>
-      <c r="BD19" s="21"/>
-      <c r="BE19" s="21"/>
-      <c r="BF19" s="21"/>
-      <c r="BG19" s="21"/>
-      <c r="BH19" s="21"/>
-      <c r="BI19" s="21"/>
-      <c r="BJ19" s="21"/>
-      <c r="BK19" s="21"/>
-      <c r="BL19" s="21"/>
-      <c r="BM19" s="21"/>
-      <c r="BN19" s="21"/>
-      <c r="BO19" s="21"/>
-      <c r="BP19" s="21"/>
-      <c r="BQ19" s="21"/>
-      <c r="BR19" s="21"/>
-      <c r="BS19" s="21"/>
-      <c r="BT19" s="21"/>
-      <c r="BU19" s="21"/>
-      <c r="BV19" s="21"/>
-      <c r="BW19" s="21"/>
-      <c r="BX19" s="21"/>
-      <c r="BY19" s="21"/>
-      <c r="BZ19" s="21"/>
-      <c r="CA19" s="21"/>
-      <c r="CB19" s="21"/>
-      <c r="CC19" s="21"/>
-      <c r="CD19" s="21"/>
-      <c r="CE19" s="21"/>
-      <c r="CF19" s="21"/>
-      <c r="CG19" s="21"/>
-      <c r="CH19" s="21"/>
-      <c r="CI19" s="21"/>
-      <c r="CJ19" s="21"/>
-      <c r="CK19" s="21"/>
-      <c r="CL19" s="21"/>
-      <c r="CM19" s="21"/>
-      <c r="CN19" s="21"/>
-      <c r="CO19" s="21"/>
-      <c r="CP19" s="21"/>
-      <c r="CQ19" s="21"/>
-      <c r="CR19" s="21"/>
-      <c r="CS19" s="21"/>
-      <c r="CT19" s="21"/>
-      <c r="CU19" s="21"/>
-      <c r="CV19" s="21"/>
+      <c r="S19" s="47"/>
+      <c r="T19" s="47"/>
+      <c r="U19" s="47"/>
+      <c r="V19" s="47"/>
+      <c r="W19" s="47"/>
+      <c r="X19" s="47"/>
+      <c r="Y19" s="47"/>
+      <c r="Z19" s="47"/>
+      <c r="AA19" s="47"/>
+      <c r="AB19" s="47"/>
+      <c r="AC19" s="47"/>
+      <c r="AD19" s="47"/>
+      <c r="AE19" s="47"/>
+      <c r="AF19" s="47"/>
+      <c r="AG19" s="47"/>
+      <c r="AH19" s="47"/>
+      <c r="AI19" s="47"/>
+      <c r="AJ19" s="47"/>
+      <c r="AK19" s="47"/>
+      <c r="AL19" s="47"/>
+      <c r="AM19" s="47"/>
+      <c r="AN19" s="47"/>
+      <c r="AO19" s="47"/>
+      <c r="AP19" s="47"/>
+      <c r="AQ19" s="47"/>
+      <c r="AR19" s="47"/>
+      <c r="AS19" s="47"/>
+      <c r="AT19" s="47"/>
+      <c r="AU19" s="47"/>
+      <c r="AV19" s="47"/>
+      <c r="AW19" s="47"/>
+      <c r="AX19" s="47"/>
+      <c r="AY19" s="47"/>
+      <c r="AZ19" s="47"/>
+      <c r="BA19" s="47"/>
+      <c r="BB19" s="47"/>
+      <c r="BC19" s="47"/>
+      <c r="BD19" s="47"/>
+      <c r="BE19" s="47"/>
+      <c r="BF19" s="47"/>
+      <c r="BG19" s="47"/>
+      <c r="BH19" s="47"/>
+      <c r="BI19" s="47"/>
+      <c r="BJ19" s="47"/>
+      <c r="BK19" s="47"/>
+      <c r="BL19" s="47"/>
+      <c r="BM19" s="47"/>
+      <c r="BN19" s="47"/>
+      <c r="BO19" s="47"/>
+      <c r="BP19" s="47"/>
+      <c r="BQ19" s="47"/>
+      <c r="BR19" s="47"/>
+      <c r="BS19" s="47"/>
+      <c r="BT19" s="47"/>
+      <c r="BU19" s="47"/>
+      <c r="BV19" s="47"/>
+      <c r="BW19" s="47"/>
+      <c r="BX19" s="47"/>
+      <c r="BY19" s="47"/>
+      <c r="BZ19" s="47"/>
+      <c r="CA19" s="47"/>
+      <c r="CB19" s="47"/>
+      <c r="CC19" s="47"/>
+      <c r="CD19" s="47"/>
+      <c r="CE19" s="47"/>
+      <c r="CF19" s="47"/>
+      <c r="CG19" s="47"/>
+      <c r="CH19" s="47"/>
+      <c r="CI19" s="47"/>
+      <c r="CJ19" s="47"/>
+      <c r="CK19" s="47"/>
+      <c r="CL19" s="47"/>
+      <c r="CM19" s="47"/>
+      <c r="CN19" s="47"/>
+      <c r="CO19" s="47"/>
+      <c r="CP19" s="47"/>
+      <c r="CQ19" s="47"/>
+      <c r="CR19" s="47"/>
+      <c r="CS19" s="47"/>
+      <c r="CT19" s="47"/>
+      <c r="CU19" s="47"/>
+      <c r="CV19" s="47"/>
       <c r="CW19" s="2"/>
     </row>
     <row r="20" spans="1:173" ht="3" customHeight="1" x14ac:dyDescent="0.2">
@@ -2315,110 +2315,110 @@
       <c r="CW20" s="2"/>
     </row>
     <row r="21" spans="1:173" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="52" t="s">
         <v>7</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
+      <c r="D21" s="52"/>
+      <c r="E21" s="52"/>
+      <c r="F21" s="52"/>
+      <c r="G21" s="52"/>
+      <c r="H21" s="52"/>
+      <c r="I21" s="52"/>
+      <c r="J21" s="52"/>
+      <c r="K21" s="52"/>
+      <c r="L21" s="52"/>
+      <c r="M21" s="52"/>
+      <c r="N21" s="52"/>
+      <c r="O21" s="52"/>
+      <c r="P21" s="52"/>
       <c r="Q21" s="4"/>
-      <c r="R21" s="20" t="s">
+      <c r="R21" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="S21" s="20"/>
-      <c r="T21" s="20"/>
-      <c r="U21" s="20"/>
-      <c r="V21" s="20"/>
-      <c r="W21" s="20"/>
-      <c r="X21" s="20"/>
-      <c r="Y21" s="20"/>
-      <c r="Z21" s="20"/>
-      <c r="AA21" s="20"/>
-      <c r="AB21" s="20"/>
-      <c r="AC21" s="20"/>
-      <c r="AD21" s="20"/>
-      <c r="AE21" s="20"/>
-      <c r="AF21" s="20"/>
-      <c r="AG21" s="20"/>
-      <c r="AH21" s="20"/>
-      <c r="AI21" s="20"/>
-      <c r="AJ21" s="20"/>
-      <c r="AK21" s="20"/>
-      <c r="AL21" s="20"/>
-      <c r="AM21" s="20"/>
-      <c r="AN21" s="20"/>
-      <c r="AO21" s="20"/>
-      <c r="AP21" s="20"/>
-      <c r="AQ21" s="20"/>
-      <c r="AR21" s="20"/>
-      <c r="AS21" s="20"/>
-      <c r="AT21" s="20"/>
-      <c r="AU21" s="20"/>
-      <c r="AV21" s="20"/>
-      <c r="AW21" s="20"/>
-      <c r="AX21" s="20"/>
-      <c r="AY21" s="20"/>
-      <c r="AZ21" s="20"/>
-      <c r="BA21" s="20"/>
-      <c r="BB21" s="20"/>
-      <c r="BC21" s="20"/>
-      <c r="BD21" s="20"/>
-      <c r="BE21" s="20"/>
-      <c r="BF21" s="20"/>
-      <c r="BG21" s="20"/>
-      <c r="BH21" s="20"/>
-      <c r="BI21" s="20"/>
-      <c r="BJ21" s="20"/>
-      <c r="BK21" s="20"/>
-      <c r="BL21" s="20"/>
-      <c r="BM21" s="20"/>
-      <c r="BN21" s="20"/>
-      <c r="BO21" s="20"/>
-      <c r="BP21" s="20"/>
-      <c r="BQ21" s="20"/>
-      <c r="BR21" s="20"/>
-      <c r="BS21" s="20"/>
-      <c r="BT21" s="20"/>
-      <c r="BU21" s="20"/>
-      <c r="BV21" s="20"/>
-      <c r="BW21" s="20"/>
-      <c r="BX21" s="20"/>
-      <c r="BY21" s="20"/>
-      <c r="BZ21" s="20"/>
-      <c r="CA21" s="20"/>
-      <c r="CB21" s="20"/>
-      <c r="CC21" s="20"/>
-      <c r="CD21" s="20"/>
-      <c r="CE21" s="20"/>
-      <c r="CF21" s="20"/>
-      <c r="CG21" s="20"/>
-      <c r="CH21" s="20"/>
-      <c r="CI21" s="20"/>
-      <c r="CJ21" s="20"/>
-      <c r="CK21" s="20"/>
-      <c r="CL21" s="20"/>
-      <c r="CM21" s="20"/>
-      <c r="CN21" s="20"/>
-      <c r="CO21" s="20"/>
-      <c r="CP21" s="20"/>
-      <c r="CQ21" s="20"/>
-      <c r="CR21" s="20"/>
-      <c r="CS21" s="20"/>
-      <c r="CT21" s="20"/>
-      <c r="CU21" s="20"/>
-      <c r="CV21" s="20"/>
+      <c r="S21" s="42"/>
+      <c r="T21" s="42"/>
+      <c r="U21" s="42"/>
+      <c r="V21" s="42"/>
+      <c r="W21" s="42"/>
+      <c r="X21" s="42"/>
+      <c r="Y21" s="42"/>
+      <c r="Z21" s="42"/>
+      <c r="AA21" s="42"/>
+      <c r="AB21" s="42"/>
+      <c r="AC21" s="42"/>
+      <c r="AD21" s="42"/>
+      <c r="AE21" s="42"/>
+      <c r="AF21" s="42"/>
+      <c r="AG21" s="42"/>
+      <c r="AH21" s="42"/>
+      <c r="AI21" s="42"/>
+      <c r="AJ21" s="42"/>
+      <c r="AK21" s="42"/>
+      <c r="AL21" s="42"/>
+      <c r="AM21" s="42"/>
+      <c r="AN21" s="42"/>
+      <c r="AO21" s="42"/>
+      <c r="AP21" s="42"/>
+      <c r="AQ21" s="42"/>
+      <c r="AR21" s="42"/>
+      <c r="AS21" s="42"/>
+      <c r="AT21" s="42"/>
+      <c r="AU21" s="42"/>
+      <c r="AV21" s="42"/>
+      <c r="AW21" s="42"/>
+      <c r="AX21" s="42"/>
+      <c r="AY21" s="42"/>
+      <c r="AZ21" s="42"/>
+      <c r="BA21" s="42"/>
+      <c r="BB21" s="42"/>
+      <c r="BC21" s="42"/>
+      <c r="BD21" s="42"/>
+      <c r="BE21" s="42"/>
+      <c r="BF21" s="42"/>
+      <c r="BG21" s="42"/>
+      <c r="BH21" s="42"/>
+      <c r="BI21" s="42"/>
+      <c r="BJ21" s="42"/>
+      <c r="BK21" s="42"/>
+      <c r="BL21" s="42"/>
+      <c r="BM21" s="42"/>
+      <c r="BN21" s="42"/>
+      <c r="BO21" s="42"/>
+      <c r="BP21" s="42"/>
+      <c r="BQ21" s="42"/>
+      <c r="BR21" s="42"/>
+      <c r="BS21" s="42"/>
+      <c r="BT21" s="42"/>
+      <c r="BU21" s="42"/>
+      <c r="BV21" s="42"/>
+      <c r="BW21" s="42"/>
+      <c r="BX21" s="42"/>
+      <c r="BY21" s="42"/>
+      <c r="BZ21" s="42"/>
+      <c r="CA21" s="42"/>
+      <c r="CB21" s="42"/>
+      <c r="CC21" s="42"/>
+      <c r="CD21" s="42"/>
+      <c r="CE21" s="42"/>
+      <c r="CF21" s="42"/>
+      <c r="CG21" s="42"/>
+      <c r="CH21" s="42"/>
+      <c r="CI21" s="42"/>
+      <c r="CJ21" s="42"/>
+      <c r="CK21" s="42"/>
+      <c r="CL21" s="42"/>
+      <c r="CM21" s="42"/>
+      <c r="CN21" s="42"/>
+      <c r="CO21" s="42"/>
+      <c r="CP21" s="42"/>
+      <c r="CQ21" s="42"/>
+      <c r="CR21" s="42"/>
+      <c r="CS21" s="42"/>
+      <c r="CT21" s="42"/>
+      <c r="CU21" s="42"/>
+      <c r="CV21" s="42"/>
       <c r="CW21" s="2"/>
     </row>
     <row r="22" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -2439,91 +2439,91 @@
       <c r="O22" s="5"/>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
-      <c r="R22" s="21" t="s">
+      <c r="R22" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="S22" s="21"/>
-      <c r="T22" s="21"/>
-      <c r="U22" s="21"/>
-      <c r="V22" s="21"/>
-      <c r="W22" s="21"/>
-      <c r="X22" s="21"/>
-      <c r="Y22" s="21"/>
-      <c r="Z22" s="21"/>
-      <c r="AA22" s="21"/>
-      <c r="AB22" s="21"/>
-      <c r="AC22" s="21"/>
-      <c r="AD22" s="21"/>
-      <c r="AE22" s="21"/>
-      <c r="AF22" s="21"/>
-      <c r="AG22" s="21"/>
-      <c r="AH22" s="21"/>
-      <c r="AI22" s="21"/>
-      <c r="AJ22" s="21"/>
-      <c r="AK22" s="21"/>
-      <c r="AL22" s="21"/>
-      <c r="AM22" s="21"/>
-      <c r="AN22" s="21"/>
-      <c r="AO22" s="21"/>
-      <c r="AP22" s="21"/>
-      <c r="AQ22" s="21"/>
-      <c r="AR22" s="21"/>
-      <c r="AS22" s="21"/>
-      <c r="AT22" s="21"/>
-      <c r="AU22" s="21"/>
-      <c r="AV22" s="21"/>
-      <c r="AW22" s="21"/>
-      <c r="AX22" s="21"/>
-      <c r="AY22" s="21"/>
-      <c r="AZ22" s="21"/>
-      <c r="BA22" s="21"/>
-      <c r="BB22" s="21"/>
-      <c r="BC22" s="21"/>
-      <c r="BD22" s="21"/>
-      <c r="BE22" s="21"/>
-      <c r="BF22" s="21"/>
-      <c r="BG22" s="21"/>
-      <c r="BH22" s="21"/>
-      <c r="BI22" s="21"/>
-      <c r="BJ22" s="21"/>
-      <c r="BK22" s="21"/>
-      <c r="BL22" s="21"/>
-      <c r="BM22" s="21"/>
-      <c r="BN22" s="21"/>
-      <c r="BO22" s="21"/>
-      <c r="BP22" s="21"/>
-      <c r="BQ22" s="21"/>
-      <c r="BR22" s="21"/>
-      <c r="BS22" s="21"/>
-      <c r="BT22" s="21"/>
-      <c r="BU22" s="21"/>
-      <c r="BV22" s="21"/>
-      <c r="BW22" s="21"/>
-      <c r="BX22" s="21"/>
-      <c r="BY22" s="21"/>
-      <c r="BZ22" s="21"/>
-      <c r="CA22" s="21"/>
-      <c r="CB22" s="21"/>
-      <c r="CC22" s="21"/>
-      <c r="CD22" s="21"/>
-      <c r="CE22" s="21"/>
-      <c r="CF22" s="21"/>
-      <c r="CG22" s="21"/>
-      <c r="CH22" s="21"/>
-      <c r="CI22" s="21"/>
-      <c r="CJ22" s="21"/>
-      <c r="CK22" s="21"/>
-      <c r="CL22" s="21"/>
-      <c r="CM22" s="21"/>
-      <c r="CN22" s="21"/>
-      <c r="CO22" s="21"/>
-      <c r="CP22" s="21"/>
-      <c r="CQ22" s="21"/>
-      <c r="CR22" s="21"/>
-      <c r="CS22" s="21"/>
-      <c r="CT22" s="21"/>
-      <c r="CU22" s="21"/>
-      <c r="CV22" s="21"/>
+      <c r="S22" s="47"/>
+      <c r="T22" s="47"/>
+      <c r="U22" s="47"/>
+      <c r="V22" s="47"/>
+      <c r="W22" s="47"/>
+      <c r="X22" s="47"/>
+      <c r="Y22" s="47"/>
+      <c r="Z22" s="47"/>
+      <c r="AA22" s="47"/>
+      <c r="AB22" s="47"/>
+      <c r="AC22" s="47"/>
+      <c r="AD22" s="47"/>
+      <c r="AE22" s="47"/>
+      <c r="AF22" s="47"/>
+      <c r="AG22" s="47"/>
+      <c r="AH22" s="47"/>
+      <c r="AI22" s="47"/>
+      <c r="AJ22" s="47"/>
+      <c r="AK22" s="47"/>
+      <c r="AL22" s="47"/>
+      <c r="AM22" s="47"/>
+      <c r="AN22" s="47"/>
+      <c r="AO22" s="47"/>
+      <c r="AP22" s="47"/>
+      <c r="AQ22" s="47"/>
+      <c r="AR22" s="47"/>
+      <c r="AS22" s="47"/>
+      <c r="AT22" s="47"/>
+      <c r="AU22" s="47"/>
+      <c r="AV22" s="47"/>
+      <c r="AW22" s="47"/>
+      <c r="AX22" s="47"/>
+      <c r="AY22" s="47"/>
+      <c r="AZ22" s="47"/>
+      <c r="BA22" s="47"/>
+      <c r="BB22" s="47"/>
+      <c r="BC22" s="47"/>
+      <c r="BD22" s="47"/>
+      <c r="BE22" s="47"/>
+      <c r="BF22" s="47"/>
+      <c r="BG22" s="47"/>
+      <c r="BH22" s="47"/>
+      <c r="BI22" s="47"/>
+      <c r="BJ22" s="47"/>
+      <c r="BK22" s="47"/>
+      <c r="BL22" s="47"/>
+      <c r="BM22" s="47"/>
+      <c r="BN22" s="47"/>
+      <c r="BO22" s="47"/>
+      <c r="BP22" s="47"/>
+      <c r="BQ22" s="47"/>
+      <c r="BR22" s="47"/>
+      <c r="BS22" s="47"/>
+      <c r="BT22" s="47"/>
+      <c r="BU22" s="47"/>
+      <c r="BV22" s="47"/>
+      <c r="BW22" s="47"/>
+      <c r="BX22" s="47"/>
+      <c r="BY22" s="47"/>
+      <c r="BZ22" s="47"/>
+      <c r="CA22" s="47"/>
+      <c r="CB22" s="47"/>
+      <c r="CC22" s="47"/>
+      <c r="CD22" s="47"/>
+      <c r="CE22" s="47"/>
+      <c r="CF22" s="47"/>
+      <c r="CG22" s="47"/>
+      <c r="CH22" s="47"/>
+      <c r="CI22" s="47"/>
+      <c r="CJ22" s="47"/>
+      <c r="CK22" s="47"/>
+      <c r="CL22" s="47"/>
+      <c r="CM22" s="47"/>
+      <c r="CN22" s="47"/>
+      <c r="CO22" s="47"/>
+      <c r="CP22" s="47"/>
+      <c r="CQ22" s="47"/>
+      <c r="CR22" s="47"/>
+      <c r="CS22" s="47"/>
+      <c r="CT22" s="47"/>
+      <c r="CU22" s="47"/>
+      <c r="CV22" s="47"/>
     </row>
     <row r="23" spans="1:173" s="2" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
@@ -2628,108 +2628,108 @@
       <c r="CV23" s="6"/>
     </row>
     <row r="24" spans="1:173" s="2" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="52" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-      <c r="I24" s="19"/>
-      <c r="J24" s="19"/>
-      <c r="K24" s="19"/>
-      <c r="L24" s="19"/>
-      <c r="M24" s="19"/>
-      <c r="N24" s="19"/>
-      <c r="O24" s="19"/>
-      <c r="P24" s="19"/>
-      <c r="Q24" s="19"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="52"/>
+      <c r="H24" s="52"/>
+      <c r="I24" s="52"/>
+      <c r="J24" s="52"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="52"/>
+      <c r="M24" s="52"/>
+      <c r="N24" s="52"/>
+      <c r="O24" s="52"/>
+      <c r="P24" s="52"/>
+      <c r="Q24" s="52"/>
       <c r="R24" s="1"/>
       <c r="S24" s="4"/>
-      <c r="T24" s="20"/>
-      <c r="U24" s="20"/>
-      <c r="V24" s="20"/>
-      <c r="W24" s="20"/>
-      <c r="X24" s="20"/>
-      <c r="Y24" s="20"/>
-      <c r="Z24" s="20"/>
-      <c r="AA24" s="20"/>
-      <c r="AB24" s="20"/>
-      <c r="AC24" s="20"/>
-      <c r="AD24" s="20"/>
-      <c r="AE24" s="20"/>
-      <c r="AF24" s="20"/>
-      <c r="AG24" s="20"/>
-      <c r="AH24" s="20"/>
-      <c r="AI24" s="20"/>
-      <c r="AJ24" s="20"/>
-      <c r="AK24" s="20"/>
-      <c r="AL24" s="20"/>
-      <c r="AM24" s="20"/>
-      <c r="AN24" s="20"/>
-      <c r="AO24" s="20"/>
-      <c r="AP24" s="20"/>
-      <c r="AQ24" s="20"/>
-      <c r="AR24" s="20"/>
-      <c r="AS24" s="20"/>
-      <c r="AT24" s="20"/>
-      <c r="AU24" s="20"/>
-      <c r="AV24" s="20"/>
-      <c r="AW24" s="20"/>
-      <c r="AX24" s="20"/>
-      <c r="AY24" s="20"/>
-      <c r="AZ24" s="20"/>
-      <c r="BA24" s="20"/>
-      <c r="BB24" s="20"/>
-      <c r="BC24" s="20"/>
-      <c r="BD24" s="20"/>
-      <c r="BE24" s="20"/>
-      <c r="BF24" s="20"/>
-      <c r="BG24" s="20"/>
-      <c r="BH24" s="20"/>
-      <c r="BI24" s="20"/>
-      <c r="BJ24" s="20"/>
-      <c r="BK24" s="20"/>
-      <c r="BL24" s="20"/>
-      <c r="BM24" s="20"/>
-      <c r="BN24" s="20"/>
-      <c r="BO24" s="20"/>
-      <c r="BP24" s="20"/>
-      <c r="BQ24" s="20"/>
-      <c r="BR24" s="20"/>
-      <c r="BS24" s="20"/>
-      <c r="BT24" s="20"/>
-      <c r="BU24" s="20"/>
-      <c r="BV24" s="20"/>
-      <c r="BW24" s="20"/>
-      <c r="BX24" s="20"/>
-      <c r="BY24" s="20"/>
-      <c r="BZ24" s="20"/>
-      <c r="CA24" s="20"/>
-      <c r="CB24" s="20"/>
-      <c r="CC24" s="20"/>
-      <c r="CD24" s="20"/>
-      <c r="CE24" s="20"/>
-      <c r="CF24" s="20"/>
-      <c r="CG24" s="20"/>
-      <c r="CH24" s="20"/>
-      <c r="CI24" s="20"/>
-      <c r="CJ24" s="20"/>
-      <c r="CK24" s="20"/>
-      <c r="CL24" s="20"/>
-      <c r="CM24" s="20"/>
-      <c r="CN24" s="20"/>
-      <c r="CO24" s="20"/>
-      <c r="CP24" s="20"/>
-      <c r="CQ24" s="20"/>
-      <c r="CR24" s="20"/>
-      <c r="CS24" s="20"/>
-      <c r="CT24" s="20"/>
-      <c r="CU24" s="20"/>
-      <c r="CV24" s="20"/>
+      <c r="T24" s="42"/>
+      <c r="U24" s="42"/>
+      <c r="V24" s="42"/>
+      <c r="W24" s="42"/>
+      <c r="X24" s="42"/>
+      <c r="Y24" s="42"/>
+      <c r="Z24" s="42"/>
+      <c r="AA24" s="42"/>
+      <c r="AB24" s="42"/>
+      <c r="AC24" s="42"/>
+      <c r="AD24" s="42"/>
+      <c r="AE24" s="42"/>
+      <c r="AF24" s="42"/>
+      <c r="AG24" s="42"/>
+      <c r="AH24" s="42"/>
+      <c r="AI24" s="42"/>
+      <c r="AJ24" s="42"/>
+      <c r="AK24" s="42"/>
+      <c r="AL24" s="42"/>
+      <c r="AM24" s="42"/>
+      <c r="AN24" s="42"/>
+      <c r="AO24" s="42"/>
+      <c r="AP24" s="42"/>
+      <c r="AQ24" s="42"/>
+      <c r="AR24" s="42"/>
+      <c r="AS24" s="42"/>
+      <c r="AT24" s="42"/>
+      <c r="AU24" s="42"/>
+      <c r="AV24" s="42"/>
+      <c r="AW24" s="42"/>
+      <c r="AX24" s="42"/>
+      <c r="AY24" s="42"/>
+      <c r="AZ24" s="42"/>
+      <c r="BA24" s="42"/>
+      <c r="BB24" s="42"/>
+      <c r="BC24" s="42"/>
+      <c r="BD24" s="42"/>
+      <c r="BE24" s="42"/>
+      <c r="BF24" s="42"/>
+      <c r="BG24" s="42"/>
+      <c r="BH24" s="42"/>
+      <c r="BI24" s="42"/>
+      <c r="BJ24" s="42"/>
+      <c r="BK24" s="42"/>
+      <c r="BL24" s="42"/>
+      <c r="BM24" s="42"/>
+      <c r="BN24" s="42"/>
+      <c r="BO24" s="42"/>
+      <c r="BP24" s="42"/>
+      <c r="BQ24" s="42"/>
+      <c r="BR24" s="42"/>
+      <c r="BS24" s="42"/>
+      <c r="BT24" s="42"/>
+      <c r="BU24" s="42"/>
+      <c r="BV24" s="42"/>
+      <c r="BW24" s="42"/>
+      <c r="BX24" s="42"/>
+      <c r="BY24" s="42"/>
+      <c r="BZ24" s="42"/>
+      <c r="CA24" s="42"/>
+      <c r="CB24" s="42"/>
+      <c r="CC24" s="42"/>
+      <c r="CD24" s="42"/>
+      <c r="CE24" s="42"/>
+      <c r="CF24" s="42"/>
+      <c r="CG24" s="42"/>
+      <c r="CH24" s="42"/>
+      <c r="CI24" s="42"/>
+      <c r="CJ24" s="42"/>
+      <c r="CK24" s="42"/>
+      <c r="CL24" s="42"/>
+      <c r="CM24" s="42"/>
+      <c r="CN24" s="42"/>
+      <c r="CO24" s="42"/>
+      <c r="CP24" s="42"/>
+      <c r="CQ24" s="42"/>
+      <c r="CR24" s="42"/>
+      <c r="CS24" s="42"/>
+      <c r="CT24" s="42"/>
+      <c r="CU24" s="42"/>
+      <c r="CV24" s="42"/>
     </row>
     <row r="25" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
@@ -2751,89 +2751,89 @@
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="5"/>
-      <c r="T25" s="21" t="s">
+      <c r="T25" s="47" t="s">
         <v>26</v>
       </c>
-      <c r="U25" s="21"/>
-      <c r="V25" s="21"/>
-      <c r="W25" s="21"/>
-      <c r="X25" s="21"/>
-      <c r="Y25" s="21"/>
-      <c r="Z25" s="21"/>
-      <c r="AA25" s="21"/>
-      <c r="AB25" s="21"/>
-      <c r="AC25" s="21"/>
-      <c r="AD25" s="21"/>
-      <c r="AE25" s="21"/>
-      <c r="AF25" s="21"/>
-      <c r="AG25" s="21"/>
-      <c r="AH25" s="21"/>
-      <c r="AI25" s="21"/>
-      <c r="AJ25" s="21"/>
-      <c r="AK25" s="21"/>
-      <c r="AL25" s="21"/>
-      <c r="AM25" s="21"/>
-      <c r="AN25" s="21"/>
-      <c r="AO25" s="21"/>
-      <c r="AP25" s="21"/>
-      <c r="AQ25" s="21"/>
-      <c r="AR25" s="21"/>
-      <c r="AS25" s="21"/>
-      <c r="AT25" s="21"/>
-      <c r="AU25" s="21"/>
-      <c r="AV25" s="21"/>
-      <c r="AW25" s="21"/>
-      <c r="AX25" s="21"/>
-      <c r="AY25" s="21"/>
-      <c r="AZ25" s="21"/>
-      <c r="BA25" s="21"/>
-      <c r="BB25" s="21"/>
-      <c r="BC25" s="21"/>
-      <c r="BD25" s="21"/>
-      <c r="BE25" s="21"/>
-      <c r="BF25" s="21"/>
-      <c r="BG25" s="21"/>
-      <c r="BH25" s="21"/>
-      <c r="BI25" s="21"/>
-      <c r="BJ25" s="21"/>
-      <c r="BK25" s="21"/>
-      <c r="BL25" s="21"/>
-      <c r="BM25" s="21"/>
-      <c r="BN25" s="21"/>
-      <c r="BO25" s="21"/>
-      <c r="BP25" s="21"/>
-      <c r="BQ25" s="21"/>
-      <c r="BR25" s="21"/>
-      <c r="BS25" s="21"/>
-      <c r="BT25" s="21"/>
-      <c r="BU25" s="21"/>
-      <c r="BV25" s="21"/>
-      <c r="BW25" s="21"/>
-      <c r="BX25" s="21"/>
-      <c r="BY25" s="21"/>
-      <c r="BZ25" s="21"/>
-      <c r="CA25" s="21"/>
-      <c r="CB25" s="21"/>
-      <c r="CC25" s="21"/>
-      <c r="CD25" s="21"/>
-      <c r="CE25" s="21"/>
-      <c r="CF25" s="21"/>
-      <c r="CG25" s="21"/>
-      <c r="CH25" s="21"/>
-      <c r="CI25" s="21"/>
-      <c r="CJ25" s="21"/>
-      <c r="CK25" s="21"/>
-      <c r="CL25" s="21"/>
-      <c r="CM25" s="21"/>
-      <c r="CN25" s="21"/>
-      <c r="CO25" s="21"/>
-      <c r="CP25" s="21"/>
-      <c r="CQ25" s="21"/>
-      <c r="CR25" s="21"/>
-      <c r="CS25" s="21"/>
-      <c r="CT25" s="21"/>
-      <c r="CU25" s="21"/>
-      <c r="CV25" s="21"/>
+      <c r="U25" s="47"/>
+      <c r="V25" s="47"/>
+      <c r="W25" s="47"/>
+      <c r="X25" s="47"/>
+      <c r="Y25" s="47"/>
+      <c r="Z25" s="47"/>
+      <c r="AA25" s="47"/>
+      <c r="AB25" s="47"/>
+      <c r="AC25" s="47"/>
+      <c r="AD25" s="47"/>
+      <c r="AE25" s="47"/>
+      <c r="AF25" s="47"/>
+      <c r="AG25" s="47"/>
+      <c r="AH25" s="47"/>
+      <c r="AI25" s="47"/>
+      <c r="AJ25" s="47"/>
+      <c r="AK25" s="47"/>
+      <c r="AL25" s="47"/>
+      <c r="AM25" s="47"/>
+      <c r="AN25" s="47"/>
+      <c r="AO25" s="47"/>
+      <c r="AP25" s="47"/>
+      <c r="AQ25" s="47"/>
+      <c r="AR25" s="47"/>
+      <c r="AS25" s="47"/>
+      <c r="AT25" s="47"/>
+      <c r="AU25" s="47"/>
+      <c r="AV25" s="47"/>
+      <c r="AW25" s="47"/>
+      <c r="AX25" s="47"/>
+      <c r="AY25" s="47"/>
+      <c r="AZ25" s="47"/>
+      <c r="BA25" s="47"/>
+      <c r="BB25" s="47"/>
+      <c r="BC25" s="47"/>
+      <c r="BD25" s="47"/>
+      <c r="BE25" s="47"/>
+      <c r="BF25" s="47"/>
+      <c r="BG25" s="47"/>
+      <c r="BH25" s="47"/>
+      <c r="BI25" s="47"/>
+      <c r="BJ25" s="47"/>
+      <c r="BK25" s="47"/>
+      <c r="BL25" s="47"/>
+      <c r="BM25" s="47"/>
+      <c r="BN25" s="47"/>
+      <c r="BO25" s="47"/>
+      <c r="BP25" s="47"/>
+      <c r="BQ25" s="47"/>
+      <c r="BR25" s="47"/>
+      <c r="BS25" s="47"/>
+      <c r="BT25" s="47"/>
+      <c r="BU25" s="47"/>
+      <c r="BV25" s="47"/>
+      <c r="BW25" s="47"/>
+      <c r="BX25" s="47"/>
+      <c r="BY25" s="47"/>
+      <c r="BZ25" s="47"/>
+      <c r="CA25" s="47"/>
+      <c r="CB25" s="47"/>
+      <c r="CC25" s="47"/>
+      <c r="CD25" s="47"/>
+      <c r="CE25" s="47"/>
+      <c r="CF25" s="47"/>
+      <c r="CG25" s="47"/>
+      <c r="CH25" s="47"/>
+      <c r="CI25" s="47"/>
+      <c r="CJ25" s="47"/>
+      <c r="CK25" s="47"/>
+      <c r="CL25" s="47"/>
+      <c r="CM25" s="47"/>
+      <c r="CN25" s="47"/>
+      <c r="CO25" s="47"/>
+      <c r="CP25" s="47"/>
+      <c r="CQ25" s="47"/>
+      <c r="CR25" s="47"/>
+      <c r="CS25" s="47"/>
+      <c r="CT25" s="47"/>
+      <c r="CU25" s="47"/>
+      <c r="CV25" s="47"/>
     </row>
     <row r="26" spans="1:173" s="3" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
@@ -3011,108 +3011,108 @@
       <c r="FQ26" s="2"/>
     </row>
     <row r="27" spans="1:173" s="3" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="32" t="s">
+      <c r="A27" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="32"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="32"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="32"/>
-      <c r="I27" s="32"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="32"/>
-      <c r="L27" s="32"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="32"/>
-      <c r="O27" s="32"/>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="32"/>
-      <c r="R27" s="32"/>
-      <c r="S27" s="32"/>
-      <c r="T27" s="32"/>
-      <c r="U27" s="32"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="32"/>
-      <c r="X27" s="32"/>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="32"/>
-      <c r="AA27" s="32"/>
-      <c r="AB27" s="32"/>
-      <c r="AC27" s="32"/>
-      <c r="AD27" s="32"/>
-      <c r="AE27" s="32"/>
-      <c r="AF27" s="32"/>
-      <c r="AG27" s="32"/>
-      <c r="AH27" s="32"/>
-      <c r="AI27" s="32"/>
-      <c r="AJ27" s="32"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="32"/>
-      <c r="AM27" s="32"/>
-      <c r="AN27" s="32"/>
-      <c r="AO27" s="32"/>
-      <c r="AP27" s="32"/>
-      <c r="AQ27" s="32"/>
-      <c r="AR27" s="32"/>
-      <c r="AS27" s="32"/>
-      <c r="AT27" s="32"/>
-      <c r="AU27" s="32"/>
-      <c r="AV27" s="32"/>
-      <c r="AW27" s="32"/>
-      <c r="AX27" s="32"/>
-      <c r="AY27" s="32"/>
-      <c r="AZ27" s="32"/>
-      <c r="BA27" s="32"/>
-      <c r="BB27" s="32"/>
-      <c r="BC27" s="32"/>
-      <c r="BD27" s="32"/>
-      <c r="BE27" s="32"/>
-      <c r="BF27" s="32"/>
-      <c r="BG27" s="32"/>
-      <c r="BH27" s="32"/>
-      <c r="BI27" s="32"/>
-      <c r="BJ27" s="32"/>
-      <c r="BK27" s="32"/>
-      <c r="BL27" s="32"/>
-      <c r="BM27" s="32"/>
-      <c r="BN27" s="32"/>
-      <c r="BO27" s="32"/>
-      <c r="BP27" s="32"/>
-      <c r="BQ27" s="32"/>
-      <c r="BR27" s="32"/>
-      <c r="BS27" s="32"/>
-      <c r="BT27" s="32"/>
-      <c r="BU27" s="32"/>
-      <c r="BV27" s="32"/>
-      <c r="BW27" s="32"/>
-      <c r="BX27" s="32"/>
-      <c r="BY27" s="32"/>
-      <c r="BZ27" s="32"/>
-      <c r="CA27" s="32"/>
-      <c r="CB27" s="32"/>
-      <c r="CC27" s="32"/>
-      <c r="CD27" s="32"/>
-      <c r="CE27" s="32"/>
-      <c r="CF27" s="32"/>
-      <c r="CG27" s="32"/>
-      <c r="CH27" s="32"/>
-      <c r="CI27" s="32"/>
-      <c r="CJ27" s="32"/>
-      <c r="CK27" s="32"/>
-      <c r="CL27" s="32"/>
-      <c r="CM27" s="32"/>
-      <c r="CN27" s="32"/>
-      <c r="CO27" s="32"/>
-      <c r="CP27" s="32"/>
-      <c r="CQ27" s="32"/>
-      <c r="CR27" s="32"/>
-      <c r="CS27" s="32"/>
-      <c r="CT27" s="32"/>
-      <c r="CU27" s="32"/>
-      <c r="CV27" s="32"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="41"/>
+      <c r="F27" s="41"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="41"/>
+      <c r="I27" s="41"/>
+      <c r="J27" s="41"/>
+      <c r="K27" s="41"/>
+      <c r="L27" s="41"/>
+      <c r="M27" s="41"/>
+      <c r="N27" s="41"/>
+      <c r="O27" s="41"/>
+      <c r="P27" s="41"/>
+      <c r="Q27" s="41"/>
+      <c r="R27" s="41"/>
+      <c r="S27" s="41"/>
+      <c r="T27" s="41"/>
+      <c r="U27" s="41"/>
+      <c r="V27" s="41"/>
+      <c r="W27" s="41"/>
+      <c r="X27" s="41"/>
+      <c r="Y27" s="41"/>
+      <c r="Z27" s="41"/>
+      <c r="AA27" s="41"/>
+      <c r="AB27" s="41"/>
+      <c r="AC27" s="41"/>
+      <c r="AD27" s="41"/>
+      <c r="AE27" s="41"/>
+      <c r="AF27" s="41"/>
+      <c r="AG27" s="41"/>
+      <c r="AH27" s="41"/>
+      <c r="AI27" s="41"/>
+      <c r="AJ27" s="41"/>
+      <c r="AK27" s="41"/>
+      <c r="AL27" s="41"/>
+      <c r="AM27" s="41"/>
+      <c r="AN27" s="41"/>
+      <c r="AO27" s="41"/>
+      <c r="AP27" s="41"/>
+      <c r="AQ27" s="41"/>
+      <c r="AR27" s="41"/>
+      <c r="AS27" s="41"/>
+      <c r="AT27" s="41"/>
+      <c r="AU27" s="41"/>
+      <c r="AV27" s="41"/>
+      <c r="AW27" s="41"/>
+      <c r="AX27" s="41"/>
+      <c r="AY27" s="41"/>
+      <c r="AZ27" s="41"/>
+      <c r="BA27" s="41"/>
+      <c r="BB27" s="41"/>
+      <c r="BC27" s="41"/>
+      <c r="BD27" s="41"/>
+      <c r="BE27" s="41"/>
+      <c r="BF27" s="41"/>
+      <c r="BG27" s="41"/>
+      <c r="BH27" s="41"/>
+      <c r="BI27" s="41"/>
+      <c r="BJ27" s="41"/>
+      <c r="BK27" s="41"/>
+      <c r="BL27" s="41"/>
+      <c r="BM27" s="41"/>
+      <c r="BN27" s="41"/>
+      <c r="BO27" s="41"/>
+      <c r="BP27" s="41"/>
+      <c r="BQ27" s="41"/>
+      <c r="BR27" s="41"/>
+      <c r="BS27" s="41"/>
+      <c r="BT27" s="41"/>
+      <c r="BU27" s="41"/>
+      <c r="BV27" s="41"/>
+      <c r="BW27" s="41"/>
+      <c r="BX27" s="41"/>
+      <c r="BY27" s="41"/>
+      <c r="BZ27" s="41"/>
+      <c r="CA27" s="41"/>
+      <c r="CB27" s="41"/>
+      <c r="CC27" s="41"/>
+      <c r="CD27" s="41"/>
+      <c r="CE27" s="41"/>
+      <c r="CF27" s="41"/>
+      <c r="CG27" s="41"/>
+      <c r="CH27" s="41"/>
+      <c r="CI27" s="41"/>
+      <c r="CJ27" s="41"/>
+      <c r="CK27" s="41"/>
+      <c r="CL27" s="41"/>
+      <c r="CM27" s="41"/>
+      <c r="CN27" s="41"/>
+      <c r="CO27" s="41"/>
+      <c r="CP27" s="41"/>
+      <c r="CQ27" s="41"/>
+      <c r="CR27" s="41"/>
+      <c r="CS27" s="41"/>
+      <c r="CT27" s="41"/>
+      <c r="CU27" s="41"/>
+      <c r="CV27" s="41"/>
       <c r="CX27" s="2"/>
       <c r="CY27" s="2"/>
       <c r="CZ27" s="2"/>
@@ -3187,124 +3187,124 @@
       <c r="FQ27" s="2"/>
     </row>
     <row r="28" spans="1:173" s="3" customFormat="1" ht="37.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="32" t="s">
+      <c r="A28" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="32"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="32"/>
-      <c r="L28" s="32"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="32"/>
-      <c r="O28" s="32"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="32"/>
-      <c r="R28" s="32"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="32"/>
-      <c r="U28" s="32"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="32" t="s">
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
+      <c r="H28" s="41"/>
+      <c r="I28" s="41"/>
+      <c r="J28" s="41"/>
+      <c r="K28" s="41"/>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="41"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="41"/>
+      <c r="S28" s="41"/>
+      <c r="T28" s="41"/>
+      <c r="U28" s="41"/>
+      <c r="V28" s="41"/>
+      <c r="W28" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="X28" s="32"/>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="32"/>
-      <c r="AA28" s="32"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="32"/>
-      <c r="AD28" s="32"/>
-      <c r="AE28" s="32"/>
-      <c r="AF28" s="32"/>
-      <c r="AG28" s="32" t="s">
+      <c r="X28" s="41"/>
+      <c r="Y28" s="41"/>
+      <c r="Z28" s="41"/>
+      <c r="AA28" s="41"/>
+      <c r="AB28" s="41"/>
+      <c r="AC28" s="41"/>
+      <c r="AD28" s="41"/>
+      <c r="AE28" s="41"/>
+      <c r="AF28" s="41"/>
+      <c r="AG28" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="AH28" s="32"/>
-      <c r="AI28" s="32"/>
-      <c r="AJ28" s="32"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="32"/>
-      <c r="AM28" s="32"/>
-      <c r="AN28" s="32"/>
-      <c r="AO28" s="32"/>
-      <c r="AP28" s="32" t="s">
+      <c r="AH28" s="41"/>
+      <c r="AI28" s="41"/>
+      <c r="AJ28" s="41"/>
+      <c r="AK28" s="41"/>
+      <c r="AL28" s="41"/>
+      <c r="AM28" s="41"/>
+      <c r="AN28" s="41"/>
+      <c r="AO28" s="41"/>
+      <c r="AP28" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="AQ28" s="32"/>
-      <c r="AR28" s="32"/>
-      <c r="AS28" s="32"/>
-      <c r="AT28" s="32"/>
-      <c r="AU28" s="32"/>
-      <c r="AV28" s="32"/>
-      <c r="AW28" s="32"/>
-      <c r="AX28" s="32"/>
-      <c r="AY28" s="32"/>
-      <c r="AZ28" s="32" t="s">
+      <c r="AQ28" s="41"/>
+      <c r="AR28" s="41"/>
+      <c r="AS28" s="41"/>
+      <c r="AT28" s="41"/>
+      <c r="AU28" s="41"/>
+      <c r="AV28" s="41"/>
+      <c r="AW28" s="41"/>
+      <c r="AX28" s="41"/>
+      <c r="AY28" s="41"/>
+      <c r="AZ28" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="BA28" s="32"/>
-      <c r="BB28" s="32"/>
-      <c r="BC28" s="32"/>
-      <c r="BD28" s="32"/>
-      <c r="BE28" s="32"/>
-      <c r="BF28" s="32"/>
-      <c r="BG28" s="32"/>
-      <c r="BH28" s="32"/>
-      <c r="BI28" s="32"/>
-      <c r="BJ28" s="32"/>
-      <c r="BK28" s="32" t="s">
+      <c r="BA28" s="41"/>
+      <c r="BB28" s="41"/>
+      <c r="BC28" s="41"/>
+      <c r="BD28" s="41"/>
+      <c r="BE28" s="41"/>
+      <c r="BF28" s="41"/>
+      <c r="BG28" s="41"/>
+      <c r="BH28" s="41"/>
+      <c r="BI28" s="41"/>
+      <c r="BJ28" s="41"/>
+      <c r="BK28" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="BL28" s="32"/>
-      <c r="BM28" s="32"/>
-      <c r="BN28" s="32"/>
-      <c r="BO28" s="32"/>
-      <c r="BP28" s="32"/>
-      <c r="BQ28" s="32"/>
-      <c r="BR28" s="32"/>
-      <c r="BS28" s="32"/>
-      <c r="BT28" s="32" t="s">
+      <c r="BL28" s="41"/>
+      <c r="BM28" s="41"/>
+      <c r="BN28" s="41"/>
+      <c r="BO28" s="41"/>
+      <c r="BP28" s="41"/>
+      <c r="BQ28" s="41"/>
+      <c r="BR28" s="41"/>
+      <c r="BS28" s="41"/>
+      <c r="BT28" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="BU28" s="32"/>
-      <c r="BV28" s="32"/>
-      <c r="BW28" s="32"/>
-      <c r="BX28" s="32"/>
-      <c r="BY28" s="32"/>
-      <c r="BZ28" s="32"/>
-      <c r="CA28" s="32"/>
-      <c r="CB28" s="32"/>
-      <c r="CC28" s="32" t="s">
+      <c r="BU28" s="41"/>
+      <c r="BV28" s="41"/>
+      <c r="BW28" s="41"/>
+      <c r="BX28" s="41"/>
+      <c r="BY28" s="41"/>
+      <c r="BZ28" s="41"/>
+      <c r="CA28" s="41"/>
+      <c r="CB28" s="41"/>
+      <c r="CC28" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="CD28" s="32"/>
-      <c r="CE28" s="32"/>
-      <c r="CF28" s="32"/>
-      <c r="CG28" s="32"/>
-      <c r="CH28" s="32"/>
-      <c r="CI28" s="32"/>
-      <c r="CJ28" s="32"/>
-      <c r="CK28" s="32"/>
-      <c r="CL28" s="32"/>
-      <c r="CM28" s="32"/>
-      <c r="CN28" s="32" t="s">
+      <c r="CD28" s="41"/>
+      <c r="CE28" s="41"/>
+      <c r="CF28" s="41"/>
+      <c r="CG28" s="41"/>
+      <c r="CH28" s="41"/>
+      <c r="CI28" s="41"/>
+      <c r="CJ28" s="41"/>
+      <c r="CK28" s="41"/>
+      <c r="CL28" s="41"/>
+      <c r="CM28" s="41"/>
+      <c r="CN28" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="CO28" s="32"/>
-      <c r="CP28" s="32"/>
-      <c r="CQ28" s="32"/>
-      <c r="CR28" s="32"/>
-      <c r="CS28" s="32"/>
-      <c r="CT28" s="32"/>
-      <c r="CU28" s="32"/>
-      <c r="CV28" s="32"/>
+      <c r="CO28" s="41"/>
+      <c r="CP28" s="41"/>
+      <c r="CQ28" s="41"/>
+      <c r="CR28" s="41"/>
+      <c r="CS28" s="41"/>
+      <c r="CT28" s="41"/>
+      <c r="CU28" s="41"/>
+      <c r="CV28" s="41"/>
       <c r="CX28" s="2"/>
       <c r="CY28" s="2"/>
       <c r="CZ28" s="2"/>
@@ -3379,124 +3379,124 @@
       <c r="FQ28" s="2"/>
     </row>
     <row r="29" spans="1:173" s="3" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="32">
+      <c r="A29" s="41">
         <v>1</v>
       </c>
-      <c r="B29" s="32"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="32"/>
-      <c r="G29" s="32"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
-      <c r="J29" s="32"/>
-      <c r="K29" s="32"/>
-      <c r="L29" s="32"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
-      <c r="O29" s="32"/>
-      <c r="P29" s="32"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="32"/>
-      <c r="T29" s="32"/>
-      <c r="U29" s="32"/>
-      <c r="V29" s="32"/>
-      <c r="W29" s="32">
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="41"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="41"/>
+      <c r="S29" s="41"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="41"/>
+      <c r="V29" s="41"/>
+      <c r="W29" s="41">
         <v>2</v>
       </c>
-      <c r="X29" s="32"/>
-      <c r="Y29" s="32"/>
-      <c r="Z29" s="32"/>
-      <c r="AA29" s="32"/>
-      <c r="AB29" s="32"/>
-      <c r="AC29" s="32"/>
-      <c r="AD29" s="32"/>
-      <c r="AE29" s="32"/>
-      <c r="AF29" s="32"/>
-      <c r="AG29" s="32">
+      <c r="X29" s="41"/>
+      <c r="Y29" s="41"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="41"/>
+      <c r="AB29" s="41"/>
+      <c r="AC29" s="41"/>
+      <c r="AD29" s="41"/>
+      <c r="AE29" s="41"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="41">
         <v>3</v>
       </c>
-      <c r="AH29" s="32"/>
-      <c r="AI29" s="32"/>
-      <c r="AJ29" s="32"/>
-      <c r="AK29" s="32"/>
-      <c r="AL29" s="32"/>
-      <c r="AM29" s="32"/>
-      <c r="AN29" s="32"/>
-      <c r="AO29" s="32"/>
-      <c r="AP29" s="32">
+      <c r="AH29" s="41"/>
+      <c r="AI29" s="41"/>
+      <c r="AJ29" s="41"/>
+      <c r="AK29" s="41"/>
+      <c r="AL29" s="41"/>
+      <c r="AM29" s="41"/>
+      <c r="AN29" s="41"/>
+      <c r="AO29" s="41"/>
+      <c r="AP29" s="41">
         <v>4</v>
       </c>
-      <c r="AQ29" s="32"/>
-      <c r="AR29" s="32"/>
-      <c r="AS29" s="32"/>
-      <c r="AT29" s="32"/>
-      <c r="AU29" s="32"/>
-      <c r="AV29" s="32"/>
-      <c r="AW29" s="32"/>
-      <c r="AX29" s="32"/>
-      <c r="AY29" s="32"/>
-      <c r="AZ29" s="32">
+      <c r="AQ29" s="41"/>
+      <c r="AR29" s="41"/>
+      <c r="AS29" s="41"/>
+      <c r="AT29" s="41"/>
+      <c r="AU29" s="41"/>
+      <c r="AV29" s="41"/>
+      <c r="AW29" s="41"/>
+      <c r="AX29" s="41"/>
+      <c r="AY29" s="41"/>
+      <c r="AZ29" s="41">
         <v>5</v>
       </c>
-      <c r="BA29" s="32"/>
-      <c r="BB29" s="32"/>
-      <c r="BC29" s="32"/>
-      <c r="BD29" s="32"/>
-      <c r="BE29" s="32"/>
-      <c r="BF29" s="32"/>
-      <c r="BG29" s="32"/>
-      <c r="BH29" s="32"/>
-      <c r="BI29" s="32"/>
-      <c r="BJ29" s="32"/>
-      <c r="BK29" s="32">
+      <c r="BA29" s="41"/>
+      <c r="BB29" s="41"/>
+      <c r="BC29" s="41"/>
+      <c r="BD29" s="41"/>
+      <c r="BE29" s="41"/>
+      <c r="BF29" s="41"/>
+      <c r="BG29" s="41"/>
+      <c r="BH29" s="41"/>
+      <c r="BI29" s="41"/>
+      <c r="BJ29" s="41"/>
+      <c r="BK29" s="41">
         <v>6</v>
       </c>
-      <c r="BL29" s="32"/>
-      <c r="BM29" s="32"/>
-      <c r="BN29" s="32"/>
-      <c r="BO29" s="32"/>
-      <c r="BP29" s="32"/>
-      <c r="BQ29" s="32"/>
-      <c r="BR29" s="32"/>
-      <c r="BS29" s="32"/>
-      <c r="BT29" s="32">
+      <c r="BL29" s="41"/>
+      <c r="BM29" s="41"/>
+      <c r="BN29" s="41"/>
+      <c r="BO29" s="41"/>
+      <c r="BP29" s="41"/>
+      <c r="BQ29" s="41"/>
+      <c r="BR29" s="41"/>
+      <c r="BS29" s="41"/>
+      <c r="BT29" s="41">
         <v>7</v>
       </c>
-      <c r="BU29" s="32"/>
-      <c r="BV29" s="32"/>
-      <c r="BW29" s="32"/>
-      <c r="BX29" s="32"/>
-      <c r="BY29" s="32"/>
-      <c r="BZ29" s="32"/>
-      <c r="CA29" s="32"/>
-      <c r="CB29" s="32"/>
-      <c r="CC29" s="32">
+      <c r="BU29" s="41"/>
+      <c r="BV29" s="41"/>
+      <c r="BW29" s="41"/>
+      <c r="BX29" s="41"/>
+      <c r="BY29" s="41"/>
+      <c r="BZ29" s="41"/>
+      <c r="CA29" s="41"/>
+      <c r="CB29" s="41"/>
+      <c r="CC29" s="41">
         <v>8</v>
       </c>
-      <c r="CD29" s="32"/>
-      <c r="CE29" s="32"/>
-      <c r="CF29" s="32"/>
-      <c r="CG29" s="32"/>
-      <c r="CH29" s="32"/>
-      <c r="CI29" s="32"/>
-      <c r="CJ29" s="32"/>
-      <c r="CK29" s="32"/>
-      <c r="CL29" s="32"/>
-      <c r="CM29" s="32"/>
-      <c r="CN29" s="32">
+      <c r="CD29" s="41"/>
+      <c r="CE29" s="41"/>
+      <c r="CF29" s="41"/>
+      <c r="CG29" s="41"/>
+      <c r="CH29" s="41"/>
+      <c r="CI29" s="41"/>
+      <c r="CJ29" s="41"/>
+      <c r="CK29" s="41"/>
+      <c r="CL29" s="41"/>
+      <c r="CM29" s="41"/>
+      <c r="CN29" s="41">
         <v>9</v>
       </c>
-      <c r="CO29" s="32"/>
-      <c r="CP29" s="32"/>
-      <c r="CQ29" s="32"/>
-      <c r="CR29" s="32"/>
-      <c r="CS29" s="32"/>
-      <c r="CT29" s="32"/>
-      <c r="CU29" s="32"/>
-      <c r="CV29" s="32"/>
+      <c r="CO29" s="41"/>
+      <c r="CP29" s="41"/>
+      <c r="CQ29" s="41"/>
+      <c r="CR29" s="41"/>
+      <c r="CS29" s="41"/>
+      <c r="CT29" s="41"/>
+      <c r="CU29" s="41"/>
+      <c r="CV29" s="41"/>
       <c r="CX29" s="2"/>
       <c r="CY29" s="2"/>
       <c r="CZ29" s="2"/>
@@ -3571,122 +3571,122 @@
       <c r="FQ29" s="2"/>
     </row>
     <row r="30" spans="1:173" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="29"/>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29"/>
-      <c r="P30" s="29"/>
-      <c r="Q30" s="29"/>
-      <c r="R30" s="29"/>
-      <c r="S30" s="29"/>
-      <c r="T30" s="29"/>
-      <c r="U30" s="29"/>
-      <c r="V30" s="30"/>
-      <c r="W30" s="31" t="s">
+      <c r="B30" s="56"/>
+      <c r="C30" s="56"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
+      <c r="F30" s="56"/>
+      <c r="G30" s="56"/>
+      <c r="H30" s="56"/>
+      <c r="I30" s="56"/>
+      <c r="J30" s="56"/>
+      <c r="K30" s="56"/>
+      <c r="L30" s="56"/>
+      <c r="M30" s="56"/>
+      <c r="N30" s="56"/>
+      <c r="O30" s="56"/>
+      <c r="P30" s="56"/>
+      <c r="Q30" s="56"/>
+      <c r="R30" s="56"/>
+      <c r="S30" s="56"/>
+      <c r="T30" s="56"/>
+      <c r="U30" s="56"/>
+      <c r="V30" s="57"/>
+      <c r="W30" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="X30" s="31"/>
-      <c r="Y30" s="31"/>
-      <c r="Z30" s="31"/>
-      <c r="AA30" s="31"/>
-      <c r="AB30" s="31"/>
-      <c r="AC30" s="31"/>
-      <c r="AD30" s="31"/>
-      <c r="AE30" s="31"/>
-      <c r="AF30" s="31"/>
-      <c r="AG30" s="25" t="s">
+      <c r="X30" s="58"/>
+      <c r="Y30" s="58"/>
+      <c r="Z30" s="58"/>
+      <c r="AA30" s="58"/>
+      <c r="AB30" s="58"/>
+      <c r="AC30" s="58"/>
+      <c r="AD30" s="58"/>
+      <c r="AE30" s="58"/>
+      <c r="AF30" s="58"/>
+      <c r="AG30" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="AH30" s="25"/>
-      <c r="AI30" s="25"/>
-      <c r="AJ30" s="25"/>
-      <c r="AK30" s="25"/>
-      <c r="AL30" s="25"/>
-      <c r="AM30" s="25"/>
-      <c r="AN30" s="25"/>
-      <c r="AO30" s="25"/>
-      <c r="AP30" s="25" t="s">
+      <c r="AH30" s="49"/>
+      <c r="AI30" s="49"/>
+      <c r="AJ30" s="49"/>
+      <c r="AK30" s="49"/>
+      <c r="AL30" s="49"/>
+      <c r="AM30" s="49"/>
+      <c r="AN30" s="49"/>
+      <c r="AO30" s="49"/>
+      <c r="AP30" s="49" t="s">
         <v>49</v>
       </c>
-      <c r="AQ30" s="25"/>
-      <c r="AR30" s="25"/>
-      <c r="AS30" s="25"/>
-      <c r="AT30" s="25"/>
-      <c r="AU30" s="25"/>
-      <c r="AV30" s="25"/>
-      <c r="AW30" s="25"/>
-      <c r="AX30" s="25"/>
-      <c r="AY30" s="25"/>
-      <c r="AZ30" s="25" t="s">
+      <c r="AQ30" s="49"/>
+      <c r="AR30" s="49"/>
+      <c r="AS30" s="49"/>
+      <c r="AT30" s="49"/>
+      <c r="AU30" s="49"/>
+      <c r="AV30" s="49"/>
+      <c r="AW30" s="49"/>
+      <c r="AX30" s="49"/>
+      <c r="AY30" s="49"/>
+      <c r="AZ30" s="49" t="s">
         <v>50</v>
       </c>
-      <c r="BA30" s="25"/>
-      <c r="BB30" s="25"/>
-      <c r="BC30" s="25"/>
-      <c r="BD30" s="25"/>
-      <c r="BE30" s="25"/>
-      <c r="BF30" s="25"/>
-      <c r="BG30" s="25"/>
-      <c r="BH30" s="25"/>
-      <c r="BI30" s="25"/>
-      <c r="BJ30" s="25"/>
-      <c r="BK30" s="34" t="s">
+      <c r="BA30" s="49"/>
+      <c r="BB30" s="49"/>
+      <c r="BC30" s="49"/>
+      <c r="BD30" s="49"/>
+      <c r="BE30" s="49"/>
+      <c r="BF30" s="49"/>
+      <c r="BG30" s="49"/>
+      <c r="BH30" s="49"/>
+      <c r="BI30" s="49"/>
+      <c r="BJ30" s="49"/>
+      <c r="BK30" s="43" t="s">
         <v>51</v>
       </c>
-      <c r="BL30" s="34"/>
-      <c r="BM30" s="34"/>
-      <c r="BN30" s="34"/>
-      <c r="BO30" s="34"/>
-      <c r="BP30" s="34"/>
-      <c r="BQ30" s="34"/>
-      <c r="BR30" s="34"/>
-      <c r="BS30" s="34"/>
-      <c r="BT30" s="26" t="s">
+      <c r="BL30" s="43"/>
+      <c r="BM30" s="43"/>
+      <c r="BN30" s="43"/>
+      <c r="BO30" s="43"/>
+      <c r="BP30" s="43"/>
+      <c r="BQ30" s="43"/>
+      <c r="BR30" s="43"/>
+      <c r="BS30" s="43"/>
+      <c r="BT30" s="50" t="s">
         <v>52</v>
       </c>
-      <c r="BU30" s="25"/>
-      <c r="BV30" s="25"/>
-      <c r="BW30" s="25"/>
-      <c r="BX30" s="25"/>
-      <c r="BY30" s="25"/>
-      <c r="BZ30" s="25"/>
-      <c r="CA30" s="25"/>
-      <c r="CB30" s="25"/>
-      <c r="CC30" s="27" t="s">
+      <c r="BU30" s="49"/>
+      <c r="BV30" s="49"/>
+      <c r="BW30" s="49"/>
+      <c r="BX30" s="49"/>
+      <c r="BY30" s="49"/>
+      <c r="BZ30" s="49"/>
+      <c r="CA30" s="49"/>
+      <c r="CB30" s="49"/>
+      <c r="CC30" s="54" t="s">
         <v>53</v>
       </c>
-      <c r="CD30" s="25"/>
-      <c r="CE30" s="25"/>
-      <c r="CF30" s="25"/>
-      <c r="CG30" s="25"/>
-      <c r="CH30" s="25"/>
-      <c r="CI30" s="25"/>
-      <c r="CJ30" s="25"/>
-      <c r="CK30" s="25"/>
-      <c r="CL30" s="25"/>
-      <c r="CM30" s="25"/>
-      <c r="CN30" s="36"/>
-      <c r="CO30" s="36"/>
-      <c r="CP30" s="36"/>
-      <c r="CQ30" s="36"/>
-      <c r="CR30" s="36"/>
-      <c r="CS30" s="36"/>
-      <c r="CT30" s="36"/>
-      <c r="CU30" s="36"/>
-      <c r="CV30" s="36"/>
+      <c r="CD30" s="49"/>
+      <c r="CE30" s="49"/>
+      <c r="CF30" s="49"/>
+      <c r="CG30" s="49"/>
+      <c r="CH30" s="49"/>
+      <c r="CI30" s="49"/>
+      <c r="CJ30" s="49"/>
+      <c r="CK30" s="49"/>
+      <c r="CL30" s="49"/>
+      <c r="CM30" s="49"/>
+      <c r="CN30" s="40"/>
+      <c r="CO30" s="40"/>
+      <c r="CP30" s="40"/>
+      <c r="CQ30" s="40"/>
+      <c r="CR30" s="40"/>
+      <c r="CS30" s="40"/>
+      <c r="CT30" s="40"/>
+      <c r="CU30" s="40"/>
+      <c r="CV30" s="40"/>
       <c r="CX30" s="2"/>
       <c r="CY30" s="2"/>
       <c r="CZ30" s="2"/>
@@ -3761,124 +3761,124 @@
       <c r="FQ30" s="2"/>
     </row>
     <row r="31" spans="1:173" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="35" t="s">
+      <c r="A31" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="B31" s="35"/>
-      <c r="C31" s="35"/>
-      <c r="D31" s="35"/>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="35"/>
-      <c r="I31" s="35"/>
-      <c r="J31" s="35"/>
-      <c r="K31" s="35"/>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="36" t="s">
+      <c r="B31" s="51"/>
+      <c r="C31" s="51"/>
+      <c r="D31" s="51"/>
+      <c r="E31" s="51"/>
+      <c r="F31" s="51"/>
+      <c r="G31" s="51"/>
+      <c r="H31" s="51"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
+      <c r="K31" s="51"/>
+      <c r="L31" s="51"/>
+      <c r="M31" s="51"/>
+      <c r="N31" s="51"/>
+      <c r="O31" s="51"/>
+      <c r="P31" s="51"/>
+      <c r="Q31" s="51"/>
+      <c r="R31" s="51"/>
+      <c r="S31" s="51"/>
+      <c r="T31" s="51"/>
+      <c r="U31" s="51"/>
+      <c r="V31" s="51"/>
+      <c r="W31" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="X31" s="36"/>
-      <c r="Y31" s="36"/>
-      <c r="Z31" s="36"/>
-      <c r="AA31" s="36"/>
-      <c r="AB31" s="36"/>
-      <c r="AC31" s="36"/>
-      <c r="AD31" s="36"/>
-      <c r="AE31" s="36"/>
-      <c r="AF31" s="36"/>
-      <c r="AG31" s="25" t="s">
+      <c r="X31" s="40"/>
+      <c r="Y31" s="40"/>
+      <c r="Z31" s="40"/>
+      <c r="AA31" s="40"/>
+      <c r="AB31" s="40"/>
+      <c r="AC31" s="40"/>
+      <c r="AD31" s="40"/>
+      <c r="AE31" s="40"/>
+      <c r="AF31" s="40"/>
+      <c r="AG31" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="AH31" s="25"/>
-      <c r="AI31" s="25"/>
-      <c r="AJ31" s="25"/>
-      <c r="AK31" s="25"/>
-      <c r="AL31" s="25"/>
-      <c r="AM31" s="25"/>
-      <c r="AN31" s="25"/>
-      <c r="AO31" s="25"/>
-      <c r="AP31" s="36" t="s">
+      <c r="AH31" s="49"/>
+      <c r="AI31" s="49"/>
+      <c r="AJ31" s="49"/>
+      <c r="AK31" s="49"/>
+      <c r="AL31" s="49"/>
+      <c r="AM31" s="49"/>
+      <c r="AN31" s="49"/>
+      <c r="AO31" s="49"/>
+      <c r="AP31" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="AQ31" s="36"/>
-      <c r="AR31" s="36"/>
-      <c r="AS31" s="36"/>
-      <c r="AT31" s="36"/>
-      <c r="AU31" s="36"/>
-      <c r="AV31" s="36"/>
-      <c r="AW31" s="36"/>
-      <c r="AX31" s="36"/>
-      <c r="AY31" s="36"/>
-      <c r="AZ31" s="25" t="s">
+      <c r="AQ31" s="40"/>
+      <c r="AR31" s="40"/>
+      <c r="AS31" s="40"/>
+      <c r="AT31" s="40"/>
+      <c r="AU31" s="40"/>
+      <c r="AV31" s="40"/>
+      <c r="AW31" s="40"/>
+      <c r="AX31" s="40"/>
+      <c r="AY31" s="40"/>
+      <c r="AZ31" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="BA31" s="25"/>
-      <c r="BB31" s="25"/>
-      <c r="BC31" s="25"/>
-      <c r="BD31" s="25"/>
-      <c r="BE31" s="25"/>
-      <c r="BF31" s="25"/>
-      <c r="BG31" s="25"/>
-      <c r="BH31" s="25"/>
-      <c r="BI31" s="25"/>
-      <c r="BJ31" s="25"/>
-      <c r="BK31" s="34" t="s">
+      <c r="BA31" s="49"/>
+      <c r="BB31" s="49"/>
+      <c r="BC31" s="49"/>
+      <c r="BD31" s="49"/>
+      <c r="BE31" s="49"/>
+      <c r="BF31" s="49"/>
+      <c r="BG31" s="49"/>
+      <c r="BH31" s="49"/>
+      <c r="BI31" s="49"/>
+      <c r="BJ31" s="49"/>
+      <c r="BK31" s="43" t="s">
         <v>24</v>
       </c>
-      <c r="BL31" s="34"/>
-      <c r="BM31" s="34"/>
-      <c r="BN31" s="34"/>
-      <c r="BO31" s="34"/>
-      <c r="BP31" s="34"/>
-      <c r="BQ31" s="34"/>
-      <c r="BR31" s="34"/>
-      <c r="BS31" s="34"/>
-      <c r="BT31" s="26" t="s">
+      <c r="BL31" s="43"/>
+      <c r="BM31" s="43"/>
+      <c r="BN31" s="43"/>
+      <c r="BO31" s="43"/>
+      <c r="BP31" s="43"/>
+      <c r="BQ31" s="43"/>
+      <c r="BR31" s="43"/>
+      <c r="BS31" s="43"/>
+      <c r="BT31" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="BU31" s="25"/>
-      <c r="BV31" s="25"/>
-      <c r="BW31" s="25"/>
-      <c r="BX31" s="25"/>
-      <c r="BY31" s="25"/>
-      <c r="BZ31" s="25"/>
-      <c r="CA31" s="25"/>
-      <c r="CB31" s="25"/>
-      <c r="CC31" s="25" t="s">
+      <c r="BU31" s="49"/>
+      <c r="BV31" s="49"/>
+      <c r="BW31" s="49"/>
+      <c r="BX31" s="49"/>
+      <c r="BY31" s="49"/>
+      <c r="BZ31" s="49"/>
+      <c r="CA31" s="49"/>
+      <c r="CB31" s="49"/>
+      <c r="CC31" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="CD31" s="25"/>
-      <c r="CE31" s="25"/>
-      <c r="CF31" s="25"/>
-      <c r="CG31" s="25"/>
-      <c r="CH31" s="25"/>
-      <c r="CI31" s="25"/>
-      <c r="CJ31" s="25"/>
-      <c r="CK31" s="25"/>
-      <c r="CL31" s="25"/>
-      <c r="CM31" s="25"/>
-      <c r="CN31" s="36" t="s">
+      <c r="CD31" s="49"/>
+      <c r="CE31" s="49"/>
+      <c r="CF31" s="49"/>
+      <c r="CG31" s="49"/>
+      <c r="CH31" s="49"/>
+      <c r="CI31" s="49"/>
+      <c r="CJ31" s="49"/>
+      <c r="CK31" s="49"/>
+      <c r="CL31" s="49"/>
+      <c r="CM31" s="49"/>
+      <c r="CN31" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="CO31" s="36"/>
-      <c r="CP31" s="36"/>
-      <c r="CQ31" s="36"/>
-      <c r="CR31" s="36"/>
-      <c r="CS31" s="36"/>
-      <c r="CT31" s="36"/>
-      <c r="CU31" s="36"/>
-      <c r="CV31" s="36"/>
+      <c r="CO31" s="40"/>
+      <c r="CP31" s="40"/>
+      <c r="CQ31" s="40"/>
+      <c r="CR31" s="40"/>
+      <c r="CS31" s="40"/>
+      <c r="CT31" s="40"/>
+      <c r="CU31" s="40"/>
+      <c r="CV31" s="40"/>
       <c r="CX31" s="2"/>
       <c r="CY31" s="2"/>
       <c r="CZ31" s="2"/>
@@ -3953,106 +3953,106 @@
       <c r="FQ31" s="2"/>
     </row>
     <row r="32" spans="1:173" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="22"/>
-      <c r="B32" s="22"/>
-      <c r="C32" s="22"/>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="22"/>
-      <c r="S32" s="22"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
-      <c r="W32" s="22"/>
-      <c r="X32" s="22"/>
-      <c r="Y32" s="22"/>
-      <c r="Z32" s="22"/>
-      <c r="AA32" s="22"/>
-      <c r="AB32" s="22"/>
-      <c r="AC32" s="22"/>
-      <c r="AD32" s="22"/>
-      <c r="AE32" s="22"/>
-      <c r="AF32" s="22"/>
-      <c r="AG32" s="22"/>
-      <c r="AH32" s="22"/>
-      <c r="AI32" s="22"/>
-      <c r="AJ32" s="22"/>
-      <c r="AK32" s="22"/>
-      <c r="AL32" s="22"/>
-      <c r="AM32" s="22"/>
-      <c r="AN32" s="22"/>
-      <c r="AO32" s="22"/>
-      <c r="AP32" s="22"/>
-      <c r="AQ32" s="22"/>
-      <c r="AR32" s="22"/>
-      <c r="AS32" s="22"/>
-      <c r="AT32" s="22"/>
-      <c r="AU32" s="22"/>
-      <c r="AV32" s="22"/>
-      <c r="AW32" s="22"/>
-      <c r="AX32" s="22"/>
-      <c r="AY32" s="22"/>
-      <c r="AZ32" s="22"/>
-      <c r="BA32" s="22"/>
-      <c r="BB32" s="22"/>
-      <c r="BC32" s="22"/>
-      <c r="BD32" s="22"/>
-      <c r="BE32" s="22"/>
-      <c r="BF32" s="22"/>
-      <c r="BG32" s="22"/>
-      <c r="BH32" s="22"/>
-      <c r="BI32" s="22"/>
-      <c r="BJ32" s="22"/>
-      <c r="BK32" s="22"/>
-      <c r="BL32" s="22"/>
-      <c r="BM32" s="22"/>
-      <c r="BN32" s="22"/>
-      <c r="BO32" s="22"/>
-      <c r="BP32" s="22"/>
-      <c r="BQ32" s="22"/>
-      <c r="BR32" s="22"/>
-      <c r="BS32" s="22"/>
-      <c r="BT32" s="22"/>
-      <c r="BU32" s="22"/>
-      <c r="BV32" s="22"/>
-      <c r="BW32" s="22"/>
-      <c r="BX32" s="22"/>
-      <c r="BY32" s="22"/>
-      <c r="BZ32" s="22"/>
-      <c r="CA32" s="22"/>
-      <c r="CB32" s="22"/>
-      <c r="CC32" s="22"/>
-      <c r="CD32" s="22"/>
-      <c r="CE32" s="22"/>
-      <c r="CF32" s="22"/>
-      <c r="CG32" s="22"/>
-      <c r="CH32" s="22"/>
-      <c r="CI32" s="22"/>
-      <c r="CJ32" s="22"/>
-      <c r="CK32" s="22"/>
-      <c r="CL32" s="22"/>
-      <c r="CM32" s="22"/>
-      <c r="CN32" s="22"/>
-      <c r="CO32" s="22"/>
-      <c r="CP32" s="22"/>
-      <c r="CQ32" s="22"/>
-      <c r="CR32" s="22"/>
-      <c r="CS32" s="22"/>
-      <c r="CT32" s="22"/>
-      <c r="CU32" s="22"/>
-      <c r="CV32" s="22"/>
+      <c r="A32" s="60"/>
+      <c r="B32" s="60"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
+      <c r="J32" s="60"/>
+      <c r="K32" s="60"/>
+      <c r="L32" s="60"/>
+      <c r="M32" s="60"/>
+      <c r="N32" s="60"/>
+      <c r="O32" s="60"/>
+      <c r="P32" s="60"/>
+      <c r="Q32" s="60"/>
+      <c r="R32" s="60"/>
+      <c r="S32" s="60"/>
+      <c r="T32" s="60"/>
+      <c r="U32" s="60"/>
+      <c r="V32" s="60"/>
+      <c r="W32" s="60"/>
+      <c r="X32" s="60"/>
+      <c r="Y32" s="60"/>
+      <c r="Z32" s="60"/>
+      <c r="AA32" s="60"/>
+      <c r="AB32" s="60"/>
+      <c r="AC32" s="60"/>
+      <c r="AD32" s="60"/>
+      <c r="AE32" s="60"/>
+      <c r="AF32" s="60"/>
+      <c r="AG32" s="60"/>
+      <c r="AH32" s="60"/>
+      <c r="AI32" s="60"/>
+      <c r="AJ32" s="60"/>
+      <c r="AK32" s="60"/>
+      <c r="AL32" s="60"/>
+      <c r="AM32" s="60"/>
+      <c r="AN32" s="60"/>
+      <c r="AO32" s="60"/>
+      <c r="AP32" s="60"/>
+      <c r="AQ32" s="60"/>
+      <c r="AR32" s="60"/>
+      <c r="AS32" s="60"/>
+      <c r="AT32" s="60"/>
+      <c r="AU32" s="60"/>
+      <c r="AV32" s="60"/>
+      <c r="AW32" s="60"/>
+      <c r="AX32" s="60"/>
+      <c r="AY32" s="60"/>
+      <c r="AZ32" s="60"/>
+      <c r="BA32" s="60"/>
+      <c r="BB32" s="60"/>
+      <c r="BC32" s="60"/>
+      <c r="BD32" s="60"/>
+      <c r="BE32" s="60"/>
+      <c r="BF32" s="60"/>
+      <c r="BG32" s="60"/>
+      <c r="BH32" s="60"/>
+      <c r="BI32" s="60"/>
+      <c r="BJ32" s="60"/>
+      <c r="BK32" s="60"/>
+      <c r="BL32" s="60"/>
+      <c r="BM32" s="60"/>
+      <c r="BN32" s="60"/>
+      <c r="BO32" s="60"/>
+      <c r="BP32" s="60"/>
+      <c r="BQ32" s="60"/>
+      <c r="BR32" s="60"/>
+      <c r="BS32" s="60"/>
+      <c r="BT32" s="60"/>
+      <c r="BU32" s="60"/>
+      <c r="BV32" s="60"/>
+      <c r="BW32" s="60"/>
+      <c r="BX32" s="60"/>
+      <c r="BY32" s="60"/>
+      <c r="BZ32" s="60"/>
+      <c r="CA32" s="60"/>
+      <c r="CB32" s="60"/>
+      <c r="CC32" s="60"/>
+      <c r="CD32" s="60"/>
+      <c r="CE32" s="60"/>
+      <c r="CF32" s="60"/>
+      <c r="CG32" s="60"/>
+      <c r="CH32" s="60"/>
+      <c r="CI32" s="60"/>
+      <c r="CJ32" s="60"/>
+      <c r="CK32" s="60"/>
+      <c r="CL32" s="60"/>
+      <c r="CM32" s="60"/>
+      <c r="CN32" s="60"/>
+      <c r="CO32" s="60"/>
+      <c r="CP32" s="60"/>
+      <c r="CQ32" s="60"/>
+      <c r="CR32" s="60"/>
+      <c r="CS32" s="60"/>
+      <c r="CT32" s="60"/>
+      <c r="CU32" s="60"/>
+      <c r="CV32" s="60"/>
       <c r="CX32" s="2"/>
       <c r="CY32" s="2"/>
       <c r="CZ32" s="2"/>
@@ -4127,78 +4127,78 @@
       <c r="FQ32" s="2"/>
     </row>
     <row r="33" spans="1:173" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="24" t="s">
+      <c r="A33" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="24"/>
-      <c r="C33" s="24"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="24"/>
-      <c r="F33" s="24"/>
-      <c r="G33" s="24"/>
-      <c r="H33" s="24"/>
-      <c r="I33" s="24"/>
-      <c r="J33" s="24"/>
-      <c r="K33" s="24"/>
-      <c r="L33" s="24"/>
-      <c r="M33" s="24"/>
-      <c r="N33" s="24"/>
-      <c r="O33" s="24"/>
-      <c r="P33" s="24"/>
-      <c r="Q33" s="24"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="62"/>
+      <c r="K33" s="62"/>
+      <c r="L33" s="62"/>
+      <c r="M33" s="62"/>
+      <c r="N33" s="62"/>
+      <c r="O33" s="62"/>
+      <c r="P33" s="62"/>
+      <c r="Q33" s="62"/>
       <c r="R33" s="8"/>
-      <c r="S33" s="17" t="s">
+      <c r="S33" s="61" t="s">
         <v>42</v>
       </c>
-      <c r="T33" s="17"/>
-      <c r="U33" s="17"/>
-      <c r="V33" s="17"/>
-      <c r="W33" s="17"/>
-      <c r="X33" s="17"/>
-      <c r="Y33" s="17"/>
-      <c r="Z33" s="17"/>
-      <c r="AA33" s="17"/>
-      <c r="AB33" s="17"/>
-      <c r="AC33" s="17"/>
-      <c r="AD33" s="17"/>
-      <c r="AE33" s="17"/>
-      <c r="AF33" s="17"/>
-      <c r="AG33" s="17"/>
-      <c r="AH33" s="17"/>
-      <c r="AI33" s="17"/>
-      <c r="AJ33" s="17"/>
-      <c r="AK33" s="17"/>
-      <c r="AL33" s="17"/>
-      <c r="AM33" s="17"/>
-      <c r="AN33" s="17"/>
-      <c r="AO33" s="17"/>
-      <c r="AP33" s="17"/>
-      <c r="AQ33" s="17"/>
-      <c r="AR33" s="17"/>
-      <c r="AS33" s="17"/>
-      <c r="AT33" s="17"/>
-      <c r="AU33" s="17"/>
-      <c r="AV33" s="17"/>
-      <c r="AW33" s="17"/>
-      <c r="AX33" s="17"/>
-      <c r="AY33" s="17"/>
-      <c r="AZ33" s="17"/>
-      <c r="BA33" s="17"/>
-      <c r="BB33" s="17"/>
-      <c r="BC33" s="17"/>
-      <c r="BD33" s="17"/>
-      <c r="BE33" s="17"/>
-      <c r="BF33" s="17"/>
-      <c r="BG33" s="17"/>
-      <c r="BH33" s="17"/>
-      <c r="BI33" s="17"/>
-      <c r="BJ33" s="17"/>
-      <c r="BK33" s="17"/>
-      <c r="BL33" s="17"/>
-      <c r="BM33" s="17"/>
-      <c r="BN33" s="17"/>
-      <c r="BO33" s="17"/>
-      <c r="BP33" s="17"/>
+      <c r="T33" s="61"/>
+      <c r="U33" s="61"/>
+      <c r="V33" s="61"/>
+      <c r="W33" s="61"/>
+      <c r="X33" s="61"/>
+      <c r="Y33" s="61"/>
+      <c r="Z33" s="61"/>
+      <c r="AA33" s="61"/>
+      <c r="AB33" s="61"/>
+      <c r="AC33" s="61"/>
+      <c r="AD33" s="61"/>
+      <c r="AE33" s="61"/>
+      <c r="AF33" s="61"/>
+      <c r="AG33" s="61"/>
+      <c r="AH33" s="61"/>
+      <c r="AI33" s="61"/>
+      <c r="AJ33" s="61"/>
+      <c r="AK33" s="61"/>
+      <c r="AL33" s="61"/>
+      <c r="AM33" s="61"/>
+      <c r="AN33" s="61"/>
+      <c r="AO33" s="61"/>
+      <c r="AP33" s="61"/>
+      <c r="AQ33" s="61"/>
+      <c r="AR33" s="61"/>
+      <c r="AS33" s="61"/>
+      <c r="AT33" s="61"/>
+      <c r="AU33" s="61"/>
+      <c r="AV33" s="61"/>
+      <c r="AW33" s="61"/>
+      <c r="AX33" s="61"/>
+      <c r="AY33" s="61"/>
+      <c r="AZ33" s="61"/>
+      <c r="BA33" s="61"/>
+      <c r="BB33" s="61"/>
+      <c r="BC33" s="61"/>
+      <c r="BD33" s="61"/>
+      <c r="BE33" s="61"/>
+      <c r="BF33" s="61"/>
+      <c r="BG33" s="61"/>
+      <c r="BH33" s="61"/>
+      <c r="BI33" s="61"/>
+      <c r="BJ33" s="61"/>
+      <c r="BK33" s="61"/>
+      <c r="BL33" s="61"/>
+      <c r="BM33" s="61"/>
+      <c r="BN33" s="61"/>
+      <c r="BO33" s="61"/>
+      <c r="BP33" s="61"/>
       <c r="BQ33" s="8"/>
       <c r="BR33" s="8" t="s">
         <v>29</v>
@@ -4208,25 +4208,25 @@
       <c r="BU33" s="8"/>
       <c r="BV33" s="8"/>
       <c r="BW33" s="8"/>
-      <c r="BX33" s="17"/>
-      <c r="BY33" s="17"/>
-      <c r="BZ33" s="17"/>
-      <c r="CA33" s="17"/>
-      <c r="CB33" s="17"/>
-      <c r="CC33" s="17"/>
-      <c r="CD33" s="17"/>
-      <c r="CE33" s="17"/>
-      <c r="CF33" s="17"/>
-      <c r="CG33" s="17"/>
-      <c r="CH33" s="17"/>
-      <c r="CI33" s="17"/>
-      <c r="CJ33" s="17"/>
-      <c r="CK33" s="17"/>
-      <c r="CL33" s="17"/>
-      <c r="CM33" s="17"/>
-      <c r="CN33" s="17"/>
-      <c r="CO33" s="17"/>
-      <c r="CP33" s="17"/>
+      <c r="BX33" s="61"/>
+      <c r="BY33" s="61"/>
+      <c r="BZ33" s="61"/>
+      <c r="CA33" s="61"/>
+      <c r="CB33" s="61"/>
+      <c r="CC33" s="61"/>
+      <c r="CD33" s="61"/>
+      <c r="CE33" s="61"/>
+      <c r="CF33" s="61"/>
+      <c r="CG33" s="61"/>
+      <c r="CH33" s="61"/>
+      <c r="CI33" s="61"/>
+      <c r="CJ33" s="61"/>
+      <c r="CK33" s="61"/>
+      <c r="CL33" s="61"/>
+      <c r="CM33" s="61"/>
+      <c r="CN33" s="61"/>
+      <c r="CO33" s="61"/>
+      <c r="CP33" s="61"/>
       <c r="CQ33" s="8"/>
       <c r="CR33" s="8" t="s">
         <v>28</v>
@@ -4327,58 +4327,58 @@
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="10"/>
-      <c r="S34" s="16" t="s">
+      <c r="S34" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
-      <c r="AA34" s="16"/>
-      <c r="AB34" s="16"/>
-      <c r="AC34" s="16"/>
-      <c r="AD34" s="16"/>
-      <c r="AE34" s="16"/>
-      <c r="AF34" s="16"/>
-      <c r="AG34" s="16"/>
-      <c r="AH34" s="16"/>
-      <c r="AI34" s="16"/>
-      <c r="AJ34" s="16"/>
-      <c r="AK34" s="16"/>
-      <c r="AL34" s="16"/>
-      <c r="AM34" s="16"/>
-      <c r="AN34" s="16"/>
-      <c r="AO34" s="16"/>
-      <c r="AP34" s="16"/>
-      <c r="AQ34" s="16"/>
-      <c r="AR34" s="16"/>
-      <c r="AS34" s="16"/>
-      <c r="AT34" s="16"/>
-      <c r="AU34" s="16"/>
-      <c r="AV34" s="16"/>
-      <c r="AW34" s="16"/>
-      <c r="AX34" s="16"/>
-      <c r="AY34" s="16"/>
-      <c r="AZ34" s="16"/>
-      <c r="BA34" s="16"/>
-      <c r="BB34" s="16"/>
-      <c r="BC34" s="16"/>
-      <c r="BD34" s="16"/>
-      <c r="BE34" s="16"/>
-      <c r="BF34" s="16"/>
-      <c r="BG34" s="16"/>
-      <c r="BH34" s="16"/>
-      <c r="BI34" s="16"/>
-      <c r="BJ34" s="16"/>
-      <c r="BK34" s="16"/>
-      <c r="BL34" s="16"/>
-      <c r="BM34" s="16"/>
-      <c r="BN34" s="16"/>
-      <c r="BO34" s="16"/>
-      <c r="BP34" s="16"/>
+      <c r="T34" s="53"/>
+      <c r="U34" s="53"/>
+      <c r="V34" s="53"/>
+      <c r="W34" s="53"/>
+      <c r="X34" s="53"/>
+      <c r="Y34" s="53"/>
+      <c r="Z34" s="53"/>
+      <c r="AA34" s="53"/>
+      <c r="AB34" s="53"/>
+      <c r="AC34" s="53"/>
+      <c r="AD34" s="53"/>
+      <c r="AE34" s="53"/>
+      <c r="AF34" s="53"/>
+      <c r="AG34" s="53"/>
+      <c r="AH34" s="53"/>
+      <c r="AI34" s="53"/>
+      <c r="AJ34" s="53"/>
+      <c r="AK34" s="53"/>
+      <c r="AL34" s="53"/>
+      <c r="AM34" s="53"/>
+      <c r="AN34" s="53"/>
+      <c r="AO34" s="53"/>
+      <c r="AP34" s="53"/>
+      <c r="AQ34" s="53"/>
+      <c r="AR34" s="53"/>
+      <c r="AS34" s="53"/>
+      <c r="AT34" s="53"/>
+      <c r="AU34" s="53"/>
+      <c r="AV34" s="53"/>
+      <c r="AW34" s="53"/>
+      <c r="AX34" s="53"/>
+      <c r="AY34" s="53"/>
+      <c r="AZ34" s="53"/>
+      <c r="BA34" s="53"/>
+      <c r="BB34" s="53"/>
+      <c r="BC34" s="53"/>
+      <c r="BD34" s="53"/>
+      <c r="BE34" s="53"/>
+      <c r="BF34" s="53"/>
+      <c r="BG34" s="53"/>
+      <c r="BH34" s="53"/>
+      <c r="BI34" s="53"/>
+      <c r="BJ34" s="53"/>
+      <c r="BK34" s="53"/>
+      <c r="BL34" s="53"/>
+      <c r="BM34" s="53"/>
+      <c r="BN34" s="53"/>
+      <c r="BO34" s="53"/>
+      <c r="BP34" s="53"/>
       <c r="BQ34" s="10"/>
       <c r="BR34" s="10"/>
       <c r="BS34" s="10"/>
@@ -4386,27 +4386,27 @@
       <c r="BU34" s="10"/>
       <c r="BV34" s="10"/>
       <c r="BW34" s="10"/>
-      <c r="BX34" s="16" t="s">
+      <c r="BX34" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="BY34" s="16"/>
-      <c r="BZ34" s="16"/>
-      <c r="CA34" s="16"/>
-      <c r="CB34" s="16"/>
-      <c r="CC34" s="16"/>
-      <c r="CD34" s="16"/>
-      <c r="CE34" s="16"/>
-      <c r="CF34" s="16"/>
-      <c r="CG34" s="16"/>
-      <c r="CH34" s="16"/>
-      <c r="CI34" s="16"/>
-      <c r="CJ34" s="16"/>
-      <c r="CK34" s="16"/>
-      <c r="CL34" s="16"/>
-      <c r="CM34" s="16"/>
-      <c r="CN34" s="16"/>
-      <c r="CO34" s="16"/>
-      <c r="CP34" s="16"/>
+      <c r="BY34" s="53"/>
+      <c r="BZ34" s="53"/>
+      <c r="CA34" s="53"/>
+      <c r="CB34" s="53"/>
+      <c r="CC34" s="53"/>
+      <c r="CD34" s="53"/>
+      <c r="CE34" s="53"/>
+      <c r="CF34" s="53"/>
+      <c r="CG34" s="53"/>
+      <c r="CH34" s="53"/>
+      <c r="CI34" s="53"/>
+      <c r="CJ34" s="53"/>
+      <c r="CK34" s="53"/>
+      <c r="CL34" s="53"/>
+      <c r="CM34" s="53"/>
+      <c r="CN34" s="53"/>
+      <c r="CO34" s="53"/>
+      <c r="CP34" s="53"/>
       <c r="CQ34" s="10"/>
       <c r="CR34" s="10"/>
       <c r="CS34" s="10"/>
@@ -4541,54 +4541,54 @@
       <c r="T36" s="12"/>
       <c r="U36" s="12"/>
       <c r="V36" s="12"/>
-      <c r="W36" s="17" t="s">
+      <c r="W36" s="61" t="s">
         <v>43</v>
       </c>
-      <c r="X36" s="17"/>
-      <c r="Y36" s="17"/>
-      <c r="Z36" s="17"/>
-      <c r="AA36" s="17"/>
-      <c r="AB36" s="17"/>
-      <c r="AC36" s="17"/>
-      <c r="AD36" s="17"/>
-      <c r="AE36" s="17"/>
-      <c r="AF36" s="17"/>
-      <c r="AG36" s="17"/>
-      <c r="AH36" s="17"/>
-      <c r="AI36" s="17"/>
-      <c r="AJ36" s="17"/>
-      <c r="AK36" s="17"/>
-      <c r="AL36" s="17"/>
-      <c r="AM36" s="17"/>
-      <c r="AN36" s="17"/>
-      <c r="AO36" s="17"/>
-      <c r="AP36" s="17"/>
-      <c r="AQ36" s="17"/>
-      <c r="AR36" s="17"/>
-      <c r="AS36" s="17"/>
-      <c r="AT36" s="17"/>
-      <c r="AU36" s="17"/>
-      <c r="AV36" s="17"/>
-      <c r="AW36" s="17"/>
-      <c r="AX36" s="17"/>
-      <c r="AY36" s="17"/>
-      <c r="AZ36" s="17"/>
-      <c r="BA36" s="17"/>
-      <c r="BB36" s="17"/>
-      <c r="BC36" s="17"/>
-      <c r="BD36" s="17"/>
-      <c r="BE36" s="17"/>
-      <c r="BF36" s="17"/>
-      <c r="BG36" s="17"/>
-      <c r="BH36" s="17"/>
-      <c r="BI36" s="17"/>
-      <c r="BJ36" s="17"/>
-      <c r="BK36" s="17"/>
-      <c r="BL36" s="17"/>
-      <c r="BM36" s="17"/>
-      <c r="BN36" s="17"/>
-      <c r="BO36" s="17"/>
-      <c r="BP36" s="17"/>
+      <c r="X36" s="61"/>
+      <c r="Y36" s="61"/>
+      <c r="Z36" s="61"/>
+      <c r="AA36" s="61"/>
+      <c r="AB36" s="61"/>
+      <c r="AC36" s="61"/>
+      <c r="AD36" s="61"/>
+      <c r="AE36" s="61"/>
+      <c r="AF36" s="61"/>
+      <c r="AG36" s="61"/>
+      <c r="AH36" s="61"/>
+      <c r="AI36" s="61"/>
+      <c r="AJ36" s="61"/>
+      <c r="AK36" s="61"/>
+      <c r="AL36" s="61"/>
+      <c r="AM36" s="61"/>
+      <c r="AN36" s="61"/>
+      <c r="AO36" s="61"/>
+      <c r="AP36" s="61"/>
+      <c r="AQ36" s="61"/>
+      <c r="AR36" s="61"/>
+      <c r="AS36" s="61"/>
+      <c r="AT36" s="61"/>
+      <c r="AU36" s="61"/>
+      <c r="AV36" s="61"/>
+      <c r="AW36" s="61"/>
+      <c r="AX36" s="61"/>
+      <c r="AY36" s="61"/>
+      <c r="AZ36" s="61"/>
+      <c r="BA36" s="61"/>
+      <c r="BB36" s="61"/>
+      <c r="BC36" s="61"/>
+      <c r="BD36" s="61"/>
+      <c r="BE36" s="61"/>
+      <c r="BF36" s="61"/>
+      <c r="BG36" s="61"/>
+      <c r="BH36" s="61"/>
+      <c r="BI36" s="61"/>
+      <c r="BJ36" s="61"/>
+      <c r="BK36" s="61"/>
+      <c r="BL36" s="61"/>
+      <c r="BM36" s="61"/>
+      <c r="BN36" s="61"/>
+      <c r="BO36" s="61"/>
+      <c r="BP36" s="61"/>
       <c r="BQ36" s="8"/>
       <c r="BR36" s="8" t="s">
         <v>29</v>
@@ -4598,25 +4598,25 @@
       <c r="BU36" s="8"/>
       <c r="BV36" s="8"/>
       <c r="BW36" s="8"/>
-      <c r="BX36" s="17"/>
-      <c r="BY36" s="17"/>
-      <c r="BZ36" s="17"/>
-      <c r="CA36" s="17"/>
-      <c r="CB36" s="17"/>
-      <c r="CC36" s="17"/>
-      <c r="CD36" s="17"/>
-      <c r="CE36" s="17"/>
-      <c r="CF36" s="17"/>
-      <c r="CG36" s="17"/>
-      <c r="CH36" s="17"/>
-      <c r="CI36" s="17"/>
-      <c r="CJ36" s="17"/>
-      <c r="CK36" s="17"/>
-      <c r="CL36" s="17"/>
-      <c r="CM36" s="17"/>
-      <c r="CN36" s="17"/>
-      <c r="CO36" s="17"/>
-      <c r="CP36" s="17"/>
+      <c r="BX36" s="61"/>
+      <c r="BY36" s="61"/>
+      <c r="BZ36" s="61"/>
+      <c r="CA36" s="61"/>
+      <c r="CB36" s="61"/>
+      <c r="CC36" s="61"/>
+      <c r="CD36" s="61"/>
+      <c r="CE36" s="61"/>
+      <c r="CF36" s="61"/>
+      <c r="CG36" s="61"/>
+      <c r="CH36" s="61"/>
+      <c r="CI36" s="61"/>
+      <c r="CJ36" s="61"/>
+      <c r="CK36" s="61"/>
+      <c r="CL36" s="61"/>
+      <c r="CM36" s="61"/>
+      <c r="CN36" s="61"/>
+      <c r="CO36" s="61"/>
+      <c r="CP36" s="61"/>
       <c r="CQ36" s="8"/>
       <c r="CR36" s="8" t="s">
         <v>28</v>
@@ -4648,54 +4648,54 @@
       <c r="T37" s="13"/>
       <c r="U37" s="13"/>
       <c r="V37" s="13"/>
-      <c r="W37" s="16" t="s">
+      <c r="W37" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="X37" s="16"/>
-      <c r="Y37" s="16"/>
-      <c r="Z37" s="16"/>
-      <c r="AA37" s="16"/>
-      <c r="AB37" s="16"/>
-      <c r="AC37" s="16"/>
-      <c r="AD37" s="16"/>
-      <c r="AE37" s="16"/>
-      <c r="AF37" s="16"/>
-      <c r="AG37" s="16"/>
-      <c r="AH37" s="16"/>
-      <c r="AI37" s="16"/>
-      <c r="AJ37" s="16"/>
-      <c r="AK37" s="16"/>
-      <c r="AL37" s="16"/>
-      <c r="AM37" s="16"/>
-      <c r="AN37" s="16"/>
-      <c r="AO37" s="16"/>
-      <c r="AP37" s="16"/>
-      <c r="AQ37" s="16"/>
-      <c r="AR37" s="16"/>
-      <c r="AS37" s="16"/>
-      <c r="AT37" s="16"/>
-      <c r="AU37" s="16"/>
-      <c r="AV37" s="16"/>
-      <c r="AW37" s="16"/>
-      <c r="AX37" s="16"/>
-      <c r="AY37" s="16"/>
-      <c r="AZ37" s="16"/>
-      <c r="BA37" s="16"/>
-      <c r="BB37" s="16"/>
-      <c r="BC37" s="16"/>
-      <c r="BD37" s="16"/>
-      <c r="BE37" s="16"/>
-      <c r="BF37" s="16"/>
-      <c r="BG37" s="16"/>
-      <c r="BH37" s="16"/>
-      <c r="BI37" s="16"/>
-      <c r="BJ37" s="16"/>
-      <c r="BK37" s="16"/>
-      <c r="BL37" s="16"/>
-      <c r="BM37" s="16"/>
-      <c r="BN37" s="16"/>
-      <c r="BO37" s="16"/>
-      <c r="BP37" s="16"/>
+      <c r="X37" s="53"/>
+      <c r="Y37" s="53"/>
+      <c r="Z37" s="53"/>
+      <c r="AA37" s="53"/>
+      <c r="AB37" s="53"/>
+      <c r="AC37" s="53"/>
+      <c r="AD37" s="53"/>
+      <c r="AE37" s="53"/>
+      <c r="AF37" s="53"/>
+      <c r="AG37" s="53"/>
+      <c r="AH37" s="53"/>
+      <c r="AI37" s="53"/>
+      <c r="AJ37" s="53"/>
+      <c r="AK37" s="53"/>
+      <c r="AL37" s="53"/>
+      <c r="AM37" s="53"/>
+      <c r="AN37" s="53"/>
+      <c r="AO37" s="53"/>
+      <c r="AP37" s="53"/>
+      <c r="AQ37" s="53"/>
+      <c r="AR37" s="53"/>
+      <c r="AS37" s="53"/>
+      <c r="AT37" s="53"/>
+      <c r="AU37" s="53"/>
+      <c r="AV37" s="53"/>
+      <c r="AW37" s="53"/>
+      <c r="AX37" s="53"/>
+      <c r="AY37" s="53"/>
+      <c r="AZ37" s="53"/>
+      <c r="BA37" s="53"/>
+      <c r="BB37" s="53"/>
+      <c r="BC37" s="53"/>
+      <c r="BD37" s="53"/>
+      <c r="BE37" s="53"/>
+      <c r="BF37" s="53"/>
+      <c r="BG37" s="53"/>
+      <c r="BH37" s="53"/>
+      <c r="BI37" s="53"/>
+      <c r="BJ37" s="53"/>
+      <c r="BK37" s="53"/>
+      <c r="BL37" s="53"/>
+      <c r="BM37" s="53"/>
+      <c r="BN37" s="53"/>
+      <c r="BO37" s="53"/>
+      <c r="BP37" s="53"/>
       <c r="BQ37" s="10"/>
       <c r="BR37" s="10"/>
       <c r="BS37" s="10"/>
@@ -4703,27 +4703,27 @@
       <c r="BU37" s="10"/>
       <c r="BV37" s="10"/>
       <c r="BW37" s="10"/>
-      <c r="BX37" s="16" t="s">
+      <c r="BX37" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="BY37" s="16"/>
-      <c r="BZ37" s="16"/>
-      <c r="CA37" s="16"/>
-      <c r="CB37" s="16"/>
-      <c r="CC37" s="16"/>
-      <c r="CD37" s="16"/>
-      <c r="CE37" s="16"/>
-      <c r="CF37" s="16"/>
-      <c r="CG37" s="16"/>
-      <c r="CH37" s="16"/>
-      <c r="CI37" s="16"/>
-      <c r="CJ37" s="16"/>
-      <c r="CK37" s="16"/>
-      <c r="CL37" s="16"/>
-      <c r="CM37" s="16"/>
-      <c r="CN37" s="16"/>
-      <c r="CO37" s="16"/>
-      <c r="CP37" s="16"/>
+      <c r="BY37" s="53"/>
+      <c r="BZ37" s="53"/>
+      <c r="CA37" s="53"/>
+      <c r="CB37" s="53"/>
+      <c r="CC37" s="53"/>
+      <c r="CD37" s="53"/>
+      <c r="CE37" s="53"/>
+      <c r="CF37" s="53"/>
+      <c r="CG37" s="53"/>
+      <c r="CH37" s="53"/>
+      <c r="CI37" s="53"/>
+      <c r="CJ37" s="53"/>
+      <c r="CK37" s="53"/>
+      <c r="CL37" s="53"/>
+      <c r="CM37" s="53"/>
+      <c r="CN37" s="53"/>
+      <c r="CO37" s="53"/>
+      <c r="CP37" s="53"/>
       <c r="CQ37" s="10"/>
       <c r="CR37" s="10"/>
       <c r="CS37" s="10"/>
@@ -4834,110 +4834,110 @@
       <c r="CV38" s="1"/>
     </row>
     <row r="39" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="52" t="s">
         <v>4</v>
       </c>
-      <c r="B39" s="19"/>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-      <c r="K39" s="19"/>
-      <c r="L39" s="19"/>
-      <c r="M39" s="19"/>
-      <c r="N39" s="19"/>
-      <c r="O39" s="19"/>
-      <c r="P39" s="19"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
+      <c r="D39" s="52"/>
+      <c r="E39" s="52"/>
+      <c r="F39" s="52"/>
+      <c r="G39" s="52"/>
+      <c r="H39" s="52"/>
+      <c r="I39" s="52"/>
+      <c r="J39" s="52"/>
+      <c r="K39" s="52"/>
+      <c r="L39" s="52"/>
+      <c r="M39" s="52"/>
+      <c r="N39" s="52"/>
+      <c r="O39" s="52"/>
+      <c r="P39" s="52"/>
       <c r="Q39" s="1"/>
-      <c r="R39" s="20" t="s">
+      <c r="R39" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="S39" s="20"/>
-      <c r="T39" s="20"/>
-      <c r="U39" s="20"/>
-      <c r="V39" s="20"/>
-      <c r="W39" s="20"/>
-      <c r="X39" s="20"/>
-      <c r="Y39" s="20"/>
-      <c r="Z39" s="20"/>
-      <c r="AA39" s="20"/>
-      <c r="AB39" s="20"/>
-      <c r="AC39" s="20"/>
-      <c r="AD39" s="20"/>
-      <c r="AE39" s="20"/>
-      <c r="AF39" s="20"/>
-      <c r="AG39" s="20"/>
-      <c r="AH39" s="20"/>
-      <c r="AI39" s="20"/>
-      <c r="AJ39" s="20"/>
-      <c r="AK39" s="20"/>
-      <c r="AL39" s="20"/>
-      <c r="AM39" s="20"/>
-      <c r="AN39" s="20"/>
-      <c r="AO39" s="20"/>
-      <c r="AP39" s="20"/>
-      <c r="AQ39" s="20"/>
-      <c r="AR39" s="20"/>
-      <c r="AS39" s="20"/>
-      <c r="AT39" s="20"/>
-      <c r="AU39" s="20"/>
-      <c r="AV39" s="20"/>
-      <c r="AW39" s="20"/>
-      <c r="AX39" s="20"/>
-      <c r="AY39" s="20"/>
-      <c r="AZ39" s="20"/>
-      <c r="BA39" s="20"/>
-      <c r="BB39" s="20"/>
-      <c r="BC39" s="20"/>
-      <c r="BD39" s="20"/>
-      <c r="BE39" s="20"/>
-      <c r="BF39" s="20"/>
-      <c r="BG39" s="20"/>
-      <c r="BH39" s="20"/>
-      <c r="BI39" s="20"/>
-      <c r="BJ39" s="20"/>
-      <c r="BK39" s="20"/>
-      <c r="BL39" s="20"/>
-      <c r="BM39" s="20"/>
-      <c r="BN39" s="20"/>
-      <c r="BO39" s="20"/>
-      <c r="BP39" s="20"/>
-      <c r="BQ39" s="20"/>
-      <c r="BR39" s="20"/>
-      <c r="BS39" s="20"/>
-      <c r="BT39" s="20"/>
-      <c r="BU39" s="20"/>
-      <c r="BV39" s="20"/>
-      <c r="BW39" s="20"/>
-      <c r="BX39" s="20"/>
-      <c r="BY39" s="20"/>
-      <c r="BZ39" s="20"/>
-      <c r="CA39" s="20"/>
-      <c r="CB39" s="20"/>
-      <c r="CC39" s="20"/>
-      <c r="CD39" s="20"/>
-      <c r="CE39" s="20"/>
-      <c r="CF39" s="20"/>
-      <c r="CG39" s="20"/>
-      <c r="CH39" s="20"/>
-      <c r="CI39" s="20"/>
-      <c r="CJ39" s="20"/>
-      <c r="CK39" s="20"/>
-      <c r="CL39" s="20"/>
-      <c r="CM39" s="20"/>
-      <c r="CN39" s="20"/>
-      <c r="CO39" s="20"/>
-      <c r="CP39" s="20"/>
-      <c r="CQ39" s="20"/>
-      <c r="CR39" s="20"/>
-      <c r="CS39" s="20"/>
-      <c r="CT39" s="20"/>
-      <c r="CU39" s="20"/>
-      <c r="CV39" s="20"/>
+      <c r="S39" s="42"/>
+      <c r="T39" s="42"/>
+      <c r="U39" s="42"/>
+      <c r="V39" s="42"/>
+      <c r="W39" s="42"/>
+      <c r="X39" s="42"/>
+      <c r="Y39" s="42"/>
+      <c r="Z39" s="42"/>
+      <c r="AA39" s="42"/>
+      <c r="AB39" s="42"/>
+      <c r="AC39" s="42"/>
+      <c r="AD39" s="42"/>
+      <c r="AE39" s="42"/>
+      <c r="AF39" s="42"/>
+      <c r="AG39" s="42"/>
+      <c r="AH39" s="42"/>
+      <c r="AI39" s="42"/>
+      <c r="AJ39" s="42"/>
+      <c r="AK39" s="42"/>
+      <c r="AL39" s="42"/>
+      <c r="AM39" s="42"/>
+      <c r="AN39" s="42"/>
+      <c r="AO39" s="42"/>
+      <c r="AP39" s="42"/>
+      <c r="AQ39" s="42"/>
+      <c r="AR39" s="42"/>
+      <c r="AS39" s="42"/>
+      <c r="AT39" s="42"/>
+      <c r="AU39" s="42"/>
+      <c r="AV39" s="42"/>
+      <c r="AW39" s="42"/>
+      <c r="AX39" s="42"/>
+      <c r="AY39" s="42"/>
+      <c r="AZ39" s="42"/>
+      <c r="BA39" s="42"/>
+      <c r="BB39" s="42"/>
+      <c r="BC39" s="42"/>
+      <c r="BD39" s="42"/>
+      <c r="BE39" s="42"/>
+      <c r="BF39" s="42"/>
+      <c r="BG39" s="42"/>
+      <c r="BH39" s="42"/>
+      <c r="BI39" s="42"/>
+      <c r="BJ39" s="42"/>
+      <c r="BK39" s="42"/>
+      <c r="BL39" s="42"/>
+      <c r="BM39" s="42"/>
+      <c r="BN39" s="42"/>
+      <c r="BO39" s="42"/>
+      <c r="BP39" s="42"/>
+      <c r="BQ39" s="42"/>
+      <c r="BR39" s="42"/>
+      <c r="BS39" s="42"/>
+      <c r="BT39" s="42"/>
+      <c r="BU39" s="42"/>
+      <c r="BV39" s="42"/>
+      <c r="BW39" s="42"/>
+      <c r="BX39" s="42"/>
+      <c r="BY39" s="42"/>
+      <c r="BZ39" s="42"/>
+      <c r="CA39" s="42"/>
+      <c r="CB39" s="42"/>
+      <c r="CC39" s="42"/>
+      <c r="CD39" s="42"/>
+      <c r="CE39" s="42"/>
+      <c r="CF39" s="42"/>
+      <c r="CG39" s="42"/>
+      <c r="CH39" s="42"/>
+      <c r="CI39" s="42"/>
+      <c r="CJ39" s="42"/>
+      <c r="CK39" s="42"/>
+      <c r="CL39" s="42"/>
+      <c r="CM39" s="42"/>
+      <c r="CN39" s="42"/>
+      <c r="CO39" s="42"/>
+      <c r="CP39" s="42"/>
+      <c r="CQ39" s="42"/>
+      <c r="CR39" s="42"/>
+      <c r="CS39" s="42"/>
+      <c r="CT39" s="42"/>
+      <c r="CU39" s="42"/>
+      <c r="CV39" s="42"/>
     </row>
     <row r="40" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
@@ -4957,91 +4957,91 @@
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-      <c r="R40" s="18" t="s">
+      <c r="R40" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="S40" s="18"/>
-      <c r="T40" s="18"/>
-      <c r="U40" s="18"/>
-      <c r="V40" s="18"/>
-      <c r="W40" s="18"/>
-      <c r="X40" s="18"/>
-      <c r="Y40" s="18"/>
-      <c r="Z40" s="18"/>
-      <c r="AA40" s="18"/>
-      <c r="AB40" s="18"/>
-      <c r="AC40" s="18"/>
-      <c r="AD40" s="18"/>
-      <c r="AE40" s="18"/>
-      <c r="AF40" s="18"/>
-      <c r="AG40" s="18"/>
-      <c r="AH40" s="18"/>
-      <c r="AI40" s="18"/>
-      <c r="AJ40" s="18"/>
-      <c r="AK40" s="18"/>
-      <c r="AL40" s="18"/>
-      <c r="AM40" s="18"/>
-      <c r="AN40" s="18"/>
-      <c r="AO40" s="18"/>
-      <c r="AP40" s="18"/>
-      <c r="AQ40" s="18"/>
-      <c r="AR40" s="18"/>
-      <c r="AS40" s="18"/>
-      <c r="AT40" s="18"/>
-      <c r="AU40" s="18"/>
-      <c r="AV40" s="18"/>
-      <c r="AW40" s="18"/>
-      <c r="AX40" s="18"/>
-      <c r="AY40" s="18"/>
-      <c r="AZ40" s="18"/>
-      <c r="BA40" s="18"/>
-      <c r="BB40" s="18"/>
-      <c r="BC40" s="18"/>
-      <c r="BD40" s="18"/>
-      <c r="BE40" s="18"/>
-      <c r="BF40" s="18"/>
-      <c r="BG40" s="18"/>
-      <c r="BH40" s="18"/>
-      <c r="BI40" s="18"/>
-      <c r="BJ40" s="18"/>
-      <c r="BK40" s="18"/>
-      <c r="BL40" s="18"/>
-      <c r="BM40" s="18"/>
-      <c r="BN40" s="18"/>
-      <c r="BO40" s="18"/>
-      <c r="BP40" s="18"/>
-      <c r="BQ40" s="18"/>
-      <c r="BR40" s="18"/>
-      <c r="BS40" s="18"/>
-      <c r="BT40" s="18"/>
-      <c r="BU40" s="18"/>
-      <c r="BV40" s="18"/>
-      <c r="BW40" s="18"/>
-      <c r="BX40" s="18"/>
-      <c r="BY40" s="18"/>
-      <c r="BZ40" s="18"/>
-      <c r="CA40" s="18"/>
-      <c r="CB40" s="18"/>
-      <c r="CC40" s="18"/>
-      <c r="CD40" s="18"/>
-      <c r="CE40" s="18"/>
-      <c r="CF40" s="18"/>
-      <c r="CG40" s="18"/>
-      <c r="CH40" s="18"/>
-      <c r="CI40" s="18"/>
-      <c r="CJ40" s="18"/>
-      <c r="CK40" s="18"/>
-      <c r="CL40" s="18"/>
-      <c r="CM40" s="18"/>
-      <c r="CN40" s="18"/>
-      <c r="CO40" s="18"/>
-      <c r="CP40" s="18"/>
-      <c r="CQ40" s="18"/>
-      <c r="CR40" s="18"/>
-      <c r="CS40" s="18"/>
-      <c r="CT40" s="18"/>
-      <c r="CU40" s="18"/>
-      <c r="CV40" s="18"/>
+      <c r="S40" s="59"/>
+      <c r="T40" s="59"/>
+      <c r="U40" s="59"/>
+      <c r="V40" s="59"/>
+      <c r="W40" s="59"/>
+      <c r="X40" s="59"/>
+      <c r="Y40" s="59"/>
+      <c r="Z40" s="59"/>
+      <c r="AA40" s="59"/>
+      <c r="AB40" s="59"/>
+      <c r="AC40" s="59"/>
+      <c r="AD40" s="59"/>
+      <c r="AE40" s="59"/>
+      <c r="AF40" s="59"/>
+      <c r="AG40" s="59"/>
+      <c r="AH40" s="59"/>
+      <c r="AI40" s="59"/>
+      <c r="AJ40" s="59"/>
+      <c r="AK40" s="59"/>
+      <c r="AL40" s="59"/>
+      <c r="AM40" s="59"/>
+      <c r="AN40" s="59"/>
+      <c r="AO40" s="59"/>
+      <c r="AP40" s="59"/>
+      <c r="AQ40" s="59"/>
+      <c r="AR40" s="59"/>
+      <c r="AS40" s="59"/>
+      <c r="AT40" s="59"/>
+      <c r="AU40" s="59"/>
+      <c r="AV40" s="59"/>
+      <c r="AW40" s="59"/>
+      <c r="AX40" s="59"/>
+      <c r="AY40" s="59"/>
+      <c r="AZ40" s="59"/>
+      <c r="BA40" s="59"/>
+      <c r="BB40" s="59"/>
+      <c r="BC40" s="59"/>
+      <c r="BD40" s="59"/>
+      <c r="BE40" s="59"/>
+      <c r="BF40" s="59"/>
+      <c r="BG40" s="59"/>
+      <c r="BH40" s="59"/>
+      <c r="BI40" s="59"/>
+      <c r="BJ40" s="59"/>
+      <c r="BK40" s="59"/>
+      <c r="BL40" s="59"/>
+      <c r="BM40" s="59"/>
+      <c r="BN40" s="59"/>
+      <c r="BO40" s="59"/>
+      <c r="BP40" s="59"/>
+      <c r="BQ40" s="59"/>
+      <c r="BR40" s="59"/>
+      <c r="BS40" s="59"/>
+      <c r="BT40" s="59"/>
+      <c r="BU40" s="59"/>
+      <c r="BV40" s="59"/>
+      <c r="BW40" s="59"/>
+      <c r="BX40" s="59"/>
+      <c r="BY40" s="59"/>
+      <c r="BZ40" s="59"/>
+      <c r="CA40" s="59"/>
+      <c r="CB40" s="59"/>
+      <c r="CC40" s="59"/>
+      <c r="CD40" s="59"/>
+      <c r="CE40" s="59"/>
+      <c r="CF40" s="59"/>
+      <c r="CG40" s="59"/>
+      <c r="CH40" s="59"/>
+      <c r="CI40" s="59"/>
+      <c r="CJ40" s="59"/>
+      <c r="CK40" s="59"/>
+      <c r="CL40" s="59"/>
+      <c r="CM40" s="59"/>
+      <c r="CN40" s="59"/>
+      <c r="CO40" s="59"/>
+      <c r="CP40" s="59"/>
+      <c r="CQ40" s="59"/>
+      <c r="CR40" s="59"/>
+      <c r="CS40" s="59"/>
+      <c r="CT40" s="59"/>
+      <c r="CU40" s="59"/>
+      <c r="CV40" s="59"/>
     </row>
     <row r="41" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
@@ -5146,193 +5146,193 @@
       <c r="CV41" s="1"/>
     </row>
     <row r="42" spans="1:173" s="2" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="19" t="s">
+      <c r="A42" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
-      <c r="G42" s="19"/>
-      <c r="H42" s="19"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="19"/>
-      <c r="L42" s="19"/>
-      <c r="M42" s="19"/>
-      <c r="N42" s="19"/>
-      <c r="O42" s="19"/>
-      <c r="P42" s="19"/>
-      <c r="Q42" s="19"/>
-      <c r="R42" s="19"/>
-      <c r="S42" s="19"/>
-      <c r="T42" s="19"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
+      <c r="D42" s="52"/>
+      <c r="E42" s="52"/>
+      <c r="F42" s="52"/>
+      <c r="G42" s="52"/>
+      <c r="H42" s="52"/>
+      <c r="I42" s="52"/>
+      <c r="J42" s="52"/>
+      <c r="K42" s="52"/>
+      <c r="L42" s="52"/>
+      <c r="M42" s="52"/>
+      <c r="N42" s="52"/>
+      <c r="O42" s="52"/>
+      <c r="P42" s="52"/>
+      <c r="Q42" s="52"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="52"/>
+      <c r="T42" s="52"/>
       <c r="U42" s="1"/>
-      <c r="V42" s="20" t="s">
+      <c r="V42" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="W42" s="20"/>
-      <c r="X42" s="20"/>
-      <c r="Y42" s="20"/>
-      <c r="Z42" s="20"/>
-      <c r="AA42" s="20"/>
-      <c r="AB42" s="20"/>
-      <c r="AC42" s="20"/>
-      <c r="AD42" s="20"/>
-      <c r="AE42" s="20"/>
-      <c r="AF42" s="20"/>
-      <c r="AG42" s="20"/>
-      <c r="AH42" s="20"/>
-      <c r="AI42" s="20"/>
-      <c r="AJ42" s="20"/>
-      <c r="AK42" s="20"/>
-      <c r="AL42" s="20"/>
-      <c r="AM42" s="20"/>
-      <c r="AN42" s="20"/>
-      <c r="AO42" s="20"/>
-      <c r="AP42" s="20"/>
-      <c r="AQ42" s="20"/>
-      <c r="AR42" s="20"/>
-      <c r="AS42" s="20"/>
-      <c r="AT42" s="20"/>
-      <c r="AU42" s="20"/>
-      <c r="AV42" s="20"/>
-      <c r="AW42" s="20"/>
-      <c r="AX42" s="20"/>
-      <c r="AY42" s="20"/>
-      <c r="AZ42" s="20"/>
-      <c r="BA42" s="20"/>
-      <c r="BB42" s="20"/>
-      <c r="BC42" s="20"/>
-      <c r="BD42" s="20"/>
-      <c r="BE42" s="20"/>
-      <c r="BF42" s="20"/>
-      <c r="BG42" s="20"/>
-      <c r="BH42" s="20"/>
-      <c r="BI42" s="20"/>
-      <c r="BJ42" s="20"/>
-      <c r="BK42" s="20"/>
-      <c r="BL42" s="20"/>
-      <c r="BM42" s="20"/>
-      <c r="BN42" s="20"/>
-      <c r="BO42" s="20"/>
-      <c r="BP42" s="20"/>
-      <c r="BQ42" s="20"/>
-      <c r="BR42" s="20"/>
-      <c r="BS42" s="20"/>
-      <c r="BT42" s="20"/>
-      <c r="BU42" s="20"/>
-      <c r="BV42" s="20"/>
-      <c r="BW42" s="20"/>
-      <c r="BX42" s="20"/>
-      <c r="BY42" s="20"/>
-      <c r="BZ42" s="20"/>
-      <c r="CA42" s="20"/>
-      <c r="CB42" s="20"/>
-      <c r="CC42" s="20"/>
-      <c r="CD42" s="20"/>
-      <c r="CE42" s="20"/>
-      <c r="CF42" s="20"/>
-      <c r="CG42" s="20"/>
-      <c r="CH42" s="20"/>
-      <c r="CI42" s="20"/>
-      <c r="CJ42" s="20"/>
-      <c r="CK42" s="20"/>
-      <c r="CL42" s="20"/>
-      <c r="CM42" s="20"/>
-      <c r="CN42" s="20"/>
-      <c r="CO42" s="20"/>
-      <c r="CP42" s="20"/>
-      <c r="CQ42" s="20"/>
-      <c r="CR42" s="20"/>
-      <c r="CS42" s="20"/>
-      <c r="CT42" s="20"/>
-      <c r="CU42" s="20"/>
-      <c r="CV42" s="20"/>
+      <c r="W42" s="42"/>
+      <c r="X42" s="42"/>
+      <c r="Y42" s="42"/>
+      <c r="Z42" s="42"/>
+      <c r="AA42" s="42"/>
+      <c r="AB42" s="42"/>
+      <c r="AC42" s="42"/>
+      <c r="AD42" s="42"/>
+      <c r="AE42" s="42"/>
+      <c r="AF42" s="42"/>
+      <c r="AG42" s="42"/>
+      <c r="AH42" s="42"/>
+      <c r="AI42" s="42"/>
+      <c r="AJ42" s="42"/>
+      <c r="AK42" s="42"/>
+      <c r="AL42" s="42"/>
+      <c r="AM42" s="42"/>
+      <c r="AN42" s="42"/>
+      <c r="AO42" s="42"/>
+      <c r="AP42" s="42"/>
+      <c r="AQ42" s="42"/>
+      <c r="AR42" s="42"/>
+      <c r="AS42" s="42"/>
+      <c r="AT42" s="42"/>
+      <c r="AU42" s="42"/>
+      <c r="AV42" s="42"/>
+      <c r="AW42" s="42"/>
+      <c r="AX42" s="42"/>
+      <c r="AY42" s="42"/>
+      <c r="AZ42" s="42"/>
+      <c r="BA42" s="42"/>
+      <c r="BB42" s="42"/>
+      <c r="BC42" s="42"/>
+      <c r="BD42" s="42"/>
+      <c r="BE42" s="42"/>
+      <c r="BF42" s="42"/>
+      <c r="BG42" s="42"/>
+      <c r="BH42" s="42"/>
+      <c r="BI42" s="42"/>
+      <c r="BJ42" s="42"/>
+      <c r="BK42" s="42"/>
+      <c r="BL42" s="42"/>
+      <c r="BM42" s="42"/>
+      <c r="BN42" s="42"/>
+      <c r="BO42" s="42"/>
+      <c r="BP42" s="42"/>
+      <c r="BQ42" s="42"/>
+      <c r="BR42" s="42"/>
+      <c r="BS42" s="42"/>
+      <c r="BT42" s="42"/>
+      <c r="BU42" s="42"/>
+      <c r="BV42" s="42"/>
+      <c r="BW42" s="42"/>
+      <c r="BX42" s="42"/>
+      <c r="BY42" s="42"/>
+      <c r="BZ42" s="42"/>
+      <c r="CA42" s="42"/>
+      <c r="CB42" s="42"/>
+      <c r="CC42" s="42"/>
+      <c r="CD42" s="42"/>
+      <c r="CE42" s="42"/>
+      <c r="CF42" s="42"/>
+      <c r="CG42" s="42"/>
+      <c r="CH42" s="42"/>
+      <c r="CI42" s="42"/>
+      <c r="CJ42" s="42"/>
+      <c r="CK42" s="42"/>
+      <c r="CL42" s="42"/>
+      <c r="CM42" s="42"/>
+      <c r="CN42" s="42"/>
+      <c r="CO42" s="42"/>
+      <c r="CP42" s="42"/>
+      <c r="CQ42" s="42"/>
+      <c r="CR42" s="42"/>
+      <c r="CS42" s="42"/>
+      <c r="CT42" s="42"/>
+      <c r="CU42" s="42"/>
+      <c r="CV42" s="42"/>
     </row>
     <row r="43" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="V43" s="18" t="s">
+      <c r="V43" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="W43" s="18"/>
-      <c r="X43" s="18"/>
-      <c r="Y43" s="18"/>
-      <c r="Z43" s="18"/>
-      <c r="AA43" s="18"/>
-      <c r="AB43" s="18"/>
-      <c r="AC43" s="18"/>
-      <c r="AD43" s="18"/>
-      <c r="AE43" s="18"/>
-      <c r="AF43" s="18"/>
-      <c r="AG43" s="18"/>
-      <c r="AH43" s="18"/>
-      <c r="AI43" s="18"/>
-      <c r="AJ43" s="18"/>
-      <c r="AK43" s="18"/>
-      <c r="AL43" s="18"/>
-      <c r="AM43" s="18"/>
-      <c r="AN43" s="18"/>
-      <c r="AO43" s="18"/>
-      <c r="AP43" s="18"/>
-      <c r="AQ43" s="18"/>
-      <c r="AR43" s="18"/>
-      <c r="AS43" s="18"/>
-      <c r="AT43" s="18"/>
-      <c r="AU43" s="18"/>
-      <c r="AV43" s="18"/>
-      <c r="AW43" s="18"/>
-      <c r="AX43" s="18"/>
-      <c r="AY43" s="18"/>
-      <c r="AZ43" s="18"/>
-      <c r="BA43" s="18"/>
-      <c r="BB43" s="18"/>
-      <c r="BC43" s="18"/>
-      <c r="BD43" s="18"/>
-      <c r="BE43" s="18"/>
-      <c r="BF43" s="18"/>
-      <c r="BG43" s="18"/>
-      <c r="BH43" s="18"/>
-      <c r="BI43" s="18"/>
-      <c r="BJ43" s="18"/>
-      <c r="BK43" s="18"/>
-      <c r="BL43" s="18"/>
-      <c r="BM43" s="18"/>
-      <c r="BN43" s="18"/>
-      <c r="BO43" s="18"/>
-      <c r="BP43" s="18"/>
-      <c r="BQ43" s="18"/>
-      <c r="BR43" s="18"/>
-      <c r="BS43" s="18"/>
-      <c r="BT43" s="18"/>
-      <c r="BU43" s="18"/>
-      <c r="BV43" s="18"/>
-      <c r="BW43" s="18"/>
-      <c r="BX43" s="18"/>
-      <c r="BY43" s="18"/>
-      <c r="BZ43" s="18"/>
-      <c r="CA43" s="18"/>
-      <c r="CB43" s="18"/>
-      <c r="CC43" s="18"/>
-      <c r="CD43" s="18"/>
-      <c r="CE43" s="18"/>
-      <c r="CF43" s="18"/>
-      <c r="CG43" s="18"/>
-      <c r="CH43" s="18"/>
-      <c r="CI43" s="18"/>
-      <c r="CJ43" s="18"/>
-      <c r="CK43" s="18"/>
-      <c r="CL43" s="18"/>
-      <c r="CM43" s="18"/>
-      <c r="CN43" s="18"/>
-      <c r="CO43" s="18"/>
-      <c r="CP43" s="18"/>
-      <c r="CQ43" s="18"/>
-      <c r="CR43" s="18"/>
-      <c r="CS43" s="18"/>
-      <c r="CT43" s="18"/>
-      <c r="CU43" s="18"/>
-      <c r="CV43" s="18"/>
+      <c r="W43" s="59"/>
+      <c r="X43" s="59"/>
+      <c r="Y43" s="59"/>
+      <c r="Z43" s="59"/>
+      <c r="AA43" s="59"/>
+      <c r="AB43" s="59"/>
+      <c r="AC43" s="59"/>
+      <c r="AD43" s="59"/>
+      <c r="AE43" s="59"/>
+      <c r="AF43" s="59"/>
+      <c r="AG43" s="59"/>
+      <c r="AH43" s="59"/>
+      <c r="AI43" s="59"/>
+      <c r="AJ43" s="59"/>
+      <c r="AK43" s="59"/>
+      <c r="AL43" s="59"/>
+      <c r="AM43" s="59"/>
+      <c r="AN43" s="59"/>
+      <c r="AO43" s="59"/>
+      <c r="AP43" s="59"/>
+      <c r="AQ43" s="59"/>
+      <c r="AR43" s="59"/>
+      <c r="AS43" s="59"/>
+      <c r="AT43" s="59"/>
+      <c r="AU43" s="59"/>
+      <c r="AV43" s="59"/>
+      <c r="AW43" s="59"/>
+      <c r="AX43" s="59"/>
+      <c r="AY43" s="59"/>
+      <c r="AZ43" s="59"/>
+      <c r="BA43" s="59"/>
+      <c r="BB43" s="59"/>
+      <c r="BC43" s="59"/>
+      <c r="BD43" s="59"/>
+      <c r="BE43" s="59"/>
+      <c r="BF43" s="59"/>
+      <c r="BG43" s="59"/>
+      <c r="BH43" s="59"/>
+      <c r="BI43" s="59"/>
+      <c r="BJ43" s="59"/>
+      <c r="BK43" s="59"/>
+      <c r="BL43" s="59"/>
+      <c r="BM43" s="59"/>
+      <c r="BN43" s="59"/>
+      <c r="BO43" s="59"/>
+      <c r="BP43" s="59"/>
+      <c r="BQ43" s="59"/>
+      <c r="BR43" s="59"/>
+      <c r="BS43" s="59"/>
+      <c r="BT43" s="59"/>
+      <c r="BU43" s="59"/>
+      <c r="BV43" s="59"/>
+      <c r="BW43" s="59"/>
+      <c r="BX43" s="59"/>
+      <c r="BY43" s="59"/>
+      <c r="BZ43" s="59"/>
+      <c r="CA43" s="59"/>
+      <c r="CB43" s="59"/>
+      <c r="CC43" s="59"/>
+      <c r="CD43" s="59"/>
+      <c r="CE43" s="59"/>
+      <c r="CF43" s="59"/>
+      <c r="CG43" s="59"/>
+      <c r="CH43" s="59"/>
+      <c r="CI43" s="59"/>
+      <c r="CJ43" s="59"/>
+      <c r="CK43" s="59"/>
+      <c r="CL43" s="59"/>
+      <c r="CM43" s="59"/>
+      <c r="CN43" s="59"/>
+      <c r="CO43" s="59"/>
+      <c r="CP43" s="59"/>
+      <c r="CQ43" s="59"/>
+      <c r="CR43" s="59"/>
+      <c r="CS43" s="59"/>
+      <c r="CT43" s="59"/>
+      <c r="CU43" s="59"/>
+      <c r="CV43" s="59"/>
     </row>
     <row r="44" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="14"/>
@@ -5437,30 +5437,30 @@
       <c r="CV44" s="14"/>
     </row>
     <row r="45" spans="1:173" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="19" t="s">
+      <c r="A45" s="52" t="s">
         <v>11</v>
       </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-      <c r="K45" s="19"/>
-      <c r="L45" s="19"/>
-      <c r="M45" s="19"/>
-      <c r="N45" s="19"/>
-      <c r="O45" s="19"/>
-      <c r="P45" s="19"/>
-      <c r="Q45" s="19"/>
-      <c r="R45" s="19"/>
-      <c r="S45" s="19"/>
-      <c r="T45" s="19"/>
-      <c r="U45" s="19"/>
-      <c r="V45" s="19"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="52"/>
+      <c r="O45" s="52"/>
+      <c r="P45" s="52"/>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="52"/>
+      <c r="V45" s="52"/>
       <c r="X45" s="66"/>
       <c r="Y45" s="66"/>
       <c r="Z45" s="66"/>
@@ -5590,20 +5590,20 @@
       <c r="BL46" s="5"/>
       <c r="BM46" s="5"/>
       <c r="BN46" s="5"/>
-      <c r="BO46" s="16" t="s">
+      <c r="BO46" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="BP46" s="16"/>
-      <c r="BQ46" s="16"/>
-      <c r="BR46" s="16"/>
-      <c r="BS46" s="16"/>
-      <c r="BT46" s="16"/>
-      <c r="BU46" s="16"/>
-      <c r="BV46" s="16"/>
-      <c r="BW46" s="16"/>
-      <c r="BX46" s="16"/>
-      <c r="BY46" s="16"/>
-      <c r="BZ46" s="16"/>
+      <c r="BP46" s="53"/>
+      <c r="BQ46" s="53"/>
+      <c r="BR46" s="53"/>
+      <c r="BS46" s="53"/>
+      <c r="BT46" s="53"/>
+      <c r="BU46" s="53"/>
+      <c r="BV46" s="53"/>
+      <c r="BW46" s="53"/>
+      <c r="BX46" s="53"/>
+      <c r="BY46" s="53"/>
+      <c r="BZ46" s="53"/>
       <c r="CA46" s="5"/>
       <c r="CB46" s="5"/>
       <c r="CC46" s="5"/>
@@ -5614,20 +5614,20 @@
       <c r="CH46" s="5"/>
       <c r="CI46" s="5"/>
       <c r="CJ46" s="5"/>
-      <c r="CK46" s="16" t="s">
+      <c r="CK46" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="CL46" s="16"/>
-      <c r="CM46" s="16"/>
-      <c r="CN46" s="16"/>
-      <c r="CO46" s="16"/>
-      <c r="CP46" s="16"/>
-      <c r="CQ46" s="16"/>
-      <c r="CR46" s="16"/>
-      <c r="CS46" s="16"/>
-      <c r="CT46" s="16"/>
-      <c r="CU46" s="16"/>
-      <c r="CV46" s="16"/>
+      <c r="CL46" s="53"/>
+      <c r="CM46" s="53"/>
+      <c r="CN46" s="53"/>
+      <c r="CO46" s="53"/>
+      <c r="CP46" s="53"/>
+      <c r="CQ46" s="53"/>
+      <c r="CR46" s="53"/>
+      <c r="CS46" s="53"/>
+      <c r="CT46" s="53"/>
+      <c r="CU46" s="53"/>
+      <c r="CV46" s="53"/>
       <c r="CW46" s="14"/>
       <c r="CX46" s="14"/>
       <c r="CY46" s="14"/>
@@ -5717,188 +5717,188 @@
       <c r="CV47" s="65"/>
     </row>
     <row r="49" spans="1:100" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="19" t="s">
+      <c r="A49" s="52" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
-      <c r="G49" s="19"/>
-      <c r="H49" s="19"/>
-      <c r="I49" s="19"/>
-      <c r="J49" s="19"/>
-      <c r="K49" s="19"/>
-      <c r="L49" s="19"/>
-      <c r="M49" s="19"/>
-      <c r="N49" s="19"/>
-      <c r="O49" s="19"/>
-      <c r="P49" s="19"/>
-      <c r="Q49" s="19"/>
-      <c r="R49" s="19"/>
-      <c r="S49" s="19"/>
-      <c r="T49" s="19"/>
-      <c r="U49" s="19"/>
-      <c r="V49" s="19"/>
-      <c r="X49" s="20"/>
-      <c r="Y49" s="20"/>
-      <c r="Z49" s="20"/>
-      <c r="AA49" s="20"/>
-      <c r="AB49" s="20"/>
-      <c r="AC49" s="20"/>
-      <c r="AD49" s="20"/>
-      <c r="AE49" s="20"/>
-      <c r="AF49" s="20"/>
-      <c r="AG49" s="20"/>
-      <c r="AH49" s="20"/>
-      <c r="AI49" s="20"/>
-      <c r="AJ49" s="20"/>
-      <c r="AK49" s="20"/>
-      <c r="AL49" s="20"/>
-      <c r="AM49" s="20"/>
-      <c r="AN49" s="20"/>
-      <c r="AO49" s="20"/>
-      <c r="AP49" s="20"/>
-      <c r="AQ49" s="20"/>
-      <c r="AR49" s="20"/>
-      <c r="AS49" s="20"/>
-      <c r="AT49" s="20"/>
-      <c r="AU49" s="20"/>
-      <c r="AV49" s="20"/>
-      <c r="AW49" s="20"/>
-      <c r="AX49" s="20"/>
-      <c r="AY49" s="20"/>
-      <c r="AZ49" s="20"/>
-      <c r="BA49" s="20"/>
-      <c r="BB49" s="20"/>
-      <c r="BC49" s="20"/>
-      <c r="BD49" s="20"/>
-      <c r="BE49" s="20"/>
-      <c r="BF49" s="20"/>
-      <c r="BG49" s="20"/>
-      <c r="BH49" s="20"/>
-      <c r="BI49" s="20"/>
-      <c r="BJ49" s="20"/>
-      <c r="BK49" s="20"/>
-      <c r="BL49" s="20"/>
-      <c r="BM49" s="20"/>
-      <c r="BN49" s="20"/>
-      <c r="BO49" s="20"/>
-      <c r="BP49" s="20"/>
-      <c r="BQ49" s="20"/>
-      <c r="BR49" s="20"/>
-      <c r="BS49" s="20"/>
-      <c r="BT49" s="20"/>
-      <c r="BU49" s="20"/>
-      <c r="BV49" s="20"/>
-      <c r="BW49" s="20"/>
-      <c r="BX49" s="20"/>
-      <c r="BY49" s="20"/>
-      <c r="BZ49" s="20"/>
-      <c r="CA49" s="20"/>
-      <c r="CB49" s="20"/>
-      <c r="CC49" s="20"/>
-      <c r="CD49" s="20"/>
-      <c r="CE49" s="20"/>
-      <c r="CF49" s="20"/>
-      <c r="CG49" s="20"/>
-      <c r="CH49" s="20"/>
-      <c r="CI49" s="20"/>
-      <c r="CJ49" s="20"/>
-      <c r="CK49" s="20"/>
-      <c r="CL49" s="20"/>
-      <c r="CM49" s="20"/>
-      <c r="CN49" s="20"/>
-      <c r="CO49" s="20"/>
-      <c r="CP49" s="20"/>
-      <c r="CQ49" s="20"/>
-      <c r="CR49" s="20"/>
-      <c r="CS49" s="20"/>
-      <c r="CT49" s="20"/>
-      <c r="CU49" s="20"/>
-      <c r="CV49" s="20"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
+      <c r="D49" s="52"/>
+      <c r="E49" s="52"/>
+      <c r="F49" s="52"/>
+      <c r="G49" s="52"/>
+      <c r="H49" s="52"/>
+      <c r="I49" s="52"/>
+      <c r="J49" s="52"/>
+      <c r="K49" s="52"/>
+      <c r="L49" s="52"/>
+      <c r="M49" s="52"/>
+      <c r="N49" s="52"/>
+      <c r="O49" s="52"/>
+      <c r="P49" s="52"/>
+      <c r="Q49" s="52"/>
+      <c r="R49" s="52"/>
+      <c r="S49" s="52"/>
+      <c r="T49" s="52"/>
+      <c r="U49" s="52"/>
+      <c r="V49" s="52"/>
+      <c r="X49" s="42"/>
+      <c r="Y49" s="42"/>
+      <c r="Z49" s="42"/>
+      <c r="AA49" s="42"/>
+      <c r="AB49" s="42"/>
+      <c r="AC49" s="42"/>
+      <c r="AD49" s="42"/>
+      <c r="AE49" s="42"/>
+      <c r="AF49" s="42"/>
+      <c r="AG49" s="42"/>
+      <c r="AH49" s="42"/>
+      <c r="AI49" s="42"/>
+      <c r="AJ49" s="42"/>
+      <c r="AK49" s="42"/>
+      <c r="AL49" s="42"/>
+      <c r="AM49" s="42"/>
+      <c r="AN49" s="42"/>
+      <c r="AO49" s="42"/>
+      <c r="AP49" s="42"/>
+      <c r="AQ49" s="42"/>
+      <c r="AR49" s="42"/>
+      <c r="AS49" s="42"/>
+      <c r="AT49" s="42"/>
+      <c r="AU49" s="42"/>
+      <c r="AV49" s="42"/>
+      <c r="AW49" s="42"/>
+      <c r="AX49" s="42"/>
+      <c r="AY49" s="42"/>
+      <c r="AZ49" s="42"/>
+      <c r="BA49" s="42"/>
+      <c r="BB49" s="42"/>
+      <c r="BC49" s="42"/>
+      <c r="BD49" s="42"/>
+      <c r="BE49" s="42"/>
+      <c r="BF49" s="42"/>
+      <c r="BG49" s="42"/>
+      <c r="BH49" s="42"/>
+      <c r="BI49" s="42"/>
+      <c r="BJ49" s="42"/>
+      <c r="BK49" s="42"/>
+      <c r="BL49" s="42"/>
+      <c r="BM49" s="42"/>
+      <c r="BN49" s="42"/>
+      <c r="BO49" s="42"/>
+      <c r="BP49" s="42"/>
+      <c r="BQ49" s="42"/>
+      <c r="BR49" s="42"/>
+      <c r="BS49" s="42"/>
+      <c r="BT49" s="42"/>
+      <c r="BU49" s="42"/>
+      <c r="BV49" s="42"/>
+      <c r="BW49" s="42"/>
+      <c r="BX49" s="42"/>
+      <c r="BY49" s="42"/>
+      <c r="BZ49" s="42"/>
+      <c r="CA49" s="42"/>
+      <c r="CB49" s="42"/>
+      <c r="CC49" s="42"/>
+      <c r="CD49" s="42"/>
+      <c r="CE49" s="42"/>
+      <c r="CF49" s="42"/>
+      <c r="CG49" s="42"/>
+      <c r="CH49" s="42"/>
+      <c r="CI49" s="42"/>
+      <c r="CJ49" s="42"/>
+      <c r="CK49" s="42"/>
+      <c r="CL49" s="42"/>
+      <c r="CM49" s="42"/>
+      <c r="CN49" s="42"/>
+      <c r="CO49" s="42"/>
+      <c r="CP49" s="42"/>
+      <c r="CQ49" s="42"/>
+      <c r="CR49" s="42"/>
+      <c r="CS49" s="42"/>
+      <c r="CT49" s="42"/>
+      <c r="CU49" s="42"/>
+      <c r="CV49" s="42"/>
     </row>
     <row r="50" spans="1:100" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="X50" s="18" t="s">
+      <c r="X50" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="Y50" s="18"/>
-      <c r="Z50" s="18"/>
-      <c r="AA50" s="18"/>
-      <c r="AB50" s="18"/>
-      <c r="AC50" s="18"/>
-      <c r="AD50" s="18"/>
-      <c r="AE50" s="18"/>
-      <c r="AF50" s="18"/>
-      <c r="AG50" s="18"/>
-      <c r="AH50" s="18"/>
-      <c r="AI50" s="18"/>
-      <c r="AJ50" s="18"/>
-      <c r="AK50" s="18"/>
-      <c r="AL50" s="18"/>
-      <c r="AM50" s="18"/>
-      <c r="AN50" s="18"/>
-      <c r="AO50" s="18"/>
-      <c r="AP50" s="18"/>
-      <c r="AQ50" s="18"/>
-      <c r="AR50" s="18"/>
-      <c r="AS50" s="18"/>
-      <c r="AT50" s="18"/>
-      <c r="AU50" s="18"/>
-      <c r="AV50" s="18"/>
-      <c r="AW50" s="18"/>
-      <c r="AX50" s="18"/>
-      <c r="AY50" s="18"/>
-      <c r="AZ50" s="18"/>
-      <c r="BA50" s="18"/>
-      <c r="BB50" s="18"/>
-      <c r="BC50" s="18"/>
-      <c r="BD50" s="18"/>
-      <c r="BE50" s="18"/>
-      <c r="BF50" s="18"/>
-      <c r="BG50" s="18"/>
-      <c r="BH50" s="18"/>
-      <c r="BI50" s="18"/>
-      <c r="BJ50" s="18"/>
-      <c r="BK50" s="18"/>
-      <c r="BL50" s="18"/>
-      <c r="BM50" s="18"/>
-      <c r="BN50" s="18"/>
-      <c r="BO50" s="18"/>
-      <c r="BP50" s="18"/>
-      <c r="BQ50" s="18"/>
-      <c r="BR50" s="18"/>
-      <c r="BS50" s="18"/>
-      <c r="BT50" s="18"/>
-      <c r="BU50" s="18"/>
-      <c r="BV50" s="18"/>
-      <c r="BW50" s="18"/>
-      <c r="BX50" s="18"/>
-      <c r="BY50" s="18"/>
-      <c r="BZ50" s="18"/>
-      <c r="CA50" s="18"/>
-      <c r="CB50" s="18"/>
-      <c r="CC50" s="18"/>
-      <c r="CD50" s="18"/>
-      <c r="CE50" s="18"/>
-      <c r="CF50" s="18"/>
-      <c r="CG50" s="18"/>
-      <c r="CH50" s="18"/>
-      <c r="CI50" s="18"/>
-      <c r="CJ50" s="18"/>
-      <c r="CK50" s="18"/>
-      <c r="CL50" s="18"/>
-      <c r="CM50" s="18"/>
-      <c r="CN50" s="18"/>
-      <c r="CO50" s="18"/>
-      <c r="CP50" s="18"/>
-      <c r="CQ50" s="18"/>
-      <c r="CR50" s="18"/>
-      <c r="CS50" s="18"/>
-      <c r="CT50" s="18"/>
-      <c r="CU50" s="18"/>
-      <c r="CV50" s="18"/>
+      <c r="Y50" s="59"/>
+      <c r="Z50" s="59"/>
+      <c r="AA50" s="59"/>
+      <c r="AB50" s="59"/>
+      <c r="AC50" s="59"/>
+      <c r="AD50" s="59"/>
+      <c r="AE50" s="59"/>
+      <c r="AF50" s="59"/>
+      <c r="AG50" s="59"/>
+      <c r="AH50" s="59"/>
+      <c r="AI50" s="59"/>
+      <c r="AJ50" s="59"/>
+      <c r="AK50" s="59"/>
+      <c r="AL50" s="59"/>
+      <c r="AM50" s="59"/>
+      <c r="AN50" s="59"/>
+      <c r="AO50" s="59"/>
+      <c r="AP50" s="59"/>
+      <c r="AQ50" s="59"/>
+      <c r="AR50" s="59"/>
+      <c r="AS50" s="59"/>
+      <c r="AT50" s="59"/>
+      <c r="AU50" s="59"/>
+      <c r="AV50" s="59"/>
+      <c r="AW50" s="59"/>
+      <c r="AX50" s="59"/>
+      <c r="AY50" s="59"/>
+      <c r="AZ50" s="59"/>
+      <c r="BA50" s="59"/>
+      <c r="BB50" s="59"/>
+      <c r="BC50" s="59"/>
+      <c r="BD50" s="59"/>
+      <c r="BE50" s="59"/>
+      <c r="BF50" s="59"/>
+      <c r="BG50" s="59"/>
+      <c r="BH50" s="59"/>
+      <c r="BI50" s="59"/>
+      <c r="BJ50" s="59"/>
+      <c r="BK50" s="59"/>
+      <c r="BL50" s="59"/>
+      <c r="BM50" s="59"/>
+      <c r="BN50" s="59"/>
+      <c r="BO50" s="59"/>
+      <c r="BP50" s="59"/>
+      <c r="BQ50" s="59"/>
+      <c r="BR50" s="59"/>
+      <c r="BS50" s="59"/>
+      <c r="BT50" s="59"/>
+      <c r="BU50" s="59"/>
+      <c r="BV50" s="59"/>
+      <c r="BW50" s="59"/>
+      <c r="BX50" s="59"/>
+      <c r="BY50" s="59"/>
+      <c r="BZ50" s="59"/>
+      <c r="CA50" s="59"/>
+      <c r="CB50" s="59"/>
+      <c r="CC50" s="59"/>
+      <c r="CD50" s="59"/>
+      <c r="CE50" s="59"/>
+      <c r="CF50" s="59"/>
+      <c r="CG50" s="59"/>
+      <c r="CH50" s="59"/>
+      <c r="CI50" s="59"/>
+      <c r="CJ50" s="59"/>
+      <c r="CK50" s="59"/>
+      <c r="CL50" s="59"/>
+      <c r="CM50" s="59"/>
+      <c r="CN50" s="59"/>
+      <c r="CO50" s="59"/>
+      <c r="CP50" s="59"/>
+      <c r="CQ50" s="59"/>
+      <c r="CR50" s="59"/>
+      <c r="CS50" s="59"/>
+      <c r="CT50" s="59"/>
+      <c r="CU50" s="59"/>
+      <c r="CV50" s="59"/>
     </row>
     <row r="51" spans="1:100" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="X51" s="5"/>
@@ -6060,113 +6060,185 @@
     </row>
     <row r="53" spans="1:100" ht="0.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="54" spans="1:100" ht="9.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="19" t="s">
+      <c r="A54" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="B54" s="19"/>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
-      <c r="H54" s="19"/>
-      <c r="I54" s="19"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="19"/>
-      <c r="L54" s="19"/>
-      <c r="M54" s="19"/>
-      <c r="N54" s="19"/>
-      <c r="O54" s="19"/>
-      <c r="P54" s="19"/>
-      <c r="Q54" s="19"/>
-      <c r="R54" s="19"/>
-      <c r="S54" s="19"/>
-      <c r="T54" s="19"/>
-      <c r="U54" s="19"/>
-      <c r="V54" s="19"/>
-      <c r="W54" s="19"/>
-      <c r="X54" s="19"/>
-      <c r="Y54" s="19"/>
-      <c r="Z54" s="19"/>
-      <c r="AA54" s="19"/>
-      <c r="AB54" s="19"/>
-      <c r="AC54" s="19"/>
-      <c r="AE54" s="20"/>
-      <c r="AF54" s="20"/>
-      <c r="AG54" s="20"/>
-      <c r="AH54" s="20"/>
-      <c r="AI54" s="20"/>
-      <c r="AJ54" s="20"/>
-      <c r="AK54" s="20"/>
-      <c r="AL54" s="20"/>
-      <c r="AM54" s="20"/>
-      <c r="AN54" s="20"/>
-      <c r="AO54" s="20"/>
-      <c r="AP54" s="20"/>
-      <c r="AQ54" s="20"/>
-      <c r="AR54" s="20"/>
-      <c r="AS54" s="20"/>
-      <c r="AT54" s="20"/>
-      <c r="AU54" s="20"/>
-      <c r="AV54" s="20"/>
-      <c r="AW54" s="20"/>
-      <c r="AX54" s="20"/>
-      <c r="AY54" s="20"/>
-      <c r="AZ54" s="20"/>
-      <c r="BA54" s="20"/>
-      <c r="BB54" s="20"/>
-      <c r="BC54" s="20"/>
-      <c r="BD54" s="20"/>
-      <c r="BE54" s="20"/>
-      <c r="BF54" s="20"/>
-      <c r="BG54" s="20"/>
-      <c r="BH54" s="20"/>
-      <c r="BI54" s="20"/>
-      <c r="BJ54" s="20"/>
-      <c r="BK54" s="20"/>
-      <c r="BL54" s="20"/>
-      <c r="BM54" s="20"/>
-      <c r="BN54" s="20"/>
-      <c r="BO54" s="20"/>
-      <c r="BP54" s="20"/>
-      <c r="BQ54" s="20"/>
-      <c r="BR54" s="20"/>
-      <c r="BS54" s="20"/>
-      <c r="BT54" s="20"/>
-      <c r="BU54" s="20"/>
-      <c r="BV54" s="20"/>
-      <c r="BW54" s="20"/>
-      <c r="BX54" s="20"/>
-      <c r="BY54" s="20"/>
-      <c r="BZ54" s="20"/>
-      <c r="CA54" s="20"/>
-      <c r="CB54" s="20"/>
-      <c r="CC54" s="20"/>
-      <c r="CD54" s="20"/>
-      <c r="CE54" s="20"/>
-      <c r="CF54" s="20"/>
-      <c r="CG54" s="20"/>
-      <c r="CH54" s="20"/>
-      <c r="CI54" s="20"/>
-      <c r="CJ54" s="20"/>
-      <c r="CK54" s="20"/>
-      <c r="CL54" s="20"/>
-      <c r="CM54" s="20"/>
-      <c r="CN54" s="20"/>
-      <c r="CO54" s="20"/>
-      <c r="CP54" s="20"/>
-      <c r="CQ54" s="20"/>
-      <c r="CR54" s="20"/>
-      <c r="CS54" s="20"/>
-      <c r="CT54" s="20"/>
-      <c r="CU54" s="20"/>
-      <c r="CV54" s="20"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="52"/>
+      <c r="D54" s="52"/>
+      <c r="E54" s="52"/>
+      <c r="F54" s="52"/>
+      <c r="G54" s="52"/>
+      <c r="H54" s="52"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="52"/>
+      <c r="K54" s="52"/>
+      <c r="L54" s="52"/>
+      <c r="M54" s="52"/>
+      <c r="N54" s="52"/>
+      <c r="O54" s="52"/>
+      <c r="P54" s="52"/>
+      <c r="Q54" s="52"/>
+      <c r="R54" s="52"/>
+      <c r="S54" s="52"/>
+      <c r="T54" s="52"/>
+      <c r="U54" s="52"/>
+      <c r="V54" s="52"/>
+      <c r="W54" s="52"/>
+      <c r="X54" s="52"/>
+      <c r="Y54" s="52"/>
+      <c r="Z54" s="52"/>
+      <c r="AA54" s="52"/>
+      <c r="AB54" s="52"/>
+      <c r="AC54" s="52"/>
+      <c r="AE54" s="42"/>
+      <c r="AF54" s="42"/>
+      <c r="AG54" s="42"/>
+      <c r="AH54" s="42"/>
+      <c r="AI54" s="42"/>
+      <c r="AJ54" s="42"/>
+      <c r="AK54" s="42"/>
+      <c r="AL54" s="42"/>
+      <c r="AM54" s="42"/>
+      <c r="AN54" s="42"/>
+      <c r="AO54" s="42"/>
+      <c r="AP54" s="42"/>
+      <c r="AQ54" s="42"/>
+      <c r="AR54" s="42"/>
+      <c r="AS54" s="42"/>
+      <c r="AT54" s="42"/>
+      <c r="AU54" s="42"/>
+      <c r="AV54" s="42"/>
+      <c r="AW54" s="42"/>
+      <c r="AX54" s="42"/>
+      <c r="AY54" s="42"/>
+      <c r="AZ54" s="42"/>
+      <c r="BA54" s="42"/>
+      <c r="BB54" s="42"/>
+      <c r="BC54" s="42"/>
+      <c r="BD54" s="42"/>
+      <c r="BE54" s="42"/>
+      <c r="BF54" s="42"/>
+      <c r="BG54" s="42"/>
+      <c r="BH54" s="42"/>
+      <c r="BI54" s="42"/>
+      <c r="BJ54" s="42"/>
+      <c r="BK54" s="42"/>
+      <c r="BL54" s="42"/>
+      <c r="BM54" s="42"/>
+      <c r="BN54" s="42"/>
+      <c r="BO54" s="42"/>
+      <c r="BP54" s="42"/>
+      <c r="BQ54" s="42"/>
+      <c r="BR54" s="42"/>
+      <c r="BS54" s="42"/>
+      <c r="BT54" s="42"/>
+      <c r="BU54" s="42"/>
+      <c r="BV54" s="42"/>
+      <c r="BW54" s="42"/>
+      <c r="BX54" s="42"/>
+      <c r="BY54" s="42"/>
+      <c r="BZ54" s="42"/>
+      <c r="CA54" s="42"/>
+      <c r="CB54" s="42"/>
+      <c r="CC54" s="42"/>
+      <c r="CD54" s="42"/>
+      <c r="CE54" s="42"/>
+      <c r="CF54" s="42"/>
+      <c r="CG54" s="42"/>
+      <c r="CH54" s="42"/>
+      <c r="CI54" s="42"/>
+      <c r="CJ54" s="42"/>
+      <c r="CK54" s="42"/>
+      <c r="CL54" s="42"/>
+      <c r="CM54" s="42"/>
+      <c r="CN54" s="42"/>
+      <c r="CO54" s="42"/>
+      <c r="CP54" s="42"/>
+      <c r="CQ54" s="42"/>
+      <c r="CR54" s="42"/>
+      <c r="CS54" s="42"/>
+      <c r="CT54" s="42"/>
+      <c r="CU54" s="42"/>
+      <c r="CV54" s="42"/>
     </row>
     <row r="55" spans="1:100" ht="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="64" spans="1:100" ht="5.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="66" ht="3" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="88">
+    <mergeCell ref="V43:CV43"/>
+    <mergeCell ref="X50:CV50"/>
+    <mergeCell ref="A54:AC54"/>
+    <mergeCell ref="AE54:CV54"/>
+    <mergeCell ref="A49:V49"/>
+    <mergeCell ref="X49:CV49"/>
+    <mergeCell ref="A45:V45"/>
+    <mergeCell ref="CK45:CV45"/>
+    <mergeCell ref="CK46:CV46"/>
+    <mergeCell ref="W47:AW47"/>
+    <mergeCell ref="CK47:CV47"/>
+    <mergeCell ref="X45:AW45"/>
+    <mergeCell ref="W46:AW46"/>
+    <mergeCell ref="BO46:BZ46"/>
+    <mergeCell ref="CA45:CJ45"/>
+    <mergeCell ref="AF16:AG16"/>
+    <mergeCell ref="AI16:BD16"/>
+    <mergeCell ref="A39:P39"/>
+    <mergeCell ref="R39:CV39"/>
+    <mergeCell ref="R40:CV40"/>
+    <mergeCell ref="T25:CV25"/>
+    <mergeCell ref="A32:CV32"/>
+    <mergeCell ref="BM16:BO16"/>
+    <mergeCell ref="BF16:BH16"/>
+    <mergeCell ref="BX33:CP33"/>
+    <mergeCell ref="S33:BP33"/>
+    <mergeCell ref="A33:Q33"/>
+    <mergeCell ref="A18:P18"/>
+    <mergeCell ref="R18:CV18"/>
+    <mergeCell ref="CC28:CM28"/>
+    <mergeCell ref="BK29:BS29"/>
+    <mergeCell ref="V42:CV42"/>
+    <mergeCell ref="A42:T42"/>
+    <mergeCell ref="BX34:CP34"/>
+    <mergeCell ref="AZ30:BJ30"/>
+    <mergeCell ref="BT30:CB30"/>
+    <mergeCell ref="CC30:CM30"/>
+    <mergeCell ref="A30:V30"/>
+    <mergeCell ref="W30:AF30"/>
+    <mergeCell ref="S34:BP34"/>
+    <mergeCell ref="BX36:CP36"/>
+    <mergeCell ref="BX37:CP37"/>
+    <mergeCell ref="W36:BP36"/>
+    <mergeCell ref="W37:BP37"/>
+    <mergeCell ref="BT29:CB29"/>
+    <mergeCell ref="CC29:CM29"/>
+    <mergeCell ref="A21:P21"/>
+    <mergeCell ref="R19:CV19"/>
+    <mergeCell ref="A27:CV27"/>
+    <mergeCell ref="AZ28:BJ28"/>
+    <mergeCell ref="A24:Q24"/>
+    <mergeCell ref="A29:V29"/>
+    <mergeCell ref="W29:AF29"/>
+    <mergeCell ref="AG29:AO29"/>
+    <mergeCell ref="AP29:AY29"/>
+    <mergeCell ref="AZ29:BJ29"/>
+    <mergeCell ref="T5:X6"/>
+    <mergeCell ref="AZ31:BJ31"/>
+    <mergeCell ref="BK31:BS31"/>
+    <mergeCell ref="BT28:CB28"/>
+    <mergeCell ref="CN28:CV28"/>
+    <mergeCell ref="BK28:BS28"/>
+    <mergeCell ref="BT31:CB31"/>
+    <mergeCell ref="CC31:CM31"/>
+    <mergeCell ref="A31:V31"/>
+    <mergeCell ref="W31:AF31"/>
+    <mergeCell ref="AG31:AO31"/>
+    <mergeCell ref="AP31:AY31"/>
+    <mergeCell ref="AG30:AO30"/>
+    <mergeCell ref="AP30:AY30"/>
+    <mergeCell ref="A28:V28"/>
+    <mergeCell ref="W28:AF28"/>
     <mergeCell ref="Z2:AR4"/>
     <mergeCell ref="Z5:AR6"/>
     <mergeCell ref="AS2:BL4"/>
@@ -6183,78 +6255,6 @@
     <mergeCell ref="AB16:AE16"/>
     <mergeCell ref="R21:CV21"/>
     <mergeCell ref="R22:CV22"/>
-    <mergeCell ref="T5:X6"/>
-    <mergeCell ref="AZ31:BJ31"/>
-    <mergeCell ref="BK31:BS31"/>
-    <mergeCell ref="BT28:CB28"/>
-    <mergeCell ref="CN28:CV28"/>
-    <mergeCell ref="BK28:BS28"/>
-    <mergeCell ref="BT31:CB31"/>
-    <mergeCell ref="CC31:CM31"/>
-    <mergeCell ref="A31:V31"/>
-    <mergeCell ref="W31:AF31"/>
-    <mergeCell ref="AG31:AO31"/>
-    <mergeCell ref="AP31:AY31"/>
-    <mergeCell ref="AG30:AO30"/>
-    <mergeCell ref="AP30:AY30"/>
-    <mergeCell ref="A28:V28"/>
-    <mergeCell ref="W28:AF28"/>
-    <mergeCell ref="BT29:CB29"/>
-    <mergeCell ref="CC29:CM29"/>
-    <mergeCell ref="A21:P21"/>
-    <mergeCell ref="R19:CV19"/>
-    <mergeCell ref="A27:CV27"/>
-    <mergeCell ref="AZ28:BJ28"/>
-    <mergeCell ref="A24:Q24"/>
-    <mergeCell ref="A29:V29"/>
-    <mergeCell ref="W29:AF29"/>
-    <mergeCell ref="AG29:AO29"/>
-    <mergeCell ref="AP29:AY29"/>
-    <mergeCell ref="AZ29:BJ29"/>
-    <mergeCell ref="V42:CV42"/>
-    <mergeCell ref="A42:T42"/>
-    <mergeCell ref="BX34:CP34"/>
-    <mergeCell ref="AZ30:BJ30"/>
-    <mergeCell ref="BT30:CB30"/>
-    <mergeCell ref="CC30:CM30"/>
-    <mergeCell ref="A30:V30"/>
-    <mergeCell ref="W30:AF30"/>
-    <mergeCell ref="AF16:AG16"/>
-    <mergeCell ref="AI16:BD16"/>
-    <mergeCell ref="A39:P39"/>
-    <mergeCell ref="R39:CV39"/>
-    <mergeCell ref="R40:CV40"/>
-    <mergeCell ref="T25:CV25"/>
-    <mergeCell ref="A32:CV32"/>
-    <mergeCell ref="BM16:BO16"/>
-    <mergeCell ref="BF16:BH16"/>
-    <mergeCell ref="BX33:CP33"/>
-    <mergeCell ref="S33:BP33"/>
-    <mergeCell ref="A33:Q33"/>
-    <mergeCell ref="A18:P18"/>
-    <mergeCell ref="R18:CV18"/>
-    <mergeCell ref="CC28:CM28"/>
-    <mergeCell ref="BK29:BS29"/>
-    <mergeCell ref="V43:CV43"/>
-    <mergeCell ref="X50:CV50"/>
-    <mergeCell ref="A54:AC54"/>
-    <mergeCell ref="AE54:CV54"/>
-    <mergeCell ref="A49:V49"/>
-    <mergeCell ref="X49:CV49"/>
-    <mergeCell ref="A45:V45"/>
-    <mergeCell ref="CK45:CV45"/>
-    <mergeCell ref="CK46:CV46"/>
-    <mergeCell ref="W47:AW47"/>
-    <mergeCell ref="CK47:CV47"/>
-    <mergeCell ref="X45:AW45"/>
-    <mergeCell ref="W46:AW46"/>
-    <mergeCell ref="BO46:BZ46"/>
-    <mergeCell ref="CA45:CJ45"/>
-    <mergeCell ref="S34:BP34"/>
-    <mergeCell ref="BX36:CP36"/>
-    <mergeCell ref="BX37:CP37"/>
-    <mergeCell ref="W36:BP36"/>
-    <mergeCell ref="W37:BP37"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.39370078740157483" bottom="0.19685039370078741" header="0" footer="0"/>
